--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V380"/>
+  <dimension ref="A1:V389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37138,10 +37138,8 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A375" t="n">
+        <v>1729</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -37193,7 +37191,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N375" s="2" t="n">
+      <c r="N375" s="1" t="n">
         <v>45988</v>
       </c>
       <c r="O375" t="inlineStr">
@@ -37238,10 +37236,8 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>1733</t>
-        </is>
+      <c r="A376" t="n">
+        <v>1733</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -37293,7 +37289,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N376" s="2" t="n">
+      <c r="N376" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="O376" t="inlineStr">
@@ -37338,10 +37334,8 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A377" t="n">
+        <v>2805</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -37393,7 +37387,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N377" s="2" t="n">
+      <c r="N377" s="1" t="n">
         <v>46085</v>
       </c>
       <c r="O377" t="inlineStr">
@@ -37438,10 +37432,8 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A378" t="n">
+        <v>2805</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -37493,7 +37485,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N378" s="2" t="n">
+      <c r="N378" s="1" t="n">
         <v>46085</v>
       </c>
       <c r="O378" t="inlineStr">
@@ -37538,10 +37530,8 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
+      <c r="A379" t="n">
+        <v>2813</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
@@ -37593,7 +37583,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N379" s="2" t="n">
+      <c r="N379" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O379" t="inlineStr">
@@ -37638,10 +37628,8 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
+      <c r="A380" t="n">
+        <v>2813</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -37685,7 +37673,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N380" s="2" t="n">
+      <c r="N380" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O380" t="inlineStr">
@@ -37724,6 +37712,906 @@
         </is>
       </c>
       <c r="V380" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Santander de Quilichao</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>106198</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN BIOINGENIERÍA</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I381" t="n">
+        <v>42</v>
+      </c>
+      <c r="J381" t="n">
+        <v>2</v>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N381" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>Ingeniería biomédica y afines</t>
+        </is>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD-COLEGIO MAYOR DE CUNDINAMARCA</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>118590</v>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EMPRENDIMIENTO</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I382" t="n">
+        <v>40</v>
+      </c>
+      <c r="J382" t="n">
+        <v>3</v>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N382" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL ATLANTICO</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Puerto Colombia</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>118578</v>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ACTIVIDAD FÍSICA ADAPTADA</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I383" t="n">
+        <v>48</v>
+      </c>
+      <c r="J383" t="n">
+        <v>4</v>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N383" s="2" t="n">
+        <v>46012</v>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>Bienestar</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>Atención, protección y servicios a la infancia, adolescencia y juventud</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INDUSTRIAL DE SANTANDER</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>118579</v>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PSIQUIATRÍA</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I384" t="n">
+        <v>167</v>
+      </c>
+      <c r="J384" t="n">
+        <v>3</v>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N384" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>118595</v>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PSICOLOGÍA ORGANIZACIONAL</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I385" t="n">
+        <v>30</v>
+      </c>
+      <c r="J385" t="n">
+        <v>2</v>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N385" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>118594</v>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN PSICOLOGÍA CLÍNICA</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I386" t="n">
+        <v>55</v>
+      </c>
+      <c r="J386" t="n">
+        <v>4</v>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N386" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>118582</v>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ADMINISTRACIÓN DE EMPRESAS - MBA</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I387" t="n">
+        <v>42</v>
+      </c>
+      <c r="J387" t="n">
+        <v>3</v>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N387" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2707</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA JUAN N. CORPAS</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>118591</v>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN MEDICINA FAMILIAR</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I388" t="n">
+        <v>192</v>
+      </c>
+      <c r="J388" t="n">
+        <v>6</v>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N388" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>ESCUELA TECNOLOGICA INSTITUTO TECNICO CENTRAL</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>118587</v>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I389" t="n">
+        <v>48</v>
+      </c>
+      <c r="J389" t="n">
+        <v>4</v>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N389" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
         <is>
           <t>Ingenierías</t>
         </is>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V389"/>
+  <dimension ref="A1:V398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37718,10 +37718,8 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A381" t="n">
+        <v>1110</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -37773,7 +37771,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N381" s="2" t="n">
+      <c r="N381" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="O381" t="inlineStr">
@@ -37818,10 +37816,8 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
+      <c r="A382" t="n">
+        <v>1121</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -37873,7 +37869,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N382" s="2" t="n">
+      <c r="N382" s="1" t="n">
         <v>46006</v>
       </c>
       <c r="O382" t="inlineStr">
@@ -37918,10 +37914,8 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
+      <c r="A383" t="n">
+        <v>1202</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -37973,7 +37967,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N383" s="2" t="n">
+      <c r="N383" s="1" t="n">
         <v>46012</v>
       </c>
       <c r="O383" t="inlineStr">
@@ -38018,10 +38012,8 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
+      <c r="A384" t="n">
+        <v>1204</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
@@ -38073,7 +38065,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N384" s="2" t="n">
+      <c r="N384" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O384" t="inlineStr">
@@ -38118,10 +38110,8 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A385" t="n">
+        <v>1826</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -38173,7 +38163,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N385" s="2" t="n">
+      <c r="N385" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O385" t="inlineStr">
@@ -38218,10 +38208,8 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A386" t="n">
+        <v>1826</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -38273,7 +38261,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N386" s="2" t="n">
+      <c r="N386" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="O386" t="inlineStr">
@@ -38318,10 +38306,8 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
+      <c r="A387" t="n">
+        <v>1830</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -38373,7 +38359,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N387" s="2" t="n">
+      <c r="N387" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O387" t="inlineStr">
@@ -38418,10 +38404,8 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>2707</t>
-        </is>
+      <c r="A388" t="n">
+        <v>2707</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -38473,7 +38457,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N388" s="2" t="n">
+      <c r="N388" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="O388" t="inlineStr">
@@ -38518,10 +38502,8 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>4108</t>
-        </is>
+      <c r="A389" t="n">
+        <v>4108</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -38573,7 +38555,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N389" s="2" t="n">
+      <c r="N389" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O389" t="inlineStr">
@@ -38614,6 +38596,906 @@
       <c r="V389" t="inlineStr">
         <is>
           <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PEDAGOGICA Y TECNOLOGICA DE COLOMBIA - UPTC</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>118616</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INGENIERÍA DE LOS RECURSOS HÍDRICOS</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I390" t="n">
+        <v>24</v>
+      </c>
+      <c r="J390" t="n">
+        <v>2</v>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N390" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>118609</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN FINANCIERA</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I391" t="n">
+        <v>39</v>
+      </c>
+      <c r="J391" t="n">
+        <v>3</v>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N391" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>118620</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN SISTEMAS INTEGRADOS DE GESTIÓN</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I392" t="n">
+        <v>40</v>
+      </c>
+      <c r="J392" t="n">
+        <v>3</v>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N392" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD FRANCISCO DE PAULA SANTANDER</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Ocaña</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>118468</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ESTRUCTURAS</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I393" t="n">
+        <v>24</v>
+      </c>
+      <c r="J393" t="n">
+        <v>2</v>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N393" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>118614</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ORTOPEDIA Y TRAUMATOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I394" t="n">
+        <v>308</v>
+      </c>
+      <c r="J394" t="n">
+        <v>4</v>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N394" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>118624</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN MODELACIÓN Y COMPUTACIÓN CIENTÍFICA</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I395" t="n">
+        <v>36</v>
+      </c>
+      <c r="J395" t="n">
+        <v>3</v>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N395" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>118605</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTELIGENCIA ARTIFICIAL Y DERECHO</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I396" t="n">
+        <v>26</v>
+      </c>
+      <c r="J396" t="n">
+        <v>2</v>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N396" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>9899</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE COLOMBIA - UNIVERSITARIA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>118596</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I397" t="n">
+        <v>30</v>
+      </c>
+      <c r="J397" t="n">
+        <v>3</v>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N397" s="2" t="n">
+        <v>43882</v>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>9899</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE COLOMBIA - UNIVERSITARIA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>118597</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA FINANCIERA</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I398" t="n">
+        <v>34</v>
+      </c>
+      <c r="J398" t="n">
+        <v>2</v>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N398" s="2" t="n">
+        <v>44308</v>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V398"/>
+  <dimension ref="A1:V432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38600,10 +38600,8 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A390" t="n">
+        <v>1106</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
@@ -38655,7 +38653,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N390" s="2" t="n">
+      <c r="N390" s="1" t="n">
         <v>46000</v>
       </c>
       <c r="O390" t="inlineStr">
@@ -38700,10 +38698,8 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A391" t="n">
+        <v>1203</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -38755,7 +38751,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N391" s="2" t="n">
+      <c r="N391" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O391" t="inlineStr">
@@ -38800,10 +38796,8 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
+      <c r="A392" t="n">
+        <v>1205</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -38855,7 +38849,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N392" s="2" t="n">
+      <c r="N392" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O392" t="inlineStr">
@@ -38900,10 +38894,8 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>1210</t>
-        </is>
+      <c r="A393" t="n">
+        <v>1210</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -38955,7 +38947,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N393" s="2" t="n">
+      <c r="N393" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="O393" t="inlineStr">
@@ -39000,10 +38992,8 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A394" t="n">
+        <v>1711</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -39055,7 +39045,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N394" s="2" t="n">
+      <c r="N394" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O394" t="inlineStr">
@@ -39100,10 +39090,8 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A395" t="n">
+        <v>1812</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -39155,7 +39143,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N395" s="2" t="n">
+      <c r="N395" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O395" t="inlineStr">
@@ -39200,10 +39188,8 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
+      <c r="A396" t="n">
+        <v>2302</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -39255,7 +39241,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N396" s="2" t="n">
+      <c r="N396" s="1" t="n">
         <v>46020</v>
       </c>
       <c r="O396" t="inlineStr">
@@ -39300,10 +39286,8 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>9899</t>
-        </is>
+      <c r="A397" t="n">
+        <v>9899</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -39355,7 +39339,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N397" s="2" t="n">
+      <c r="N397" s="1" t="n">
         <v>43882</v>
       </c>
       <c r="O397" t="inlineStr">
@@ -39400,10 +39384,8 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>9899</t>
-        </is>
+      <c r="A398" t="n">
+        <v>9899</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -39455,7 +39437,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N398" s="2" t="n">
+      <c r="N398" s="1" t="n">
         <v>44308</v>
       </c>
       <c r="O398" t="inlineStr">
@@ -39496,6 +39478,3408 @@
       <c r="V398" t="inlineStr">
         <is>
           <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SURCOLOMBIANA</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>118673</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ESTRUCTURAS</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I399" t="n">
+        <v>26</v>
+      </c>
+      <c r="J399" t="n">
+        <v>2</v>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N399" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL TOLIMA</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F400" t="n">
+        <v>118671</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ESTADÍSTICA APLICADA Y CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I400" t="n">
+        <v>44</v>
+      </c>
+      <c r="J400" t="n">
+        <v>3</v>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N400" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>Estadística</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>118647</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO CONSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I401" t="n">
+        <v>25</v>
+      </c>
+      <c r="J401" t="n">
+        <v>2</v>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N401" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EXTERNADO DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F402" t="n">
+        <v>118648</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE RIESGOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I402" t="n">
+        <v>25</v>
+      </c>
+      <c r="J402" t="n">
+        <v>2</v>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N402" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
+        <v>118651</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN PSICOLOGÍA SOCIAL</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I403" t="n">
+        <v>44</v>
+      </c>
+      <c r="J403" t="n">
+        <v>4</v>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N403" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F404" t="n">
+        <v>118666</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DESARROLLO DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I404" t="n">
+        <v>24</v>
+      </c>
+      <c r="J404" t="n">
+        <v>2</v>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N404" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>118645</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE INSTITUCIONES DE LA SALUD</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I405" t="n">
+        <v>26</v>
+      </c>
+      <c r="J405" t="n">
+        <v>2</v>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N405" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F406" t="n">
+        <v>118664</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SEGURIDAD DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I406" t="n">
+        <v>30</v>
+      </c>
+      <c r="J406" t="n">
+        <v>2</v>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N406" s="2" t="n">
+        <v>45650</v>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>118631</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SOSTENIBILIDAD Y GOBERNANZA</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I407" t="n">
+        <v>26</v>
+      </c>
+      <c r="J407" t="n">
+        <v>2</v>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N407" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>1724</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F408" t="n">
+        <v>118530</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I408" t="n">
+        <v>52</v>
+      </c>
+      <c r="J408" t="n">
+        <v>4</v>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N408" s="2" t="n">
+        <v>45977</v>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>Odontología y estudios dentales</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>1726</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE ORIENTE -UCO</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>118674</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CIENCIAS BIOLÓGICAS</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I409" t="n">
+        <v>40</v>
+      </c>
+      <c r="J409" t="n">
+        <v>4</v>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N409" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>Biología, microbiología y afines</t>
+        </is>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>1727</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>118652</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE LA CONSTRUCCIÓN E INTERVENTORÍA</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I410" t="n">
+        <v>25</v>
+      </c>
+      <c r="J410" t="n">
+        <v>2</v>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N410" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>118641</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SEGURIDAD DIGITAL</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I411" t="n">
+        <v>32</v>
+      </c>
+      <c r="J411" t="n">
+        <v>2</v>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N411" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>118642</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SEGURIDAD DIGITAL</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I412" t="n">
+        <v>32</v>
+      </c>
+      <c r="J412" t="n">
+        <v>2</v>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N412" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F413" t="n">
+        <v>118633</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ENFERMERÍA ONCOLÓGICA</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I413" t="n">
+        <v>52</v>
+      </c>
+      <c r="J413" t="n">
+        <v>3</v>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F414" t="n">
+        <v>118644</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EVALUACIÓN Y MANEJO DEL IMPACTO AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I414" t="n">
+        <v>72</v>
+      </c>
+      <c r="J414" t="n">
+        <v>4</v>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LA GRAN COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F415" t="n">
+        <v>118627</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INTELIGENCIA ANALÍTICA PARA LA TOMA DE DECISIONES</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I415" t="n">
+        <v>42</v>
+      </c>
+      <c r="J415" t="n">
+        <v>3</v>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>Estadística</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V415" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SALLE</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F416" t="n">
+        <v>118630</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ONCOLOGÍA CLÍNICA DE PEQUEÑOS ANIMALES</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I416" t="n">
+        <v>34</v>
+      </c>
+      <c r="J416" t="n">
+        <v>2</v>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>Medicina veterinaria</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LIBRE</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F417" t="n">
+        <v>118643</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA TRIBUTARIA</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I417" t="n">
+        <v>49</v>
+      </c>
+      <c r="J417" t="n">
+        <v>3</v>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N417" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F418" t="n">
+        <v>118653</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ENFERMERÍA EN CUIDADO CRÍTITO PEDIÁTRICO</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Presencial-Virtual</t>
+        </is>
+      </c>
+      <c r="I418" t="n">
+        <v>30</v>
+      </c>
+      <c r="J418" t="n">
+        <v>2</v>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N418" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>1814</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA LATINOAMERICANA-UNAULA-</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F419" t="n">
+        <v>118649</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANALÍTICA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I419" t="n">
+        <v>24</v>
+      </c>
+      <c r="J419" t="n">
+        <v>2</v>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N419" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSIDAD PILOTO DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F420" t="n">
+        <v>118638</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN SEGURIDAD INFORMATICA</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I420" t="n">
+        <v>27</v>
+      </c>
+      <c r="J420" t="n">
+        <v>1</v>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N420" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F421" t="n">
+        <v>118629</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTELIGENCIA ARTIFICIAL APLICADA</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I421" t="n">
+        <v>22</v>
+      </c>
+      <c r="J421" t="n">
+        <v>2</v>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N421" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F422" t="n">
+        <v>118628</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ENFERMERÍA ONCOLÓGICA</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I422" t="n">
+        <v>57</v>
+      </c>
+      <c r="J422" t="n">
+        <v>4</v>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N422" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F423" t="n">
+        <v>90793</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN ADMINISTRACION DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I423" t="n">
+        <v>48</v>
+      </c>
+      <c r="J423" t="n">
+        <v>4</v>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L423" t="n">
+        <v>13364000</v>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N423" s="2" t="n">
+        <v>40429</v>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V423" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATÓLICA LUIS AMIGÓ</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F424" t="n">
+        <v>118665</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I424" t="n">
+        <v>28</v>
+      </c>
+      <c r="J424" t="n">
+        <v>2</v>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N424" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA SANITAS</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F425" t="n">
+        <v>118662</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ENDOCRINOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I425" t="n">
+        <v>120</v>
+      </c>
+      <c r="J425" t="n">
+        <v>4</v>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N425" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2811</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ESCUELA COLOMBIANA DE INGENIERIA JULIO GARAVITO</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F426" t="n">
+        <v>118659</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INGENIERÍA ELECTRÓNICA</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I426" t="n">
+        <v>40</v>
+      </c>
+      <c r="J426" t="n">
+        <v>2</v>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N426" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAN</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F427" t="n">
+        <v>118650</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTELIGENCIA COMERCIAL Y DE MERCADEO</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I427" t="n">
+        <v>28</v>
+      </c>
+      <c r="J427" t="n">
+        <v>2</v>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N427" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F428" t="n">
+        <v>118669</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ENERGÍAS RENOVABLES</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I428" t="n">
+        <v>26</v>
+      </c>
+      <c r="J428" t="n">
+        <v>2</v>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N428" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>Electricidad y energía</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>Ingeniería eléctrica y afines</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2840</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA EMPRESARIAL ALEXANDER VON HUMBOLDT - CUE</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F429" t="n">
+        <v>118672</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTERVENCIÓN PSICOSOCIAL COMUNITARIA</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I429" t="n">
+        <v>26</v>
+      </c>
+      <c r="J429" t="n">
+        <v>2</v>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N429" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>Sociología, Antropología y estudios culturales</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA ANTONIO JOSE CAMACHO</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F430" t="n">
+        <v>118682</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE NEGOCIOS</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Presencial-Virtual</t>
+        </is>
+      </c>
+      <c r="I430" t="n">
+        <v>30</v>
+      </c>
+      <c r="J430" t="n">
+        <v>2</v>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N430" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA ANTONIO JOSE CAMACHO</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F431" t="n">
+        <v>118683</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INGENIERÍA ELECTRÓNICA</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I431" t="n">
+        <v>40</v>
+      </c>
+      <c r="J431" t="n">
+        <v>3</v>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N431" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CLARETIANA - UNICLARETIANA</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Chocó</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Quibdó</t>
+        </is>
+      </c>
+      <c r="F432" t="n">
+        <v>118639</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ESTUDIOS BÍBLICOS</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I432" t="n">
+        <v>39</v>
+      </c>
+      <c r="J432" t="n">
+        <v>3</v>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N432" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>Religión y Teología</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>Filosofía, teología y afines</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V432"/>
+  <dimension ref="A1:V482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39482,10 +39482,8 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>1114</t>
-        </is>
+      <c r="A399" t="n">
+        <v>1114</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -39537,7 +39535,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N399" s="2" t="n">
+      <c r="N399" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O399" t="inlineStr">
@@ -39582,10 +39580,8 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
+      <c r="A400" t="n">
+        <v>1207</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -39637,7 +39633,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N400" s="2" t="n">
+      <c r="N400" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="O400" t="inlineStr">
@@ -39682,10 +39678,8 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="A401" t="n">
+        <v>1705</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -39737,7 +39731,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N401" s="2" t="n">
+      <c r="N401" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O401" t="inlineStr">
@@ -39782,10 +39776,8 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+      <c r="A402" t="n">
+        <v>1706</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -39837,7 +39829,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N402" s="2" t="n">
+      <c r="N402" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O402" t="inlineStr">
@@ -39882,10 +39874,8 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A403" t="n">
+        <v>1710</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -39937,7 +39927,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N403" s="2" t="n">
+      <c r="N403" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O403" t="inlineStr">
@@ -39982,10 +39972,8 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A404" t="n">
+        <v>1712</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -40037,7 +40025,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N404" s="2" t="n">
+      <c r="N404" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O404" t="inlineStr">
@@ -40082,10 +40070,8 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A405" t="n">
+        <v>1712</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
@@ -40137,7 +40123,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N405" s="2" t="n">
+      <c r="N405" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O405" t="inlineStr">
@@ -40182,10 +40168,8 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A406" t="n">
+        <v>1713</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
@@ -40237,7 +40221,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N406" s="2" t="n">
+      <c r="N406" s="1" t="n">
         <v>45650</v>
       </c>
       <c r="O406" t="inlineStr">
@@ -40282,10 +40266,8 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A407" t="n">
+        <v>1714</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
@@ -40337,7 +40319,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N407" s="2" t="n">
+      <c r="N407" s="1" t="n">
         <v>45995</v>
       </c>
       <c r="O407" t="inlineStr">
@@ -40382,10 +40364,8 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>1724</t>
-        </is>
+      <c r="A408" t="n">
+        <v>1724</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
@@ -40437,7 +40417,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N408" s="2" t="n">
+      <c r="N408" s="1" t="n">
         <v>45977</v>
       </c>
       <c r="O408" t="inlineStr">
@@ -40482,10 +40462,8 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>1726</t>
-        </is>
+      <c r="A409" t="n">
+        <v>1726</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
@@ -40537,7 +40515,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N409" s="2" t="n">
+      <c r="N409" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O409" t="inlineStr">
@@ -40582,10 +40560,8 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>1727</t>
-        </is>
+      <c r="A410" t="n">
+        <v>1727</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
@@ -40637,7 +40613,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N410" s="2" t="n">
+      <c r="N410" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O410" t="inlineStr">
@@ -40682,10 +40658,8 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A411" t="n">
+        <v>1729</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
@@ -40737,7 +40711,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N411" s="2" t="n">
+      <c r="N411" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="O411" t="inlineStr">
@@ -40782,10 +40756,8 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A412" t="n">
+        <v>1729</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -40837,7 +40809,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N412" s="2" t="n">
+      <c r="N412" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="O412" t="inlineStr">
@@ -40882,10 +40854,8 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A413" t="n">
+        <v>1729</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
@@ -40937,7 +40907,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N413" s="2" t="n">
+      <c r="N413" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O413" t="inlineStr">
@@ -40982,10 +40952,8 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A414" t="n">
+        <v>1729</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
@@ -41037,7 +41005,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N414" s="2" t="n">
+      <c r="N414" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O414" t="inlineStr">
@@ -41082,10 +41050,8 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
+      <c r="A415" t="n">
+        <v>1802</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
@@ -41137,7 +41103,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N415" s="2" t="n">
+      <c r="N415" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O415" t="inlineStr">
@@ -41182,10 +41148,8 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="A416" t="n">
+        <v>1803</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
@@ -41237,7 +41201,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N416" s="2" t="n">
+      <c r="N416" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O416" t="inlineStr">
@@ -41282,10 +41246,8 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>1809</t>
-        </is>
+      <c r="A417" t="n">
+        <v>1809</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
@@ -41337,7 +41299,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N417" s="2" t="n">
+      <c r="N417" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O417" t="inlineStr">
@@ -41382,10 +41344,8 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A418" t="n">
+        <v>1813</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
@@ -41437,7 +41397,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N418" s="2" t="n">
+      <c r="N418" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O418" t="inlineStr">
@@ -41482,10 +41442,8 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>1814</t>
-        </is>
+      <c r="A419" t="n">
+        <v>1814</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
@@ -41537,7 +41495,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N419" s="2" t="n">
+      <c r="N419" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O419" t="inlineStr">
@@ -41582,10 +41540,8 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="A420" t="n">
+        <v>1815</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
@@ -41637,7 +41593,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N420" s="2" t="n">
+      <c r="N420" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O420" t="inlineStr">
@@ -41682,10 +41638,8 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A421" t="n">
+        <v>1828</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
@@ -41737,7 +41691,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N421" s="2" t="n">
+      <c r="N421" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="O421" t="inlineStr">
@@ -41782,10 +41736,8 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A422" t="n">
+        <v>1828</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
@@ -41837,7 +41789,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N422" s="2" t="n">
+      <c r="N422" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="O422" t="inlineStr">
@@ -41882,10 +41834,8 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
+      <c r="A423" t="n">
+        <v>1830</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
@@ -41939,7 +41889,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N423" s="2" t="n">
+      <c r="N423" s="1" t="n">
         <v>40429</v>
       </c>
       <c r="O423" t="inlineStr">
@@ -41984,10 +41934,8 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
+      <c r="A424" t="n">
+        <v>2719</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
@@ -42039,7 +41987,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N424" s="2" t="n">
+      <c r="N424" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="O424" t="inlineStr">
@@ -42084,10 +42032,8 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
+      <c r="A425" t="n">
+        <v>2746</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
@@ -42139,7 +42085,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N425" s="2" t="n">
+      <c r="N425" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O425" t="inlineStr">
@@ -42184,10 +42130,8 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>2811</t>
-        </is>
+      <c r="A426" t="n">
+        <v>2811</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
@@ -42239,7 +42183,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N426" s="2" t="n">
+      <c r="N426" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O426" t="inlineStr">
@@ -42284,10 +42228,8 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
+      <c r="A427" t="n">
+        <v>2812</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -42339,7 +42281,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N427" s="2" t="n">
+      <c r="N427" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O427" t="inlineStr">
@@ -42384,10 +42326,8 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A428" t="n">
+        <v>2832</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
@@ -42439,7 +42379,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N428" s="2" t="n">
+      <c r="N428" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O428" t="inlineStr">
@@ -42484,10 +42424,8 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>2840</t>
-        </is>
+      <c r="A429" t="n">
+        <v>2840</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
@@ -42539,7 +42477,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N429" s="2" t="n">
+      <c r="N429" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O429" t="inlineStr">
@@ -42584,10 +42522,8 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
+      <c r="A430" t="n">
+        <v>3301</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -42639,7 +42575,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N430" s="2" t="n">
+      <c r="N430" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="O430" t="inlineStr">
@@ -42684,10 +42620,8 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
+      <c r="A431" t="n">
+        <v>3301</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
@@ -42739,7 +42673,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N431" s="2" t="n">
+      <c r="N431" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O431" t="inlineStr">
@@ -42784,10 +42718,8 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>9116</t>
-        </is>
+      <c r="A432" t="n">
+        <v>9116</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
@@ -42839,7 +42771,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N432" s="2" t="n">
+      <c r="N432" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="O432" t="inlineStr">
@@ -42880,6 +42812,5006 @@
       <c r="V432" t="inlineStr">
         <is>
           <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F433" t="n">
+        <v>106623</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I433" t="n">
+        <v>24</v>
+      </c>
+      <c r="J433" t="n">
+        <v>2</v>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N433" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD-COLEGIO MAYOR DE CUNDINAMARCA</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F434" t="n">
+        <v>118694</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN DE PROYECTOS Y ANALÍTICA DE DATOS BIM</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I434" t="n">
+        <v>48</v>
+      </c>
+      <c r="J434" t="n">
+        <v>4</v>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N434" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>Arquitectura y urbanismo</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>Arquitectura y afines</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F435" t="n">
+        <v>118750</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANALÍTICA Y GESTIÓN FINANCIERA</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I435" t="n">
+        <v>26</v>
+      </c>
+      <c r="J435" t="n">
+        <v>2</v>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N435" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INDUSTRIAL DE SANTANDER</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F436" t="n">
+        <v>118697</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DIDÁCTICA DE LENGUAS Y CULTURAS</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I436" t="n">
+        <v>48</v>
+      </c>
+      <c r="J436" t="n">
+        <v>3</v>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N436" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>118707</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN ESTUDIOS DEL DESARROLLO</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I437" t="n">
+        <v>80</v>
+      </c>
+      <c r="J437" t="n">
+        <v>6</v>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N437" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE PAMPLONA</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Pamplona</t>
+        </is>
+      </c>
+      <c r="F438" t="n">
+        <v>118693</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN SALUD MENTAL</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Híbrida (A distancia-Virtual)</t>
+        </is>
+      </c>
+      <c r="I438" t="n">
+        <v>48</v>
+      </c>
+      <c r="J438" t="n">
+        <v>4</v>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N438" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA GUAJIRA</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F439" t="n">
+        <v>118756</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ALTA GERENCIA E INNOVACIÓN ORGANIZACIONAL</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I439" t="n">
+        <v>44</v>
+      </c>
+      <c r="J439" t="n">
+        <v>3</v>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N439" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>PONTIFICIA UNIVERSIDAD JAVERIANA</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F440" t="n">
+        <v>118708</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ORIENTACIÓN SOCIO - OCUPACIONAL</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I440" t="n">
+        <v>24</v>
+      </c>
+      <c r="J440" t="n">
+        <v>2</v>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N440" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INCCA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F441" t="n">
+        <v>118757</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO DE FAMILIA</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I441" t="n">
+        <v>27</v>
+      </c>
+      <c r="J441" t="n">
+        <v>2</v>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="N441" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EXTERNADO DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F442" t="n">
+        <v>118686</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>??ESPECIALIZACIÓN EN DERECHO COMERCIAL?</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I442" t="n">
+        <v>26</v>
+      </c>
+      <c r="J442" t="n">
+        <v>1</v>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N442" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F443" t="n">
+        <v>118747</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANALÍTICA DE NEGOCIOS</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I443" t="n">
+        <v>25</v>
+      </c>
+      <c r="J443" t="n">
+        <v>2</v>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N443" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F444" t="n">
+        <v>118735</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN HUMANIDADES APLICADAS</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I444" t="n">
+        <v>36</v>
+      </c>
+      <c r="J444" t="n">
+        <v>3</v>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="N444" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>Humanidades (excepto idiomas) no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>Antropología y  artes liberales</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F445" t="n">
+        <v>118709</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ECONOMÍA PARA LAS ORGANIZACIONES</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I445" t="n">
+        <v>24</v>
+      </c>
+      <c r="J445" t="n">
+        <v>2</v>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N445" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F446" t="n">
+        <v>118705</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN FINANZAS ANALÍTICAS</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I446" t="n">
+        <v>21</v>
+      </c>
+      <c r="J446" t="n">
+        <v>2</v>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N446" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F447" t="n">
+        <v>118688</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN SOSTENIBILIDAD Y GOBERNANZA</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I447" t="n">
+        <v>40</v>
+      </c>
+      <c r="J447" t="n">
+        <v>3</v>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N447" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F448" t="n">
+        <v>118743</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE PROYECTOS Y CONSULTORÍA</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I448" t="n">
+        <v>36</v>
+      </c>
+      <c r="J448" t="n">
+        <v>3</v>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N448" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F449" t="n">
+        <v>118716</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I449" t="n">
+        <v>48</v>
+      </c>
+      <c r="J449" t="n">
+        <v>3</v>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N449" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F450" t="n">
+        <v>118715</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I450" t="n">
+        <v>48</v>
+      </c>
+      <c r="J450" t="n">
+        <v>3</v>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N450" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F451" t="n">
+        <v>118700</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ENFERMERÍA EN SALUD MENTAL Y PSIQUIATRÍA</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I451" t="n">
+        <v>54</v>
+      </c>
+      <c r="J451" t="n">
+        <v>3</v>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N451" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F452" t="n">
+        <v>118738</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE PRODUCTIVIDAD Y COMPETITIVIDAD</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I452" t="n">
+        <v>48</v>
+      </c>
+      <c r="J452" t="n">
+        <v>3</v>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N452" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F453" t="n">
+        <v>118739</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE PRODUCTIVIDAD Y COMPETITIVIDAD</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I453" t="n">
+        <v>48</v>
+      </c>
+      <c r="J453" t="n">
+        <v>3</v>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N453" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE BOYACA UNIBOYACA</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F454" t="n">
+        <v>118742</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN CIENCIAS AMBIENTALES</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I454" t="n">
+        <v>95</v>
+      </c>
+      <c r="J454" t="n">
+        <v>7</v>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N454" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>Medio ambiente</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>Ciencias del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>Geología, otros programas de ciencias naturales</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V454" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE BOYACA UNIBOYACA</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F455" t="n">
+        <v>118758</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN GESTIÓN E INNOVACIÓN EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I455" t="n">
+        <v>87</v>
+      </c>
+      <c r="J455" t="n">
+        <v>6</v>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N455" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F456" t="n">
+        <v>118759</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN CIENCIAS DE LA SALUD</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I456" t="n">
+        <v>90</v>
+      </c>
+      <c r="J456" t="n">
+        <v>7</v>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N456" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>Salud no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F457" t="n">
+        <v>118744</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I457" t="n">
+        <v>81</v>
+      </c>
+      <c r="J457" t="n">
+        <v>3</v>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N457" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>1816</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F458" t="n">
+        <v>118729</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I458" t="n">
+        <v>24</v>
+      </c>
+      <c r="J458" t="n">
+        <v>2</v>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N458" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>1816</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F459" t="n">
+        <v>118723</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ENDODONCIA</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I459" t="n">
+        <v>77</v>
+      </c>
+      <c r="J459" t="n">
+        <v>4</v>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N459" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>Odontología y estudios dentales</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>Odontología</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F460" t="n">
+        <v>118730</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN CLÍNICA CIRUGÍA DE TEJIDOS BLANDOS EN ANIMALES DE COMPAÑÍA</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I460" t="n">
+        <v>25</v>
+      </c>
+      <c r="J460" t="n">
+        <v>3</v>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N460" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>Medicina veterinaria</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V460" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F461" t="n">
+        <v>118728</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE ORGANIZACIONES DE PROPIEDAD HORIZONTAL</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I461" t="n">
+        <v>23</v>
+      </c>
+      <c r="J461" t="n">
+        <v>2</v>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N461" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F462" t="n">
+        <v>118727</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE ORGANIZACIONES DE PROPIEDAD HORIZONTAL</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I462" t="n">
+        <v>23</v>
+      </c>
+      <c r="J462" t="n">
+        <v>2</v>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N462" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V462" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F463" t="n">
+        <v>118724</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GINECOLOGÍA Y OBSTETRICIA</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I463" t="n">
+        <v>212</v>
+      </c>
+      <c r="J463" t="n">
+        <v>6</v>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N463" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V463" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F464" t="n">
+        <v>118725</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PEDIATRÍA</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I464" t="n">
+        <v>202</v>
+      </c>
+      <c r="J464" t="n">
+        <v>6</v>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N464" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F465" t="n">
+        <v>118726</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN TRIBUTACIÓN</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I465" t="n">
+        <v>36</v>
+      </c>
+      <c r="J465" t="n">
+        <v>5</v>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N465" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V465" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F466" t="n">
+        <v>118752</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN HEMATOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I466" t="n">
+        <v>136</v>
+      </c>
+      <c r="J466" t="n">
+        <v>2</v>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N466" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V466" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F467" t="n">
+        <v>118684</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I467" t="n">
+        <v>30</v>
+      </c>
+      <c r="J467" t="n">
+        <v>2</v>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N467" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T467" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V467" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F468" t="n">
+        <v>118704</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ENFERMERÍA MATERNO PERINATAL</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I468" t="n">
+        <v>27</v>
+      </c>
+      <c r="J468" t="n">
+        <v>2</v>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N468" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T468" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V468" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F469" t="n">
+        <v>118746</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ENERGÍAS RENOVABLES</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Presencial-Virtual</t>
+        </is>
+      </c>
+      <c r="I469" t="n">
+        <v>22</v>
+      </c>
+      <c r="J469" t="n">
+        <v>2</v>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N469" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>Electricidad y energía</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>Ingeniería eléctrica y afines</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V469" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE IBAGUE</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F470" t="n">
+        <v>118754</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN POLÍTICA Y GERENCIA PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I470" t="n">
+        <v>36</v>
+      </c>
+      <c r="J470" t="n">
+        <v>3</v>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N470" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T470" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V470" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSIDAD DEL SINU - ELIAS BECHARA ZAINUM - UNISINU -</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F471" t="n">
+        <v>118763</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN REHABILITACIÓN ORAL</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I471" t="n">
+        <v>96</v>
+      </c>
+      <c r="J471" t="n">
+        <v>5</v>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N471" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>Odontología y estudios dentales</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V471" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F472" t="n">
+        <v>118712</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN SALUD PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I472" t="n">
+        <v>48</v>
+      </c>
+      <c r="J472" t="n">
+        <v>4</v>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N472" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>Salud no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F473" t="n">
+        <v>118721</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN TURISMO INTELIGENTE</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I473" t="n">
+        <v>44</v>
+      </c>
+      <c r="J473" t="n">
+        <v>4</v>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N473" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T473" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F474" t="n">
+        <v>118719</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ANALÍTICA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I474" t="n">
+        <v>48</v>
+      </c>
+      <c r="J474" t="n">
+        <v>3</v>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N474" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V474" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INTERNACIONAL DEL TRÓPICO AMERICANO - UNITRÓPICO</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="F475" t="n">
+        <v>118714</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CONSTRUCCIÓN SOSTENIBLE EN PROYECTOS DE EDIFICACIÓN E INFRAESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I475" t="n">
+        <v>45</v>
+      </c>
+      <c r="J475" t="n">
+        <v>4</v>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N475" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>Arquitectura y afines</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V475" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2828</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL HUILA-CORHUILA-</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F476" t="n">
+        <v>118748</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I476" t="n">
+        <v>24</v>
+      </c>
+      <c r="J476" t="n">
+        <v>2</v>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N476" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F477" t="n">
+        <v>118706</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ESPIRITUALIDAD</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I477" t="n">
+        <v>42</v>
+      </c>
+      <c r="J477" t="n">
+        <v>4</v>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N477" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>Religión y Teología</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>Filosofía, teología y afines</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F478" t="n">
+        <v>118695</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I478" t="n">
+        <v>40</v>
+      </c>
+      <c r="J478" t="n">
+        <v>4</v>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N478" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F479" t="n">
+        <v>118761</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PENAL</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I479" t="n">
+        <v>30</v>
+      </c>
+      <c r="J479" t="n">
+        <v>2</v>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N479" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F480" t="n">
+        <v>118701</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I480" t="n">
+        <v>28</v>
+      </c>
+      <c r="J480" t="n">
+        <v>2</v>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="N480" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2849</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AUTONOMA DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F481" t="n">
+        <v>118731</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PENAL</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I481" t="n">
+        <v>25</v>
+      </c>
+      <c r="J481" t="n">
+        <v>2</v>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N481" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F482" t="n">
+        <v>118696</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN FORMULACIÓN Y EVALUACIÓN DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I482" t="n">
+        <v>24</v>
+      </c>
+      <c r="J482" t="n">
+        <v>2</v>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N482" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V482"/>
+  <dimension ref="A1:V525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42816,10 +42816,8 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A433" t="n">
+        <v>1110</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
@@ -42871,7 +42869,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N433" s="2" t="n">
+      <c r="N433" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O433" t="inlineStr">
@@ -42916,10 +42914,8 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
+      <c r="A434" t="n">
+        <v>1121</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
@@ -42971,7 +42967,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N434" s="2" t="n">
+      <c r="N434" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O434" t="inlineStr">
@@ -43016,10 +43012,8 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A435" t="n">
+        <v>1203</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
@@ -43071,7 +43065,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N435" s="2" t="n">
+      <c r="N435" s="1" t="n">
         <v>46107</v>
       </c>
       <c r="O435" t="inlineStr">
@@ -43116,10 +43110,8 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
+      <c r="A436" t="n">
+        <v>1204</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -43171,7 +43163,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N436" s="2" t="n">
+      <c r="N436" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O436" t="inlineStr">
@@ -43216,10 +43208,8 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
+      <c r="A437" t="n">
+        <v>1205</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -43271,7 +43261,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N437" s="2" t="n">
+      <c r="N437" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O437" t="inlineStr">
@@ -43316,10 +43306,8 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
+      <c r="A438" t="n">
+        <v>1212</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
@@ -43371,7 +43359,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N438" s="2" t="n">
+      <c r="N438" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O438" t="inlineStr">
@@ -43416,10 +43404,8 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A439" t="n">
+        <v>1218</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -43471,7 +43457,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N439" s="2" t="n">
+      <c r="N439" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="O439" t="inlineStr">
@@ -43516,10 +43502,8 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A440" t="n">
+        <v>1701</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
@@ -43571,7 +43555,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N440" s="2" t="n">
+      <c r="N440" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O440" t="inlineStr">
@@ -43616,10 +43600,8 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
+      <c r="A441" t="n">
+        <v>1703</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
@@ -43671,7 +43653,7 @@
           <t>Mensual</t>
         </is>
       </c>
-      <c r="N441" s="2" t="n">
+      <c r="N441" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O441" t="inlineStr">
@@ -43716,10 +43698,8 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+      <c r="A442" t="n">
+        <v>1706</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
@@ -43771,7 +43751,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N442" s="2" t="n">
+      <c r="N442" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O442" t="inlineStr">
@@ -43816,10 +43796,8 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A443" t="n">
+        <v>1709</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
@@ -43871,7 +43849,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N443" s="2" t="n">
+      <c r="N443" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="O443" t="inlineStr">
@@ -43916,10 +43894,8 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A444" t="n">
+        <v>1711</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
@@ -43971,7 +43947,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N444" s="2" t="n">
+      <c r="N444" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O444" t="inlineStr">
@@ -44016,10 +43992,8 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A445" t="n">
+        <v>1712</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -44071,7 +44045,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N445" s="2" t="n">
+      <c r="N445" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O445" t="inlineStr">
@@ -44116,10 +44090,8 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A446" t="n">
+        <v>1712</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -44171,7 +44143,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N446" s="2" t="n">
+      <c r="N446" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O446" t="inlineStr">
@@ -44216,10 +44188,8 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A447" t="n">
+        <v>1714</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -44271,7 +44241,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N447" s="2" t="n">
+      <c r="N447" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O447" t="inlineStr">
@@ -44316,10 +44286,8 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A448" t="n">
+        <v>1722</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -44371,7 +44339,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N448" s="2" t="n">
+      <c r="N448" s="1" t="n">
         <v>46079</v>
       </c>
       <c r="O448" t="inlineStr">
@@ -44416,10 +44384,8 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A449" t="n">
+        <v>1729</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -44471,7 +44437,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N449" s="2" t="n">
+      <c r="N449" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O449" t="inlineStr">
@@ -44516,10 +44482,8 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A450" t="n">
+        <v>1729</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -44571,7 +44535,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N450" s="2" t="n">
+      <c r="N450" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O450" t="inlineStr">
@@ -44616,10 +44580,8 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A451" t="n">
+        <v>1729</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -44671,7 +44633,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N451" s="2" t="n">
+      <c r="N451" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O451" t="inlineStr">
@@ -44716,10 +44678,8 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A452" t="n">
+        <v>1729</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -44771,7 +44731,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N452" s="2" t="n">
+      <c r="N452" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O452" t="inlineStr">
@@ -44816,10 +44776,8 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A453" t="n">
+        <v>1729</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -44871,7 +44829,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N453" s="2" t="n">
+      <c r="N453" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O453" t="inlineStr">
@@ -44916,10 +44874,8 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
+      <c r="A454" t="n">
+        <v>1734</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -44971,7 +44927,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N454" s="2" t="n">
+      <c r="N454" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O454" t="inlineStr">
@@ -45016,10 +44972,8 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
+      <c r="A455" t="n">
+        <v>1734</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -45071,7 +45025,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N455" s="2" t="n">
+      <c r="N455" s="1" t="n">
         <v>46057</v>
       </c>
       <c r="O455" t="inlineStr">
@@ -45116,10 +45070,8 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A456" t="n">
+        <v>1805</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -45171,7 +45123,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N456" s="2" t="n">
+      <c r="N456" s="1" t="n">
         <v>46057</v>
       </c>
       <c r="O456" t="inlineStr">
@@ -45216,10 +45168,8 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A457" t="n">
+        <v>1805</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -45271,7 +45221,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N457" s="2" t="n">
+      <c r="N457" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="O457" t="inlineStr">
@@ -45316,10 +45266,8 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>1816</t>
-        </is>
+      <c r="A458" t="n">
+        <v>1816</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -45371,7 +45319,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N458" s="2" t="n">
+      <c r="N458" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="O458" t="inlineStr">
@@ -45416,10 +45364,8 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>1816</t>
-        </is>
+      <c r="A459" t="n">
+        <v>1816</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -45471,7 +45417,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N459" s="2" t="n">
+      <c r="N459" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="O459" t="inlineStr">
@@ -45516,10 +45462,8 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>1817</t>
-        </is>
+      <c r="A460" t="n">
+        <v>1817</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -45571,7 +45515,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N460" s="2" t="n">
+      <c r="N460" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="O460" t="inlineStr">
@@ -45616,10 +45560,8 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A461" t="n">
+        <v>1818</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -45671,7 +45613,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N461" s="2" t="n">
+      <c r="N461" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="O461" t="inlineStr">
@@ -45716,10 +45658,8 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A462" t="n">
+        <v>1818</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -45771,7 +45711,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N462" s="2" t="n">
+      <c r="N462" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="O462" t="inlineStr">
@@ -45816,10 +45756,8 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A463" t="n">
+        <v>1818</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -45871,7 +45809,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N463" s="2" t="n">
+      <c r="N463" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="O463" t="inlineStr">
@@ -45916,10 +45854,8 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A464" t="n">
+        <v>1818</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -45971,7 +45907,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N464" s="2" t="n">
+      <c r="N464" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="O464" t="inlineStr">
@@ -46016,10 +45952,8 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A465" t="n">
+        <v>1818</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -46071,7 +46005,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N465" s="2" t="n">
+      <c r="N465" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="O465" t="inlineStr">
@@ -46116,10 +46050,8 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A466" t="n">
+        <v>1823</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -46171,7 +46103,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N466" s="2" t="n">
+      <c r="N466" s="1" t="n">
         <v>46086</v>
       </c>
       <c r="O466" t="inlineStr">
@@ -46216,10 +46148,8 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A467" t="n">
+        <v>1826</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -46271,7 +46201,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N467" s="2" t="n">
+      <c r="N467" s="1" t="n">
         <v>46014</v>
       </c>
       <c r="O467" t="inlineStr">
@@ -46316,10 +46246,8 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A468" t="n">
+        <v>1826</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -46371,7 +46299,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N468" s="2" t="n">
+      <c r="N468" s="1" t="n">
         <v>45972</v>
       </c>
       <c r="O468" t="inlineStr">
@@ -46416,10 +46344,8 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
+      <c r="A469" t="n">
+        <v>1830</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -46471,7 +46397,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N469" s="2" t="n">
+      <c r="N469" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="O469" t="inlineStr">
@@ -46516,10 +46442,8 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
+      <c r="A470" t="n">
+        <v>1831</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -46571,7 +46495,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N470" s="2" t="n">
+      <c r="N470" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="O470" t="inlineStr">
@@ -46616,10 +46540,8 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
+      <c r="A471" t="n">
+        <v>1834</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -46671,7 +46593,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N471" s="2" t="n">
+      <c r="N471" s="1" t="n">
         <v>46008</v>
       </c>
       <c r="O471" t="inlineStr">
@@ -46716,10 +46638,8 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A472" t="n">
+        <v>2102</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -46771,7 +46691,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N472" s="2" t="n">
+      <c r="N472" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O472" t="inlineStr">
@@ -46816,10 +46736,8 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A473" t="n">
+        <v>2102</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -46871,7 +46789,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N473" s="2" t="n">
+      <c r="N473" s="1" t="n">
         <v>46015</v>
       </c>
       <c r="O473" t="inlineStr">
@@ -46916,10 +46834,8 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A474" t="n">
+        <v>2728</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -46971,7 +46887,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N474" s="2" t="n">
+      <c r="N474" s="1" t="n">
         <v>46000</v>
       </c>
       <c r="O474" t="inlineStr">
@@ -47016,10 +46932,8 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>2743</t>
-        </is>
+      <c r="A475" t="n">
+        <v>2743</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -47071,7 +46985,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N475" s="2" t="n">
+      <c r="N475" s="1" t="n">
         <v>45951</v>
       </c>
       <c r="O475" t="inlineStr">
@@ -47116,10 +47030,8 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>2828</t>
-        </is>
+      <c r="A476" t="n">
+        <v>2828</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -47171,7 +47083,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N476" s="2" t="n">
+      <c r="N476" s="1" t="n">
         <v>46098</v>
       </c>
       <c r="O476" t="inlineStr">
@@ -47216,10 +47128,8 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A477" t="n">
+        <v>2829</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -47271,7 +47181,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N477" s="2" t="n">
+      <c r="N477" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O477" t="inlineStr">
@@ -47316,10 +47226,8 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A478" t="n">
+        <v>2829</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -47371,7 +47279,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N478" s="2" t="n">
+      <c r="N478" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O478" t="inlineStr">
@@ -47416,10 +47324,8 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A479" t="n">
+        <v>2833</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -47471,7 +47377,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N479" s="2" t="n">
+      <c r="N479" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="O479" t="inlineStr">
@@ -47516,10 +47422,8 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A480" t="n">
+        <v>2833</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -47571,7 +47475,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N480" s="2" t="n">
+      <c r="N480" s="1" t="n">
         <v>46008</v>
       </c>
       <c r="O480" t="inlineStr">
@@ -47616,10 +47520,8 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>2849</t>
-        </is>
+      <c r="A481" t="n">
+        <v>2849</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -47671,7 +47573,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N481" s="2" t="n">
+      <c r="N481" s="1" t="n">
         <v>46002</v>
       </c>
       <c r="O481" t="inlineStr">
@@ -47716,10 +47618,8 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>3104</t>
-        </is>
+      <c r="A482" t="n">
+        <v>3104</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -47771,7 +47671,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N482" s="2" t="n">
+      <c r="N482" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O482" t="inlineStr">
@@ -47810,6 +47710,4306 @@
         </is>
       </c>
       <c r="V482" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F483" t="n">
+        <v>118787</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN COMUNICACIÓN E IMAGEN</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I483" t="n">
+        <v>130</v>
+      </c>
+      <c r="J483" t="n">
+        <v>8</v>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr"/>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PEDAGOGICA Y TECNOLOGICA DE COLOMBIA - UPTC</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F484" t="n">
+        <v>118786</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN GESTIÓN, INNOVACIÓN Y EMPRENDIMIENTO</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I484" t="n">
+        <v>102</v>
+      </c>
+      <c r="J484" t="n">
+        <v>7</v>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N484" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PEDAGOGICA Y TECNOLOGICA DE COLOMBIA - UPTC</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="F485" t="n">
+        <v>118821</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN DE ACTIVOS Y DE MANTENIMIENTO</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I485" t="n">
+        <v>27</v>
+      </c>
+      <c r="J485" t="n">
+        <v>2</v>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N485" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>Mecánica y profesiones afines a la metalistería</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>Ingeniería eléctrica y afines</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD POPULAR DEL CESAR</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F486" t="n">
+        <v>118784</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAESTRÍA EN INGENIERÍA, CON ÉNFASIS EN INVESTIGACIÓN 	</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I486" t="n">
+        <v>46</v>
+      </c>
+      <c r="J486" t="n">
+        <v>4</v>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N486" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U486" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE NARIÑO</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F487" t="n">
+        <v>118785</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ERGONOMÍA Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I487" t="n">
+        <v>53</v>
+      </c>
+      <c r="J487" t="n">
+        <v>4</v>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N487" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL TOLIMA</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F488" t="n">
+        <v>118813</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN FINANZAS</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Híbrida (A distancia-Virtual)</t>
+        </is>
+      </c>
+      <c r="I488" t="n">
+        <v>30</v>
+      </c>
+      <c r="J488" t="n">
+        <v>1</v>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr"/>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N488" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T488" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U488" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EXTERNADO DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F489" t="n">
+        <v>118820</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN DEL GASTO PÚBLICO</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I489" t="n">
+        <v>40</v>
+      </c>
+      <c r="J489" t="n">
+        <v>3</v>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr"/>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N489" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T489" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F490" t="n">
+        <v>118736</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN EDUCACION</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I490" t="n">
+        <v>36</v>
+      </c>
+      <c r="J490" t="n">
+        <v>3</v>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N490" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T490" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F491" t="n">
+        <v>118778</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO NOTARIAL Y REGISTRAL</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I491" t="n">
+        <v>24</v>
+      </c>
+      <c r="J491" t="n">
+        <v>2</v>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr"/>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N491" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD MARIANA</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F492" t="n">
+        <v>118817</v>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN NEUROEDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I492" t="n">
+        <v>82</v>
+      </c>
+      <c r="J492" t="n">
+        <v>6</v>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N492" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a educación</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a educación</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F493" t="n">
+        <v>118810</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DESARROLLO TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I493" t="n">
+        <v>24</v>
+      </c>
+      <c r="J493" t="n">
+        <v>2</v>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N493" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>Medio ambiente</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>Ciencias del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F494" t="n">
+        <v>118824</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN CIENCIA DE DATOS E INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I494" t="n">
+        <v>112</v>
+      </c>
+      <c r="J494" t="n">
+        <v>8</v>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N494" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>Estadística</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F495" t="n">
+        <v>118765</v>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ONCOLOGÍA CLÍNICA</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I495" t="n">
+        <v>162</v>
+      </c>
+      <c r="J495" t="n">
+        <v>4</v>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L495" t="n">
+        <v>22570000</v>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N495" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DEL CARIBE- UNIAUTONOMA</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F496" t="n">
+        <v>118805</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA TRIBUTARIA</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I496" t="n">
+        <v>45</v>
+      </c>
+      <c r="J496" t="n">
+        <v>3</v>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N496" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T496" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U496" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DEL CARIBE- UNIAUTONOMA</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F497" t="n">
+        <v>118806</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA TRIBUTARIA</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I497" t="n">
+        <v>45</v>
+      </c>
+      <c r="J497" t="n">
+        <v>3</v>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N497" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F498" t="n">
+        <v>118670</v>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO DISCIPLINARIO</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I498" t="n">
+        <v>22</v>
+      </c>
+      <c r="J498" t="n">
+        <v>2</v>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N498" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T498" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U498" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F499" t="n">
+        <v>118626</v>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CONTRATACIÓN ESTATAL</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I499" t="n">
+        <v>40</v>
+      </c>
+      <c r="J499" t="n">
+        <v>4</v>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N499" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T499" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U499" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F500" t="n">
+        <v>118766</v>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO DE GÉNERO</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I500" t="n">
+        <v>24</v>
+      </c>
+      <c r="J500" t="n">
+        <v>2</v>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N500" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T500" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U500" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F501" t="n">
+        <v>118811</v>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN FISIOTERAPIA EN CUIDADO CRITICO DEL ADULTO</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I501" t="n">
+        <v>32</v>
+      </c>
+      <c r="J501" t="n">
+        <v>3</v>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr"/>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N501" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>Terapias</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T501" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F502" t="n">
+        <v>118826</v>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CIENCIAS COGNITIVAS</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I502" t="n">
+        <v>48</v>
+      </c>
+      <c r="J502" t="n">
+        <v>4</v>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N502" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias sociales, periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias sociales, periodismo e información</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T502" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F503" t="n">
+        <v>118825</v>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CIENCIAS COGNITIVAS</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I503" t="n">
+        <v>48</v>
+      </c>
+      <c r="J503" t="n">
+        <v>4</v>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N503" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias sociales, periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias sociales, periodismo e información</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T503" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F504" t="n">
+        <v>118800</v>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ECONOMÍA FINANCIERA</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I504" t="n">
+        <v>43</v>
+      </c>
+      <c r="J504" t="n">
+        <v>3</v>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N504" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F505" t="n">
+        <v>118799</v>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ECONOMÍA FINANCIERA</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I505" t="n">
+        <v>43</v>
+      </c>
+      <c r="J505" t="n">
+        <v>3</v>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N505" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T505" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V505" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>1833</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSIDAD DEL SINU - ELIAS BECHARA ZAINUM - UNISINU -</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F506" t="n">
+        <v>118801</v>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE SISTEMAS ELECTRICOS DE POTENCIA</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I506" t="n">
+        <v>24</v>
+      </c>
+      <c r="J506" t="n">
+        <v>2</v>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N506" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>Electricidad y energía</t>
+        </is>
+      </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>Ingeniería eléctrica y afines</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T506" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2206</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>INSTITUTO DEPARTAMENTAL DE BELLAS ARTES</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F507" t="n">
+        <v>118661</v>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANIMACIÓN DIGITAL</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I507" t="n">
+        <v>28</v>
+      </c>
+      <c r="J507" t="n">
+        <v>2</v>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N507" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>UNIDAD CENTRAL DEL VALLE DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Tuluá</t>
+        </is>
+      </c>
+      <c r="F508" t="n">
+        <v>118720</v>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SISTEMAS TELEMÁTICOS CON ÉNFASIS EN TRANSFORMACIÓN DIGITAL</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I508" t="n">
+        <v>28</v>
+      </c>
+      <c r="J508" t="n">
+        <v>2</v>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N508" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>Publicidad y afines</t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>POLITECNICO GRANCOLOMBIANO</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F509" t="n">
+        <v>118718</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DERECHO PROCESAL</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I509" t="n">
+        <v>44</v>
+      </c>
+      <c r="J509" t="n">
+        <v>3</v>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N509" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA-CEIPA-</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="F510" t="n">
+        <v>118106</v>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ANALÍTICA PARA LOS NEGOCIOS</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Presencial-Virtual</t>
+        </is>
+      </c>
+      <c r="I510" t="n">
+        <v>40</v>
+      </c>
+      <c r="J510" t="n">
+        <v>22</v>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N510" s="2" t="n">
+        <v>45643</v>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias naturales, matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias naturales, matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F511" t="n">
+        <v>118783</v>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I511" t="n">
+        <v>50</v>
+      </c>
+      <c r="J511" t="n">
+        <v>3</v>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N511" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA SEMINARIO BIBLICO DE COLOMBIA - FUSBC</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F512" t="n">
+        <v>118779</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN MINISTERIO CRISTIANO</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I512" t="n">
+        <v>53</v>
+      </c>
+      <c r="J512" t="n">
+        <v>4</v>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N512" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>Religión y Teología</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>Filosofía, teología y afines</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V512" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA SEMINARIO BIBLICO DE COLOMBIA - FUSBC</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F513" t="n">
+        <v>118780</v>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN MINISTERIO CRISTIANO</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I513" t="n">
+        <v>53</v>
+      </c>
+      <c r="J513" t="n">
+        <v>4</v>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N513" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>Religión y Teología</t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>Filosofía, teología y afines</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V513" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA SANITAS</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F514" t="n">
+        <v>118781</v>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PSICOGERONTOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I514" t="n">
+        <v>29</v>
+      </c>
+      <c r="J514" t="n">
+        <v>2</v>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr"/>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N514" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V514" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL CARIBE - CECAR</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F515" t="n">
+        <v>118702</v>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ALTA GERENCIA</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I515" t="n">
+        <v>28</v>
+      </c>
+      <c r="J515" t="n">
+        <v>2</v>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N515" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V515" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL CARIBE - CECAR</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F516" t="n">
+        <v>118703</v>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ALTA GERENCIA</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I516" t="n">
+        <v>28</v>
+      </c>
+      <c r="J516" t="n">
+        <v>2</v>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr"/>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N516" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V516" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA RAFAEL NUÑEZ</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F517" t="n">
+        <v>118775</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTERVENCIÓN SOCIAL Y DESARROLLO LOCAL</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I517" t="n">
+        <v>27</v>
+      </c>
+      <c r="J517" t="n">
+        <v>2</v>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N517" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>Trabajo social</t>
+        </is>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V517" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F518" t="n">
+        <v>118773</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I518" t="n">
+        <v>42</v>
+      </c>
+      <c r="J518" t="n">
+        <v>3</v>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N518" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T518" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V518" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F519" t="n">
+        <v>118774</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I519" t="n">
+        <v>42</v>
+      </c>
+      <c r="J519" t="n">
+        <v>3</v>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr"/>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N519" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T519" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V519" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA ANTONIO JOSE CAMACHO</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F520" t="n">
+        <v>118764</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ASEGURAMIENTO DE LA CALIDAD DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I520" t="n">
+        <v>28</v>
+      </c>
+      <c r="J520" t="n">
+        <v>2</v>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N520" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T520" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U520" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V520" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA TALLER CINCO CENTRO DE DISEÑO</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F521" t="n">
+        <v>118802</v>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ESCULTURA Y TEXTURA DIGITAL</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I521" t="n">
+        <v>24</v>
+      </c>
+      <c r="J521" t="n">
+        <v>2</v>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N521" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>Artes plásticas, visuales y afines</t>
+        </is>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T521" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U521" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V521" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA TALLER CINCO CENTRO DE DISEÑO</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F522" t="n">
+        <v>118803</v>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN NARRATIVAS TRANSMEDIA</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I522" t="n">
+        <v>24</v>
+      </c>
+      <c r="J522" t="n">
+        <v>2</v>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N522" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>Artes plásticas, visuales y afines</t>
+        </is>
+      </c>
+      <c r="S522" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T522" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U522" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V522" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F523" t="n">
+        <v>118812</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ADMINISTRACIÓN (MBA)</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I523" t="n">
+        <v>38</v>
+      </c>
+      <c r="J523" t="n">
+        <v>3</v>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N523" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T523" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U523" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V523" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F524" t="n">
+        <v>118776</v>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE INSTITUCIONES EDUCATIVAS</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I524" t="n">
+        <v>24</v>
+      </c>
+      <c r="J524" t="n">
+        <v>2</v>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N524" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T524" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U524" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V524" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>9943</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="F525" t="n">
+        <v>118814</v>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORÍA FORENSE Y CUMPLIMIENTO</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I525" t="n">
+        <v>24</v>
+      </c>
+      <c r="J525" t="n">
+        <v>2</v>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N525" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T525" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="U525" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V525" t="inlineStr">
         <is>
           <t>Escuela de Negocios</t>
         </is>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V525"/>
+  <dimension ref="A1:V558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47716,10 +47716,8 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
+      <c r="A483" t="n">
+        <v>1101</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -47814,10 +47812,8 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A484" t="n">
+        <v>1106</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -47869,7 +47865,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N484" s="2" t="n">
+      <c r="N484" s="1" t="n">
         <v>46049</v>
       </c>
       <c r="O484" t="inlineStr">
@@ -47914,10 +47910,8 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
+      <c r="A485" t="n">
+        <v>1107</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -47969,7 +47963,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N485" s="2" t="n">
+      <c r="N485" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="O485" t="inlineStr">
@@ -48014,10 +48008,8 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
+      <c r="A486" t="n">
+        <v>1120</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -48069,7 +48061,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N486" s="2" t="n">
+      <c r="N486" s="1" t="n">
         <v>46042</v>
       </c>
       <c r="O486" t="inlineStr">
@@ -48114,10 +48106,8 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
+      <c r="A487" t="n">
+        <v>1206</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -48169,7 +48159,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N487" s="2" t="n">
+      <c r="N487" s="1" t="n">
         <v>46057</v>
       </c>
       <c r="O487" t="inlineStr">
@@ -48214,10 +48204,8 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
+      <c r="A488" t="n">
+        <v>1207</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -48269,7 +48257,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N488" s="2" t="n">
+      <c r="N488" s="1" t="n">
         <v>46050</v>
       </c>
       <c r="O488" t="inlineStr">
@@ -48314,10 +48302,8 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
+      <c r="A489" t="n">
+        <v>1706</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -48369,7 +48355,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N489" s="2" t="n">
+      <c r="N489" s="1" t="n">
         <v>46128</v>
       </c>
       <c r="O489" t="inlineStr">
@@ -48414,10 +48400,8 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A490" t="n">
+        <v>1713</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -48469,7 +48453,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N490" s="2" t="n">
+      <c r="N490" s="1" t="n">
         <v>46084</v>
       </c>
       <c r="O490" t="inlineStr">
@@ -48514,10 +48498,8 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A491" t="n">
+        <v>1716</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -48569,7 +48551,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N491" s="2" t="n">
+      <c r="N491" s="1" t="n">
         <v>46050</v>
       </c>
       <c r="O491" t="inlineStr">
@@ -48614,10 +48596,8 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>1720</t>
-        </is>
+      <c r="A492" t="n">
+        <v>1720</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -48669,7 +48649,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N492" s="2" t="n">
+      <c r="N492" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="O492" t="inlineStr">
@@ -48714,10 +48694,8 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A493" t="n">
+        <v>1722</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -48769,7 +48747,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N493" s="2" t="n">
+      <c r="N493" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="O493" t="inlineStr">
@@ -48814,10 +48792,8 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A494" t="n">
+        <v>1729</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -48869,7 +48845,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N494" s="2" t="n">
+      <c r="N494" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O494" t="inlineStr">
@@ -48914,10 +48890,8 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A495" t="n">
+        <v>1729</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -48971,7 +48945,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N495" s="2" t="n">
+      <c r="N495" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O495" t="inlineStr">
@@ -49016,10 +48990,8 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
+      <c r="A496" t="n">
+        <v>1804</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -49071,7 +49043,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N496" s="2" t="n">
+      <c r="N496" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="O496" t="inlineStr">
@@ -49116,10 +49088,8 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
+      <c r="A497" t="n">
+        <v>1804</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -49171,7 +49141,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N497" s="2" t="n">
+      <c r="N497" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="O497" t="inlineStr">
@@ -49216,10 +49186,8 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A498" t="n">
+        <v>1805</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -49271,7 +49239,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N498" s="2" t="n">
+      <c r="N498" s="1" t="n">
         <v>46014</v>
       </c>
       <c r="O498" t="inlineStr">
@@ -49316,10 +49284,8 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A499" t="n">
+        <v>1812</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -49371,7 +49337,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N499" s="2" t="n">
+      <c r="N499" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O499" t="inlineStr">
@@ -49416,10 +49382,8 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A500" t="n">
+        <v>1818</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -49471,7 +49435,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N500" s="2" t="n">
+      <c r="N500" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="O500" t="inlineStr">
@@ -49516,10 +49480,8 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
+      <c r="A501" t="n">
+        <v>1825</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -49571,7 +49533,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N501" s="2" t="n">
+      <c r="N501" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O501" t="inlineStr">
@@ -49616,10 +49578,8 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
+      <c r="A502" t="n">
+        <v>1825</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -49671,7 +49631,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N502" s="2" t="n">
+      <c r="N502" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O502" t="inlineStr">
@@ -49716,10 +49676,8 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
+      <c r="A503" t="n">
+        <v>1825</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -49771,7 +49729,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N503" s="2" t="n">
+      <c r="N503" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O503" t="inlineStr">
@@ -49816,10 +49774,8 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
+      <c r="A504" t="n">
+        <v>1825</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -49871,7 +49827,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N504" s="2" t="n">
+      <c r="N504" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O504" t="inlineStr">
@@ -49916,10 +49872,8 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
+      <c r="A505" t="n">
+        <v>1825</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -49971,7 +49925,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N505" s="2" t="n">
+      <c r="N505" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O505" t="inlineStr">
@@ -50016,10 +49970,8 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A506" t="n">
+        <v>1833</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -50071,7 +50023,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N506" s="2" t="n">
+      <c r="N506" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O506" t="inlineStr">
@@ -50116,10 +50068,8 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>2206</t>
-        </is>
+      <c r="A507" t="n">
+        <v>2206</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -50171,7 +50121,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N507" s="2" t="n">
+      <c r="N507" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O507" t="inlineStr">
@@ -50216,10 +50166,8 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
+      <c r="A508" t="n">
+        <v>2301</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -50271,7 +50219,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N508" s="2" t="n">
+      <c r="N508" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O508" t="inlineStr">
@@ -50316,10 +50264,8 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
+      <c r="A509" t="n">
+        <v>2725</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -50371,7 +50317,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N509" s="2" t="n">
+      <c r="N509" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O509" t="inlineStr">
@@ -50416,10 +50362,8 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>2727</t>
-        </is>
+      <c r="A510" t="n">
+        <v>2727</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -50471,7 +50415,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N510" s="2" t="n">
+      <c r="N510" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O510" t="inlineStr">
@@ -50516,10 +50460,8 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A511" t="n">
+        <v>2728</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -50571,7 +50513,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N511" s="2" t="n">
+      <c r="N511" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O511" t="inlineStr">
@@ -50616,10 +50558,8 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
+      <c r="A512" t="n">
+        <v>2736</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -50671,7 +50611,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N512" s="2" t="n">
+      <c r="N512" s="1" t="n">
         <v>45994</v>
       </c>
       <c r="O512" t="inlineStr">
@@ -50716,10 +50656,8 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
+      <c r="A513" t="n">
+        <v>2736</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -50771,7 +50709,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N513" s="2" t="n">
+      <c r="N513" s="1" t="n">
         <v>45994</v>
       </c>
       <c r="O513" t="inlineStr">
@@ -50816,10 +50754,8 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
+      <c r="A514" t="n">
+        <v>2746</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -50871,7 +50807,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N514" s="2" t="n">
+      <c r="N514" s="1" t="n">
         <v>45994</v>
       </c>
       <c r="O514" t="inlineStr">
@@ -50916,10 +50852,8 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>2823</t>
-        </is>
+      <c r="A515" t="n">
+        <v>2823</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -50971,7 +50905,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N515" s="2" t="n">
+      <c r="N515" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="O515" t="inlineStr">
@@ -51016,10 +50950,8 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>2823</t>
-        </is>
+      <c r="A516" t="n">
+        <v>2823</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -51071,7 +51003,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N516" s="2" t="n">
+      <c r="N516" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="O516" t="inlineStr">
@@ -51116,10 +51048,8 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
+      <c r="A517" t="n">
+        <v>2825</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -51171,7 +51101,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N517" s="2" t="n">
+      <c r="N517" s="1" t="n">
         <v>46050</v>
       </c>
       <c r="O517" t="inlineStr">
@@ -51216,10 +51146,8 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A518" t="n">
+        <v>2833</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -51271,7 +51199,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N518" s="2" t="n">
+      <c r="N518" s="1" t="n">
         <v>45993</v>
       </c>
       <c r="O518" t="inlineStr">
@@ -51316,10 +51244,8 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A519" t="n">
+        <v>2833</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -51371,7 +51297,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N519" s="2" t="n">
+      <c r="N519" s="1" t="n">
         <v>45993</v>
       </c>
       <c r="O519" t="inlineStr">
@@ -51416,10 +51342,8 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
+      <c r="A520" t="n">
+        <v>3301</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -51471,7 +51395,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N520" s="2" t="n">
+      <c r="N520" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O520" t="inlineStr">
@@ -51516,10 +51440,8 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
+      <c r="A521" t="n">
+        <v>4835</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -51571,7 +51493,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N521" s="2" t="n">
+      <c r="N521" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O521" t="inlineStr">
@@ -51616,10 +51538,8 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
+      <c r="A522" t="n">
+        <v>4835</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -51671,7 +51591,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N522" s="2" t="n">
+      <c r="N522" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O522" t="inlineStr">
@@ -51716,10 +51636,8 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A523" t="n">
+        <v>9119</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -51771,7 +51689,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N523" s="2" t="n">
+      <c r="N523" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="O523" t="inlineStr">
@@ -51816,10 +51734,8 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>9913</t>
-        </is>
+      <c r="A524" t="n">
+        <v>9913</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -51871,7 +51787,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N524" s="2" t="n">
+      <c r="N524" s="1" t="n">
         <v>46050</v>
       </c>
       <c r="O524" t="inlineStr">
@@ -51916,10 +51832,8 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>9943</t>
-        </is>
+      <c r="A525" t="n">
+        <v>9943</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -51971,7 +51885,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N525" s="2" t="n">
+      <c r="N525" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="O525" t="inlineStr">
@@ -52012,6 +51926,3302 @@
       <c r="V525" t="inlineStr">
         <is>
           <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F526" t="n">
+        <v>118853</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN FINANCIERA</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I526" t="n">
+        <v>28</v>
+      </c>
+      <c r="J526" t="n">
+        <v>2</v>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr"/>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T526" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U526" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V526" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F527" t="n">
+        <v>118852</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN APRENDIZAJE AUTOMÁTICO MEDIANTE INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I527" t="n">
+        <v>28</v>
+      </c>
+      <c r="J527" t="n">
+        <v>2</v>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr"/>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S527" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T527" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U527" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V527" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD POPULAR DEL CESAR</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F528" t="n">
+        <v>118862</v>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN DE LA CALIDAD Y AUDITORIA DE SERVICIOS DE SALUD</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I528" t="n">
+        <v>25</v>
+      </c>
+      <c r="J528" t="n">
+        <v>2</v>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N528" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T528" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U528" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V528" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F529" t="n">
+        <v>118865</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN FINANCIERA</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I529" t="n">
+        <v>44</v>
+      </c>
+      <c r="J529" t="n">
+        <v>3</v>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N529" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T529" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U529" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V529" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE NARIÑO</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F530" t="n">
+        <v>118874</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN INGENIERÍA</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I530" t="n">
+        <v>96</v>
+      </c>
+      <c r="J530" t="n">
+        <v>3</v>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N530" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T530" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U530" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V530" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE PAMPLONA</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Pamplona</t>
+        </is>
+      </c>
+      <c r="F531" t="n">
+        <v>118873</v>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN INGENIERÍA ELECTRÓNICA</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I531" t="n">
+        <v>100</v>
+      </c>
+      <c r="J531" t="n">
+        <v>8</v>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr"/>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N531" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R531" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T531" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U531" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V531" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE PAMPLONA</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Pamplona</t>
+        </is>
+      </c>
+      <c r="F532" t="n">
+        <v>118872</v>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INTERVENCIÓN SOCIAL Y COMUNITARIA</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Híbrida (A distancia-Virtual)</t>
+        </is>
+      </c>
+      <c r="I532" t="n">
+        <v>42</v>
+      </c>
+      <c r="J532" t="n">
+        <v>4</v>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N532" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q532" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R532" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S532" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T532" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U532" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V532" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>PONTIFICIA UNIVERSIDAD JAVERIANA</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F533" t="n">
+        <v>118863</v>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ARQUITECTURA DEL PAISAJE</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I533" t="n">
+        <v>42</v>
+      </c>
+      <c r="J533" t="n">
+        <v>3</v>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N533" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>Arquitectura y urbanismo</t>
+        </is>
+      </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>Arquitectura y afines</t>
+        </is>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T533" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U533" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V533" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F534" t="n">
+        <v>118856</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I534" t="n">
+        <v>28</v>
+      </c>
+      <c r="J534" t="n">
+        <v>2</v>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N534" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T534" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U534" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V534" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F535" t="n">
+        <v>118871</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN COMUNICACIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I535" t="n">
+        <v>36</v>
+      </c>
+      <c r="J535" t="n">
+        <v>3</v>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr"/>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N535" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T535" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V535" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F536" t="n">
+        <v>118831</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN DERECHO</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I536" t="n">
+        <v>75</v>
+      </c>
+      <c r="J536" t="n">
+        <v>7</v>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N536" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T536" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U536" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V536" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F537" t="n">
+        <v>118827</v>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ARQUITECTURA DE SISTEMAS DE INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I537" t="n">
+        <v>47</v>
+      </c>
+      <c r="J537" t="n">
+        <v>4</v>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr"/>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N537" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R537" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T537" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U537" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V537" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LIBRE</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F538" t="n">
+        <v>118833</v>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANÁLISIS ESTRATÉGICO DE DATOS</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I538" t="n">
+        <v>29</v>
+      </c>
+      <c r="J538" t="n">
+        <v>2</v>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr"/>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N538" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T538" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V538" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LIBRE</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F539" t="n">
+        <v>118832</v>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANÁLISIS ESTRATÉGICO DE DATOS</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I539" t="n">
+        <v>29</v>
+      </c>
+      <c r="J539" t="n">
+        <v>2</v>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr"/>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N539" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R539" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T539" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V539" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F540" t="n">
+        <v>118849</v>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN COMUNICACIÓN EN SALUD</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I540" t="n">
+        <v>21</v>
+      </c>
+      <c r="J540" t="n">
+        <v>2</v>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr"/>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N540" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T540" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V540" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F541" t="n">
+        <v>118843</v>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GEOPOLÍTICA Y GEOECONOMÍA</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I541" t="n">
+        <v>23</v>
+      </c>
+      <c r="J541" t="n">
+        <v>2</v>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr"/>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N541" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T541" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V541" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F542" t="n">
+        <v>118847</v>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I542" t="n">
+        <v>43</v>
+      </c>
+      <c r="J542" t="n">
+        <v>4</v>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr"/>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N542" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q542" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S542" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T542" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V542" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>1824</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F543" t="n">
+        <v>118876</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN REHABILITACION ORAL</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I543" t="n">
+        <v>80</v>
+      </c>
+      <c r="J543" t="n">
+        <v>4</v>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N543" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q543" t="inlineStr">
+        <is>
+          <t>Odontología y estudios dentales</t>
+        </is>
+      </c>
+      <c r="R543" t="inlineStr">
+        <is>
+          <t>Odontología</t>
+        </is>
+      </c>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T543" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V543" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F544" t="n">
+        <v>118875</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INCLUSIÓN SOCIAL</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I544" t="n">
+        <v>47</v>
+      </c>
+      <c r="J544" t="n">
+        <v>4</v>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N544" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T544" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V544" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F545" t="n">
+        <v>118860</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN CLIODINÁMICA</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I545" t="n">
+        <v>72</v>
+      </c>
+      <c r="J545" t="n">
+        <v>7</v>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N545" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>Bibliotecología, otros de ciencias sociales y humanas</t>
+        </is>
+      </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T545" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V545" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA MARIA CANO</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F546" t="n">
+        <v>118835</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN FONOAUDIOLOGÍA EN CUIDADO CRÍTICO</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I546" t="n">
+        <v>30</v>
+      </c>
+      <c r="J546" t="n">
+        <v>2</v>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N546" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>Terapias</t>
+        </is>
+      </c>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T546" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V546" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2828</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL HUILA-CORHUILA-</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F547" t="n">
+        <v>118834</v>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ARQUITECTURA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I547" t="n">
+        <v>24</v>
+      </c>
+      <c r="J547" t="n">
+        <v>2</v>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N547" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T547" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U547" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V547" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DE BARRANQUILLA - IUB</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F548" t="n">
+        <v>118861</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE TI Y CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I548" t="n">
+        <v>30</v>
+      </c>
+      <c r="J548" t="n">
+        <v>2</v>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr"/>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N548" s="2" t="n">
+        <v>45623</v>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q548" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T548" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V548" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F549" t="n">
+        <v>118838</v>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE MARKETING</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I549" t="n">
+        <v>45</v>
+      </c>
+      <c r="J549" t="n">
+        <v>3</v>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr"/>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N549" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q549" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S549" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T549" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U549" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V549" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>3720</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA ESUMER</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F550" t="n">
+        <v>118836</v>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA LOGÍSTICA INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I550" t="n">
+        <v>29</v>
+      </c>
+      <c r="J550" t="n">
+        <v>2</v>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr"/>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N550" s="2" t="n">
+        <v>44153</v>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T550" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U550" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V550" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F551" t="n">
+        <v>118851</v>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I551" t="n">
+        <v>28</v>
+      </c>
+      <c r="J551" t="n">
+        <v>2</v>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr"/>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N551" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q551" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S551" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T551" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V551" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F552" t="n">
+        <v>118866</v>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I552" t="n">
+        <v>44</v>
+      </c>
+      <c r="J552" t="n">
+        <v>3</v>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr"/>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N552" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q552" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R552" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S552" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T552" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V552" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F553" t="n">
+        <v>118869</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN LIDERAZGO Y COACHING ORGANIZACIONAL</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I553" t="n">
+        <v>39</v>
+      </c>
+      <c r="J553" t="n">
+        <v>3</v>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr"/>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N553" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q553" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R553" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T553" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U553" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V553" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F554" t="n">
+        <v>118868</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN LIDERAZGO Y COACHING ORGANIZACIONAL</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I554" t="n">
+        <v>39</v>
+      </c>
+      <c r="J554" t="n">
+        <v>3</v>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr"/>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N554" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q554" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R554" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S554" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T554" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V554" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>9900</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA U DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F555" t="n">
+        <v>118877</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN FINANZAS Y BANCA</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I555" t="n">
+        <v>32</v>
+      </c>
+      <c r="J555" t="n">
+        <v>2</v>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr"/>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N555" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q555" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S555" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T555" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V555" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>9900</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA U DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F556" t="n">
+        <v>118870</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN RELACIONES LABORALES Y SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I556" t="n">
+        <v>30</v>
+      </c>
+      <c r="J556" t="n">
+        <v>2</v>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr"/>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N556" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q556" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T556" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V556" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F557" t="n">
+        <v>118839</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO DIGITAL</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I557" t="n">
+        <v>24</v>
+      </c>
+      <c r="J557" t="n">
+        <v>2</v>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr"/>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N557" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q557" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R557" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T557" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V557" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>9938</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA DEL CHICAMOCHA</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F558" t="n">
+        <v>118864</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I558" t="n">
+        <v>26</v>
+      </c>
+      <c r="J558" t="n">
+        <v>2</v>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr"/>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N558" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>Servicios de higiene y salud ocupacional</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>Salud y protección laboral</t>
+        </is>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T558" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V558" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V558"/>
+  <dimension ref="A1:V598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51930,10 +51930,8 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
+      <c r="A526" t="n">
+        <v>1101</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -52028,10 +52026,8 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>1103</t>
-        </is>
+      <c r="A527" t="n">
+        <v>1103</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -52126,10 +52122,8 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
+      <c r="A528" t="n">
+        <v>1120</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -52181,7 +52175,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N528" s="2" t="n">
+      <c r="N528" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O528" t="inlineStr">
@@ -52226,10 +52220,8 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
+      <c r="A529" t="n">
+        <v>1205</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
@@ -52281,7 +52273,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N529" s="2" t="n">
+      <c r="N529" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="O529" t="inlineStr">
@@ -52326,10 +52318,8 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
+      <c r="A530" t="n">
+        <v>1206</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -52381,7 +52371,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N530" s="2" t="n">
+      <c r="N530" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O530" t="inlineStr">
@@ -52426,10 +52416,8 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
+      <c r="A531" t="n">
+        <v>1212</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
@@ -52481,7 +52469,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N531" s="2" t="n">
+      <c r="N531" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O531" t="inlineStr">
@@ -52526,10 +52514,8 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
+      <c r="A532" t="n">
+        <v>1212</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
@@ -52581,7 +52567,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N532" s="2" t="n">
+      <c r="N532" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O532" t="inlineStr">
@@ -52626,10 +52612,8 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A533" t="n">
+        <v>1701</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
@@ -52681,7 +52665,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N533" s="2" t="n">
+      <c r="N533" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O533" t="inlineStr">
@@ -52726,10 +52710,8 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A534" t="n">
+        <v>1709</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
@@ -52781,7 +52763,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N534" s="2" t="n">
+      <c r="N534" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O534" t="inlineStr">
@@ -52826,10 +52808,8 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A535" t="n">
+        <v>1712</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -52881,7 +52861,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N535" s="2" t="n">
+      <c r="N535" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O535" t="inlineStr">
@@ -52926,10 +52906,8 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A536" t="n">
+        <v>1805</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -52981,7 +52959,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N536" s="2" t="n">
+      <c r="N536" s="1" t="n">
         <v>46139</v>
       </c>
       <c r="O536" t="inlineStr">
@@ -53026,10 +53004,8 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A537" t="n">
+        <v>1805</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -53081,7 +53057,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N537" s="2" t="n">
+      <c r="N537" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="O537" t="inlineStr">
@@ -53126,10 +53102,8 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>1809</t>
-        </is>
+      <c r="A538" t="n">
+        <v>1809</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -53181,7 +53155,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N538" s="2" t="n">
+      <c r="N538" s="1" t="n">
         <v>46050</v>
       </c>
       <c r="O538" t="inlineStr">
@@ -53226,10 +53200,8 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>1809</t>
-        </is>
+      <c r="A539" t="n">
+        <v>1809</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -53281,7 +53253,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N539" s="2" t="n">
+      <c r="N539" s="1" t="n">
         <v>46050</v>
       </c>
       <c r="O539" t="inlineStr">
@@ -53326,10 +53298,8 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A540" t="n">
+        <v>1818</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -53381,7 +53351,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N540" s="2" t="n">
+      <c r="N540" s="1" t="n">
         <v>46100</v>
       </c>
       <c r="O540" t="inlineStr">
@@ -53426,10 +53396,8 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A541" t="n">
+        <v>1818</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -53481,7 +53449,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N541" s="2" t="n">
+      <c r="N541" s="1" t="n">
         <v>46100</v>
       </c>
       <c r="O541" t="inlineStr">
@@ -53526,10 +53494,8 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A542" t="n">
+        <v>1818</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -53581,7 +53547,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N542" s="2" t="n">
+      <c r="N542" s="1" t="n">
         <v>46100</v>
       </c>
       <c r="O542" t="inlineStr">
@@ -53626,10 +53592,8 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>1824</t>
-        </is>
+      <c r="A543" t="n">
+        <v>1824</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -53681,7 +53645,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N543" s="2" t="n">
+      <c r="N543" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O543" t="inlineStr">
@@ -53726,10 +53690,8 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A544" t="n">
+        <v>1826</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -53781,7 +53743,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N544" s="2" t="n">
+      <c r="N544" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O544" t="inlineStr">
@@ -53826,10 +53788,8 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A545" t="n">
+        <v>2102</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -53881,7 +53841,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N545" s="2" t="n">
+      <c r="N545" s="1" t="n">
         <v>46051</v>
       </c>
       <c r="O545" t="inlineStr">
@@ -53926,10 +53886,8 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>2721</t>
-        </is>
+      <c r="A546" t="n">
+        <v>2721</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
@@ -53981,7 +53939,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N546" s="2" t="n">
+      <c r="N546" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O546" t="inlineStr">
@@ -54026,10 +53984,8 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>2828</t>
-        </is>
+      <c r="A547" t="n">
+        <v>2828</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
@@ -54081,7 +54037,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N547" s="2" t="n">
+      <c r="N547" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O547" t="inlineStr">
@@ -54126,10 +54082,8 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>3117</t>
-        </is>
+      <c r="A548" t="n">
+        <v>3117</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
@@ -54181,7 +54135,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N548" s="2" t="n">
+      <c r="N548" s="1" t="n">
         <v>45623</v>
       </c>
       <c r="O548" t="inlineStr">
@@ -54226,10 +54180,8 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
+      <c r="A549" t="n">
+        <v>3204</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
@@ -54281,7 +54233,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N549" s="2" t="n">
+      <c r="N549" s="1" t="n">
         <v>46050</v>
       </c>
       <c r="O549" t="inlineStr">
@@ -54326,10 +54278,8 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>3720</t>
-        </is>
+      <c r="A550" t="n">
+        <v>3720</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
@@ -54381,7 +54331,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N550" s="2" t="n">
+      <c r="N550" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="O550" t="inlineStr">
@@ -54426,10 +54376,8 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A551" t="n">
+        <v>4813</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
@@ -54481,7 +54429,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N551" s="2" t="n">
+      <c r="N551" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="O551" t="inlineStr">
@@ -54526,10 +54474,8 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A552" t="n">
+        <v>9119</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -54581,7 +54527,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N552" s="2" t="n">
+      <c r="N552" s="1" t="n">
         <v>46099</v>
       </c>
       <c r="O552" t="inlineStr">
@@ -54626,10 +54572,8 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A553" t="n">
+        <v>9119</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -54681,7 +54625,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N553" s="2" t="n">
+      <c r="N553" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O553" t="inlineStr">
@@ -54726,10 +54670,8 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A554" t="n">
+        <v>9119</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -54781,7 +54723,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N554" s="2" t="n">
+      <c r="N554" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O554" t="inlineStr">
@@ -54826,10 +54768,8 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>9900</t>
-        </is>
+      <c r="A555" t="n">
+        <v>9900</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
@@ -54881,7 +54821,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N555" s="2" t="n">
+      <c r="N555" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O555" t="inlineStr">
@@ -54926,10 +54866,8 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>9900</t>
-        </is>
+      <c r="A556" t="n">
+        <v>9900</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
@@ -54981,7 +54919,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N556" s="2" t="n">
+      <c r="N556" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O556" t="inlineStr">
@@ -55026,10 +54964,8 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>9913</t>
-        </is>
+      <c r="A557" t="n">
+        <v>9913</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
@@ -55081,7 +55017,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N557" s="2" t="n">
+      <c r="N557" s="1" t="n">
         <v>46050</v>
       </c>
       <c r="O557" t="inlineStr">
@@ -55126,10 +55062,8 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>9938</t>
-        </is>
+      <c r="A558" t="n">
+        <v>9938</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
@@ -55181,7 +55115,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N558" s="2" t="n">
+      <c r="N558" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="O558" t="inlineStr">
@@ -55222,6 +55156,4006 @@
       <c r="V558" t="inlineStr">
         <is>
           <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PEDAGOGICA Y TECNOLOGICA DE COLOMBIA - UPTC</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F559" t="n">
+        <v>118893</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CANNABIS Y CANNABINOIDES</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I559" t="n">
+        <v>24</v>
+      </c>
+      <c r="J559" t="n">
+        <v>2</v>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr"/>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N559" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias naturales, matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias naturales, matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>Química y afines</t>
+        </is>
+      </c>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T559" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V559" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PEDAGOGICA Y TECNOLOGICA DE COLOMBIA - UPTC</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F560" t="n">
+        <v>118894</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CANNABIS Y CANNABINOIDES</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I560" t="n">
+        <v>24</v>
+      </c>
+      <c r="J560" t="n">
+        <v>2</v>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr"/>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N560" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias naturales, matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias naturales, matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>Química y afines</t>
+        </is>
+      </c>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T560" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V560" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PEDAGOGICA Y TECNOLOGICA DE COLOMBIA - UPTC</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F561" t="n">
+        <v>118902</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN SEGURIDAD Y CALIDAD ALIMENTARIA</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I561" t="n">
+        <v>24</v>
+      </c>
+      <c r="J561" t="n">
+        <v>2</v>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr"/>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N561" s="2" t="n">
+        <v>45306</v>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias naturales, matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias naturales, matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>Química y afines</t>
+        </is>
+      </c>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V561" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F562" t="n">
+        <v>118957</v>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN EDUCACION</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I562" t="n">
+        <v>53</v>
+      </c>
+      <c r="J562" t="n">
+        <v>4</v>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr"/>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N562" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V562" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F563" t="n">
+        <v>118937</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I563" t="n">
+        <v>50</v>
+      </c>
+      <c r="J563" t="n">
+        <v>4</v>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr"/>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N563" s="2" t="n">
+        <v>43719</v>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V563" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F564" t="n">
+        <v>118896</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GEOMÁTICA</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I564" t="n">
+        <v>46</v>
+      </c>
+      <c r="J564" t="n">
+        <v>4</v>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr"/>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N564" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>Ciencias físicas</t>
+        </is>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>Ciencias de la tierra</t>
+        </is>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T564" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V564" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F565" t="n">
+        <v>118918</v>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN LITERATURAS COLOMBIANA Y LATINOAMERICANA</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I565" t="n">
+        <v>48</v>
+      </c>
+      <c r="J565" t="n">
+        <v>4</v>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr"/>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N565" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>Literatura y lingüística</t>
+        </is>
+      </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>Lenguas modernas, literatura, linguística y afines</t>
+        </is>
+      </c>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T565" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U565" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V565" t="inlineStr">
+        <is>
+          <t>Instituto de Idiomas</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F566" t="n">
+        <v>118891</v>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN BANCA DE INVERSIÓN Y CAPITAL PRIVADO</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>Presencial-Virtual</t>
+        </is>
+      </c>
+      <c r="I566" t="n">
+        <v>22</v>
+      </c>
+      <c r="J566" t="n">
+        <v>2</v>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr"/>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N566" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q566" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S566" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T566" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U566" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V566" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F567" t="n">
+        <v>118890</v>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CREACIÓN DIGITAL Y PRODUCCIÓN DE VIDEOJUEGOS</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I567" t="n">
+        <v>42</v>
+      </c>
+      <c r="J567" t="n">
+        <v>3</v>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr"/>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N567" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q567" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R567" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T567" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U567" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V567" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>1717</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F568" t="n">
+        <v>118880</v>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN RESPONSABILIDAD Y SEGUROS</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I568" t="n">
+        <v>24</v>
+      </c>
+      <c r="J568" t="n">
+        <v>2</v>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr"/>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N568" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q568" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R568" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S568" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T568" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U568" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V568" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F569" t="n">
+        <v>118951</v>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE MARKETING Y COMUNICACIÓN DIGITAL</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I569" t="n">
+        <v>20</v>
+      </c>
+      <c r="J569" t="n">
+        <v>2</v>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr"/>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N569" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q569" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R569" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S569" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T569" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V569" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F570" t="n">
+        <v>118950</v>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE MARKETING Y COMUNICACIÓN DIGITAL</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I570" t="n">
+        <v>20</v>
+      </c>
+      <c r="J570" t="n">
+        <v>2</v>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr"/>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N570" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q570" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S570" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T570" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U570" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V570" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F571" t="n">
+        <v>118895</v>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN COMUNICACIÓN</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I571" t="n">
+        <v>37</v>
+      </c>
+      <c r="J571" t="n">
+        <v>3</v>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr"/>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N571" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q571" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R571" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S571" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T571" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U571" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V571" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F572" t="n">
+        <v>118949</v>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DESARROLLO, GOBIERNO Y POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I572" t="n">
+        <v>36</v>
+      </c>
+      <c r="J572" t="n">
+        <v>3</v>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr"/>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N572" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q572" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R572" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S572" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T572" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V572" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F573" t="n">
+        <v>118930</v>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN TECNOLOGÍAS DE LA INFORMACIÓN GEOGRÁFICA</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I573" t="n">
+        <v>35</v>
+      </c>
+      <c r="J573" t="n">
+        <v>3</v>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr"/>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N573" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V573" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F574" t="n">
+        <v>118908</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DERECHO ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I574" t="n">
+        <v>24</v>
+      </c>
+      <c r="J574" t="n">
+        <v>2</v>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr"/>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N574" s="2" t="n">
+        <v>44377</v>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V574" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F575" t="n">
+        <v>118904</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I575" t="n">
+        <v>24</v>
+      </c>
+      <c r="J575" t="n">
+        <v>2</v>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr"/>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N575" s="2" t="n">
+        <v>45218</v>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V575" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F576" t="n">
+        <v>118905</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN POLITICAS Y LEGISLACION TRIBUTARIA</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I576" t="n">
+        <v>24</v>
+      </c>
+      <c r="J576" t="n">
+        <v>2</v>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr"/>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N576" s="2" t="n">
+        <v>44392</v>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V576" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F577" t="n">
+        <v>118932</v>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ANALÍTICA DE DATOS APLICADA A LA SOCIEDAD Y LA ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I577" t="n">
+        <v>33</v>
+      </c>
+      <c r="J577" t="n">
+        <v>3</v>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr"/>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N577" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V577" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F578" t="n">
+        <v>118929</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I578" t="n">
+        <v>36</v>
+      </c>
+      <c r="J578" t="n">
+        <v>3</v>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr"/>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N578" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V578" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F579" t="n">
+        <v>118934</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN INGENIERIA EN ENERGIA</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I579" t="n">
+        <v>37</v>
+      </c>
+      <c r="J579" t="n">
+        <v>3</v>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr"/>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N579" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>Ingeniería eléctrica y afines</t>
+        </is>
+      </c>
+      <c r="S579" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V579" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F580" t="n">
+        <v>118936</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANALÍTICA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I580" t="n">
+        <v>27</v>
+      </c>
+      <c r="J580" t="n">
+        <v>2</v>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr"/>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N580" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S580" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V580" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ANTONIO NARIÑO</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F581" t="n">
+        <v>118889</v>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ENFERMERÍA MATERNO PERINATAL</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I581" t="n">
+        <v>27</v>
+      </c>
+      <c r="J581" t="n">
+        <v>2</v>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr"/>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N581" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S581" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V581" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F582" t="n">
+        <v>118917</v>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN OPERACIONES DE CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I582" t="n">
+        <v>24</v>
+      </c>
+      <c r="J582" t="n">
+        <v>2</v>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr"/>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N582" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S582" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V582" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>1834</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSIDAD DEL SINU - ELIAS BECHARA ZAINUM - UNISINU -</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F583" t="n">
+        <v>118888</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN PERIODONCIA</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I583" t="n">
+        <v>88</v>
+      </c>
+      <c r="J583" t="n">
+        <v>5</v>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr"/>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N583" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q583" t="inlineStr">
+        <is>
+          <t>Odontología y estudios dentales</t>
+        </is>
+      </c>
+      <c r="R583" t="inlineStr">
+        <is>
+          <t>Odontología</t>
+        </is>
+      </c>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V583" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>DIRECCION DE EDUCACION POLICIAL</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F584" t="n">
+        <v>118898</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN INVESTIGACION DE ACCIDENTES DE TRANSITO</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I584" t="n">
+        <v>26</v>
+      </c>
+      <c r="J584" t="n">
+        <v>2</v>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr"/>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N584" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q584" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S584" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V584" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA KONRAD LORENZ</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F585" t="n">
+        <v>118952</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INTELIGENCIA ARTIFICIAL APLICADA A CONTEXTOS HUMANOS Y SOCIALES</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I585" t="n">
+        <v>34</v>
+      </c>
+      <c r="J585" t="n">
+        <v>3</v>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr"/>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N585" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q585" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R585" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S585" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T585" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V585" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATÓLICA LUIS AMIGÓ</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F586" t="n">
+        <v>118892</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ADICCIONES Y SALUD MENTAL</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I586" t="n">
+        <v>40</v>
+      </c>
+      <c r="J586" t="n">
+        <v>3</v>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr"/>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N586" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q586" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R586" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S586" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V586" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CATOLICA LUMEN GENTIUM - UNICATÓLICA - CALI</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F587" t="n">
+        <v>118946</v>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN EDUCACIÓN MEDIADA POR TECNOLOGÍAS</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I587" t="n">
+        <v>24</v>
+      </c>
+      <c r="J587" t="n">
+        <v>2</v>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr"/>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N587" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q587" t="inlineStr">
+        <is>
+          <t>Formación para docentes sin asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S587" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V587" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F588" t="n">
+        <v>118854</v>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I588" t="n">
+        <v>24</v>
+      </c>
+      <c r="J588" t="n">
+        <v>2</v>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr"/>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N588" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q588" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R588" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S588" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V588" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA ANTONIO JOSE CAMACHO</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F589" t="n">
+        <v>118881</v>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I589" t="n">
+        <v>44</v>
+      </c>
+      <c r="J589" t="n">
+        <v>4</v>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr"/>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N589" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q589" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R589" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S589" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V589" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>4721</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA HORIZONTE</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F590" t="n">
+        <v>118911</v>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN COMUNICACIÓN DIGITAL</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I590" t="n">
+        <v>26</v>
+      </c>
+      <c r="J590" t="n">
+        <v>2</v>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr"/>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N590" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q590" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R590" t="inlineStr">
+        <is>
+          <t>Publicidad y afines</t>
+        </is>
+      </c>
+      <c r="S590" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V590" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>4721</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA HORIZONTE</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F591" t="n">
+        <v>118910</v>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE LA CALIDAD</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I591" t="n">
+        <v>34</v>
+      </c>
+      <c r="J591" t="n">
+        <v>2</v>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr"/>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N591" s="2" t="n">
+        <v>44141</v>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q591" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R591" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V591" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>ESCUELA NAVAL DE CADETES ALMIRANTE PADILLA</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F592" t="n">
+        <v>118931</v>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DERECHO INTERNACIONAL DEL MAR Y MARÍTIMO</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I592" t="n">
+        <v>59</v>
+      </c>
+      <c r="J592" t="n">
+        <v>4</v>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr"/>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N592" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q592" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R592" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S592" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T592" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U592" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V592" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F593" t="n">
+        <v>118907</v>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN SEGURIDAD INFORMATICA</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I593" t="n">
+        <v>27</v>
+      </c>
+      <c r="J593" t="n">
+        <v>2</v>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr"/>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N593" s="2" t="n">
+        <v>44153</v>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q593" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S593" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T593" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U593" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V593" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F594" t="n">
+        <v>118883</v>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN TECNOLÓGICA EN MARKETING Y MODELO DE NEGOCIOS ONLINE</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I594" t="n">
+        <v>18</v>
+      </c>
+      <c r="J594" t="n">
+        <v>1</v>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr"/>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N594" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q594" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R594" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S594" t="inlineStr">
+        <is>
+          <t>Especialización tecnológica</t>
+        </is>
+      </c>
+      <c r="T594" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V594" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F595" t="n">
+        <v>118882</v>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN TECNOLÓGICA EN MARKETING Y MODELO DE NEGOCIOS ONLINE</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I595" t="n">
+        <v>18</v>
+      </c>
+      <c r="J595" t="n">
+        <v>1</v>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr"/>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N595" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q595" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R595" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S595" t="inlineStr">
+        <is>
+          <t>Especialización tecnológica</t>
+        </is>
+      </c>
+      <c r="T595" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U595" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V595" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F596" t="n">
+        <v>118884</v>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN TECNOLÓGICA EN MARKETING Y MODELO DE NEGOCIOS ONLINE</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I596" t="n">
+        <v>18</v>
+      </c>
+      <c r="J596" t="n">
+        <v>1</v>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr"/>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N596" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q596" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R596" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S596" t="inlineStr">
+        <is>
+          <t>Especialización tecnológica</t>
+        </is>
+      </c>
+      <c r="T596" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U596" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V596" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F597" t="n">
+        <v>118925</v>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN DE LA CALIDAD INTEGRAL EN LAS ORGANIZACIONES</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I597" t="n">
+        <v>38</v>
+      </c>
+      <c r="J597" t="n">
+        <v>3</v>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr"/>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N597" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q597" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S597" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T597" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U597" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V597" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F598" t="n">
+        <v>118926</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN DE LA CALIDAD INTEGRAL EN LAS ORGANIZACIONES</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I598" t="n">
+        <v>38</v>
+      </c>
+      <c r="J598" t="n">
+        <v>3</v>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr"/>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N598" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q598" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R598" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S598" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T598" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="U598" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V598" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V598"/>
+  <dimension ref="A1:V615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55160,10 +55160,8 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A559" t="n">
+        <v>1106</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
@@ -55215,7 +55213,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N559" s="2" t="n">
+      <c r="N559" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="O559" t="inlineStr">
@@ -55260,10 +55258,8 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A560" t="n">
+        <v>1106</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
@@ -55315,7 +55311,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N560" s="2" t="n">
+      <c r="N560" s="1" t="n">
         <v>46120</v>
       </c>
       <c r="O560" t="inlineStr">
@@ -55360,10 +55356,8 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A561" t="n">
+        <v>1106</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
@@ -55415,7 +55409,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N561" s="2" t="n">
+      <c r="N561" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="O561" t="inlineStr">
@@ -55460,10 +55454,8 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A562" t="n">
+        <v>1203</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
@@ -55515,7 +55507,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N562" s="2" t="n">
+      <c r="N562" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="O562" t="inlineStr">
@@ -55560,10 +55552,8 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A563" t="n">
+        <v>1203</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
@@ -55615,7 +55605,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N563" s="2" t="n">
+      <c r="N563" s="1" t="n">
         <v>43719</v>
       </c>
       <c r="O563" t="inlineStr">
@@ -55660,10 +55650,8 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A564" t="n">
+        <v>1203</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
@@ -55715,7 +55703,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N564" s="2" t="n">
+      <c r="N564" s="1" t="n">
         <v>46127</v>
       </c>
       <c r="O564" t="inlineStr">
@@ -55760,10 +55748,8 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A565" t="n">
+        <v>1203</v>
       </c>
       <c r="B565" t="inlineStr">
         <is>
@@ -55815,7 +55801,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N565" s="2" t="n">
+      <c r="N565" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="O565" t="inlineStr">
@@ -55860,10 +55846,8 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A566" t="n">
+        <v>1712</v>
       </c>
       <c r="B566" t="inlineStr">
         <is>
@@ -55915,7 +55899,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N566" s="2" t="n">
+      <c r="N566" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O566" t="inlineStr">
@@ -55960,10 +55944,8 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A567" t="n">
+        <v>1716</v>
       </c>
       <c r="B567" t="inlineStr">
         <is>
@@ -56015,7 +55997,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N567" s="2" t="n">
+      <c r="N567" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="O567" t="inlineStr">
@@ -56060,10 +56042,8 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>1717</t>
-        </is>
+      <c r="A568" t="n">
+        <v>1717</v>
       </c>
       <c r="B568" t="inlineStr">
         <is>
@@ -56115,7 +56095,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N568" s="2" t="n">
+      <c r="N568" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O568" t="inlineStr">
@@ -56160,10 +56140,8 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A569" t="n">
+        <v>1722</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
@@ -56215,7 +56193,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N569" s="2" t="n">
+      <c r="N569" s="1" t="n">
         <v>46170</v>
       </c>
       <c r="O569" t="inlineStr">
@@ -56260,10 +56238,8 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A570" t="n">
+        <v>1722</v>
       </c>
       <c r="B570" t="inlineStr">
         <is>
@@ -56315,7 +56291,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N570" s="2" t="n">
+      <c r="N570" s="1" t="n">
         <v>46170</v>
       </c>
       <c r="O570" t="inlineStr">
@@ -56360,10 +56336,8 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A571" t="n">
+        <v>1722</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
@@ -56415,7 +56389,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N571" s="2" t="n">
+      <c r="N571" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="O571" t="inlineStr">
@@ -56460,10 +56434,8 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A572" t="n">
+        <v>1722</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
@@ -56515,7 +56487,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N572" s="2" t="n">
+      <c r="N572" s="1" t="n">
         <v>46170</v>
       </c>
       <c r="O572" t="inlineStr">
@@ -56560,10 +56532,8 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A573" t="n">
+        <v>1722</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
@@ -56615,7 +56585,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N573" s="2" t="n">
+      <c r="N573" s="1" t="n">
         <v>46139</v>
       </c>
       <c r="O573" t="inlineStr">
@@ -56660,10 +56630,8 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A574" t="n">
+        <v>1812</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
@@ -56715,7 +56683,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N574" s="2" t="n">
+      <c r="N574" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="O574" t="inlineStr">
@@ -56760,10 +56728,8 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A575" t="n">
+        <v>1812</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
@@ -56815,7 +56781,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N575" s="2" t="n">
+      <c r="N575" s="1" t="n">
         <v>45218</v>
       </c>
       <c r="O575" t="inlineStr">
@@ -56860,10 +56826,8 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A576" t="n">
+        <v>1812</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
@@ -56915,7 +56879,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N576" s="2" t="n">
+      <c r="N576" s="1" t="n">
         <v>44392</v>
       </c>
       <c r="O576" t="inlineStr">
@@ -56960,10 +56924,8 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A577" t="n">
+        <v>1813</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -57015,7 +56977,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N577" s="2" t="n">
+      <c r="N577" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O577" t="inlineStr">
@@ -57060,10 +57022,8 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A578" t="n">
+        <v>1823</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -57115,7 +57075,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N578" s="2" t="n">
+      <c r="N578" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O578" t="inlineStr">
@@ -57160,10 +57120,8 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A579" t="n">
+        <v>1823</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -57215,7 +57173,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N579" s="2" t="n">
+      <c r="N579" s="1" t="n">
         <v>46126</v>
       </c>
       <c r="O579" t="inlineStr">
@@ -57260,10 +57218,8 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A580" t="n">
+        <v>1826</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -57315,7 +57271,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N580" s="2" t="n">
+      <c r="N580" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O580" t="inlineStr">
@@ -57360,10 +57316,8 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A581" t="n">
+        <v>1826</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -57415,7 +57369,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N581" s="2" t="n">
+      <c r="N581" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O581" t="inlineStr">
@@ -57460,10 +57414,8 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A582" t="n">
+        <v>1828</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -57515,7 +57467,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N582" s="2" t="n">
+      <c r="N582" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O582" t="inlineStr">
@@ -57560,10 +57512,8 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
+      <c r="A583" t="n">
+        <v>1834</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
@@ -57615,7 +57565,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N583" s="2" t="n">
+      <c r="N583" s="1" t="n">
         <v>46105</v>
       </c>
       <c r="O583" t="inlineStr">
@@ -57660,10 +57610,8 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="A584" t="n">
+        <v>2106</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
@@ -57715,7 +57663,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N584" s="2" t="n">
+      <c r="N584" s="1" t="n">
         <v>46139</v>
       </c>
       <c r="O584" t="inlineStr">
@@ -57760,10 +57708,8 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>2712</t>
-        </is>
+      <c r="A585" t="n">
+        <v>2712</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
@@ -57815,7 +57761,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N585" s="2" t="n">
+      <c r="N585" s="1" t="n">
         <v>46140</v>
       </c>
       <c r="O585" t="inlineStr">
@@ -57860,10 +57806,8 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
+      <c r="A586" t="n">
+        <v>2719</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
@@ -57915,7 +57859,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N586" s="2" t="n">
+      <c r="N586" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O586" t="inlineStr">
@@ -57960,10 +57904,8 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>2731</t>
-        </is>
+      <c r="A587" t="n">
+        <v>2731</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
@@ -58015,7 +57957,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N587" s="2" t="n">
+      <c r="N587" s="1" t="n">
         <v>46169</v>
       </c>
       <c r="O587" t="inlineStr">
@@ -58060,10 +58002,8 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A588" t="n">
+        <v>2829</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
@@ -58115,7 +58055,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N588" s="2" t="n">
+      <c r="N588" s="1" t="n">
         <v>46071</v>
       </c>
       <c r="O588" t="inlineStr">
@@ -58160,10 +58100,8 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
+      <c r="A589" t="n">
+        <v>3301</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
@@ -58215,7 +58153,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N589" s="2" t="n">
+      <c r="N589" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O589" t="inlineStr">
@@ -58260,10 +58198,8 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>4721</t>
-        </is>
+      <c r="A590" t="n">
+        <v>4721</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
@@ -58315,7 +58251,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N590" s="2" t="n">
+      <c r="N590" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O590" t="inlineStr">
@@ -58360,10 +58296,8 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>4721</t>
-        </is>
+      <c r="A591" t="n">
+        <v>4721</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
@@ -58415,7 +58349,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N591" s="2" t="n">
+      <c r="N591" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="O591" t="inlineStr">
@@ -58460,10 +58394,8 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>9105</t>
-        </is>
+      <c r="A592" t="n">
+        <v>9105</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
@@ -58515,7 +58447,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N592" s="2" t="n">
+      <c r="N592" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O592" t="inlineStr">
@@ -58560,10 +58492,8 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A593" t="n">
+        <v>9119</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
@@ -58615,7 +58545,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N593" s="2" t="n">
+      <c r="N593" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="O593" t="inlineStr">
@@ -58660,10 +58590,8 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A594" t="n">
+        <v>9119</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
@@ -58715,7 +58643,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N594" s="2" t="n">
+      <c r="N594" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O594" t="inlineStr">
@@ -58760,10 +58688,8 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A595" t="n">
+        <v>9119</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
@@ -58815,7 +58741,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N595" s="2" t="n">
+      <c r="N595" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O595" t="inlineStr">
@@ -58860,10 +58786,8 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A596" t="n">
+        <v>9119</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
@@ -58915,7 +58839,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N596" s="2" t="n">
+      <c r="N596" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O596" t="inlineStr">
@@ -58960,10 +58884,8 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A597" t="n">
+        <v>9119</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
@@ -59015,7 +58937,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N597" s="2" t="n">
+      <c r="N597" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="O597" t="inlineStr">
@@ -59060,10 +58982,8 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A598" t="n">
+        <v>9119</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
@@ -59115,7 +59035,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N598" s="2" t="n">
+      <c r="N598" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="O598" t="inlineStr">
@@ -59156,6 +59076,1706 @@
       <c r="V598" t="inlineStr">
         <is>
           <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PEDAGOGICA Y TECNOLOGICA DE COLOMBIA - UPTC</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="F599" t="n">
+        <v>118983</v>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN PLANIFICACIÓN Y GESTIÓN DEL TURISMO</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I599" t="n">
+        <v>48</v>
+      </c>
+      <c r="J599" t="n">
+        <v>4</v>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr"/>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N599" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>Servicios personales</t>
+        </is>
+      </c>
+      <c r="Q599" t="inlineStr">
+        <is>
+          <t>Viajes, turismo y actividades recreativas</t>
+        </is>
+      </c>
+      <c r="R599" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S599" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T599" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U599" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V599" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F600" t="n">
+        <v>118965</v>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN SALUD MENTAL Y CONVIVENCIA EN CONTEXTOS EDUCATIVOS</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I600" t="n">
+        <v>39</v>
+      </c>
+      <c r="J600" t="n">
+        <v>3</v>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr"/>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N600" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q600" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S600" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T600" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U600" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V600" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F601" t="n">
+        <v>118975</v>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INTERNET DE LAS COSAS Y TRANSFORMACIÓN DIGITAL</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I601" t="n">
+        <v>43</v>
+      </c>
+      <c r="J601" t="n">
+        <v>3</v>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr"/>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N601" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q601" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R601" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S601" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T601" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U601" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V601" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F602" t="n">
+        <v>118974</v>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GESTION FINANCIERA EMPRESARIAL</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I602" t="n">
+        <v>24</v>
+      </c>
+      <c r="J602" t="n">
+        <v>2</v>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr"/>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N602" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q602" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R602" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S602" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T602" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U602" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V602" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F603" t="n">
+        <v>118962</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INGENIERÍA CLÍNICA</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I603" t="n">
+        <v>25</v>
+      </c>
+      <c r="J603" t="n">
+        <v>2</v>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr"/>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N603" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q603" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R603" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U603" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V603" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F604" t="n">
+        <v>118963</v>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INGENIERÍA CLÍNICA</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I604" t="n">
+        <v>25</v>
+      </c>
+      <c r="J604" t="n">
+        <v>2</v>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr"/>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N604" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q604" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T604" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U604" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V604" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F605" t="n">
+        <v>118964</v>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I605" t="n">
+        <v>36</v>
+      </c>
+      <c r="J605" t="n">
+        <v>3</v>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr"/>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N605" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q605" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R605" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S605" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T605" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U605" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V605" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F606" t="n">
+        <v>118961</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INGENIERÍA FARMACÉUTICA</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I606" t="n">
+        <v>35</v>
+      </c>
+      <c r="J606" t="n">
+        <v>3</v>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr"/>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N606" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q606" t="inlineStr">
+        <is>
+          <t>Ingeniería y procesos químicos</t>
+        </is>
+      </c>
+      <c r="R606" t="inlineStr">
+        <is>
+          <t>Ingeniería química y afines</t>
+        </is>
+      </c>
+      <c r="S606" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T606" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U606" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V606" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F607" t="n">
+        <v>118976</v>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I607" t="n">
+        <v>28</v>
+      </c>
+      <c r="J607" t="n">
+        <v>2</v>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr"/>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="N607" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q607" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S607" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T607" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U607" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V607" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA ANTONIO JOSE DE SUCRE - CORPOSUCRE</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F608" t="n">
+        <v>118960</v>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA FINANCIERA</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I608" t="n">
+        <v>28</v>
+      </c>
+      <c r="J608" t="n">
+        <v>2</v>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr"/>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N608" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q608" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R608" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S608" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T608" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U608" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V608" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>CENTRO DE EDUCACION MILITAR - CEMIL</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F609" t="n">
+        <v>118982</v>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN AMBIENTAL Y DESARROLLO  TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Híbrida (A distancia-Virtual)</t>
+        </is>
+      </c>
+      <c r="I609" t="n">
+        <v>29</v>
+      </c>
+      <c r="J609" t="n">
+        <v>2</v>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr"/>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N609" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>Medio ambiente</t>
+        </is>
+      </c>
+      <c r="Q609" t="inlineStr">
+        <is>
+          <t>Medio ambiente no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R609" t="inlineStr">
+        <is>
+          <t>Geología, otros programas de ciencias naturales</t>
+        </is>
+      </c>
+      <c r="S609" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T609" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U609" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V609" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>4110</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE EL ESPINAL - UNIESPINAL</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Espinal</t>
+        </is>
+      </c>
+      <c r="F610" t="n">
+        <v>118972</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE PROYECTOS DE CONSTRUCCIÓN</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I610" t="n">
+        <v>27</v>
+      </c>
+      <c r="J610" t="n">
+        <v>2</v>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr"/>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N610" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q610" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R610" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S610" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T610" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U610" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V610" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F611" t="n">
+        <v>118978</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANALITICA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I611" t="n">
+        <v>28</v>
+      </c>
+      <c r="J611" t="n">
+        <v>2</v>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr"/>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N611" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q611" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R611" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S611" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T611" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U611" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V611" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F612" t="n">
+        <v>118979</v>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANALITICA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I612" t="n">
+        <v>28</v>
+      </c>
+      <c r="J612" t="n">
+        <v>2</v>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr"/>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N612" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q612" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S612" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T612" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U612" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V612" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F613" t="n">
+        <v>118980</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PEDAGOGÍA Y DOCENCIA</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I613" t="n">
+        <v>29</v>
+      </c>
+      <c r="J613" t="n">
+        <v>2</v>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr"/>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N613" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q613" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R613" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S613" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T613" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U613" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V613" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F614" t="n">
+        <v>118981</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PEDAGOGÍA Y DOCENCIA</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I614" t="n">
+        <v>29</v>
+      </c>
+      <c r="J614" t="n">
+        <v>2</v>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr"/>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N614" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q614" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R614" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S614" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T614" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U614" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V614" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F615" t="n">
+        <v>118977</v>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN NEUROPSICOLOGÍA EN LA EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I615" t="n">
+        <v>24</v>
+      </c>
+      <c r="J615" t="n">
+        <v>2</v>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr"/>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N615" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q615" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R615" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S615" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T615" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="U615" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V615" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V615"/>
+  <dimension ref="A1:V632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59080,10 +59080,8 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
+      <c r="A599" t="n">
+        <v>1107</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
@@ -59135,7 +59133,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N599" s="2" t="n">
+      <c r="N599" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="O599" t="inlineStr">
@@ -59180,10 +59178,8 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A600" t="n">
+        <v>1713</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
@@ -59235,7 +59231,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N600" s="2" t="n">
+      <c r="N600" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="O600" t="inlineStr">
@@ -59280,10 +59276,8 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
+      <c r="A601" t="n">
+        <v>1718</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
@@ -59335,7 +59329,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N601" s="2" t="n">
+      <c r="N601" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O601" t="inlineStr">
@@ -59380,10 +59374,8 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A602" t="n">
+        <v>1812</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
@@ -59435,7 +59427,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N602" s="2" t="n">
+      <c r="N602" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O602" t="inlineStr">
@@ -59480,10 +59472,8 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
+      <c r="A603" t="n">
+        <v>1825</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
@@ -59535,7 +59525,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N603" s="2" t="n">
+      <c r="N603" s="1" t="n">
         <v>46175</v>
       </c>
       <c r="O603" t="inlineStr">
@@ -59580,10 +59570,8 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
+      <c r="A604" t="n">
+        <v>1825</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
@@ -59635,7 +59623,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N604" s="2" t="n">
+      <c r="N604" s="1" t="n">
         <v>46175</v>
       </c>
       <c r="O604" t="inlineStr">
@@ -59680,10 +59668,8 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A605" t="n">
+        <v>1828</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
@@ -59735,7 +59721,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N605" s="2" t="n">
+      <c r="N605" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="O605" t="inlineStr">
@@ -59780,10 +59766,8 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A606" t="n">
+        <v>1828</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
@@ -59835,7 +59819,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N606" s="2" t="n">
+      <c r="N606" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="O606" t="inlineStr">
@@ -59880,10 +59864,8 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A607" t="n">
+        <v>2833</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
@@ -59935,7 +59917,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N607" s="2" t="n">
+      <c r="N607" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O607" t="inlineStr">
@@ -59980,10 +59962,8 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>2850</t>
-        </is>
+      <c r="A608" t="n">
+        <v>2850</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
@@ -60035,7 +60015,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N608" s="2" t="n">
+      <c r="N608" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O608" t="inlineStr">
@@ -60080,10 +60060,8 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>2905</t>
-        </is>
+      <c r="A609" t="n">
+        <v>2905</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
@@ -60135,7 +60113,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N609" s="2" t="n">
+      <c r="N609" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="O609" t="inlineStr">
@@ -60180,10 +60158,8 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>4110</t>
-        </is>
+      <c r="A610" t="n">
+        <v>4110</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
@@ -60235,7 +60211,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N610" s="2" t="n">
+      <c r="N610" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="O610" t="inlineStr">
@@ -60280,10 +60256,8 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A611" t="n">
+        <v>9119</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
@@ -60335,7 +60309,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N611" s="2" t="n">
+      <c r="N611" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O611" t="inlineStr">
@@ -60380,10 +60354,8 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A612" t="n">
+        <v>9119</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
@@ -60435,7 +60407,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N612" s="2" t="n">
+      <c r="N612" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O612" t="inlineStr">
@@ -60480,10 +60452,8 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A613" t="n">
+        <v>9119</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
@@ -60535,7 +60505,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N613" s="2" t="n">
+      <c r="N613" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="O613" t="inlineStr">
@@ -60580,10 +60550,8 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A614" t="n">
+        <v>9119</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
@@ -60635,7 +60603,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N614" s="2" t="n">
+      <c r="N614" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="O614" t="inlineStr">
@@ -60680,10 +60648,8 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>9913</t>
-        </is>
+      <c r="A615" t="n">
+        <v>9913</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
@@ -60735,7 +60701,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N615" s="2" t="n">
+      <c r="N615" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O615" t="inlineStr">
@@ -60776,6 +60742,1706 @@
       <c r="V615" t="inlineStr">
         <is>
           <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Santander de Quilichao</t>
+        </is>
+      </c>
+      <c r="F616" t="n">
+        <v>106198</v>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN BIOINGENIERÍA</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I616" t="n">
+        <v>42</v>
+      </c>
+      <c r="J616" t="n">
+        <v>2</v>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr"/>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N616" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q616" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>Ingeniería biomédica y afines</t>
+        </is>
+      </c>
+      <c r="S616" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V616" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SURCOLOMBIANA</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F617" t="n">
+        <v>119000</v>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INFRAESTRUCTURA VIAL</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I617" t="n">
+        <v>26</v>
+      </c>
+      <c r="J617" t="n">
+        <v>2</v>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr"/>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N617" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q617" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R617" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S617" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T617" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U617" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V617" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F618" t="n">
+        <v>118995</v>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA E INTERVENTORÍA DE PROYECTOS DE CONSTRUCCIÓN</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I618" t="n">
+        <v>38</v>
+      </c>
+      <c r="J618" t="n">
+        <v>3</v>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr"/>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N618" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q618" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>Arquitectura y afines</t>
+        </is>
+      </c>
+      <c r="S618" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T618" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U618" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V618" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F619" t="n">
+        <v>119013</v>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN PSICOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I619" t="n">
+        <v>80</v>
+      </c>
+      <c r="J619" t="n">
+        <v>8</v>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr"/>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N619" s="2" t="n">
+        <v>44264</v>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q619" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S619" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T619" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U619" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V619" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F620" t="n">
+        <v>118991</v>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA Y GESTIÓN DE LA  EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I620" t="n">
+        <v>48</v>
+      </c>
+      <c r="J620" t="n">
+        <v>3</v>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr"/>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N620" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q620" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R620" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S620" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T620" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U620" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V620" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F621" t="n">
+        <v>119001</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN ALTA GERENCIA</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I621" t="n">
+        <v>24</v>
+      </c>
+      <c r="J621" t="n">
+        <v>2</v>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr"/>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N621" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q621" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R621" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S621" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T621" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U621" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V621" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F622" t="n">
+        <v>118993</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE MARCA</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I622" t="n">
+        <v>24</v>
+      </c>
+      <c r="J622" t="n">
+        <v>2</v>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr"/>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N622" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias sociales, periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q622" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a ciencias sociales, periodismo e información</t>
+        </is>
+      </c>
+      <c r="R622" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S622" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T622" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U622" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V622" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Espinal</t>
+        </is>
+      </c>
+      <c r="F623" t="n">
+        <v>118163</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I623" t="n">
+        <v>22</v>
+      </c>
+      <c r="J623" t="n">
+        <v>2</v>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr"/>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N623" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q623" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S623" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T623" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U623" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V623" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F624" t="n">
+        <v>119002</v>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I624" t="n">
+        <v>37</v>
+      </c>
+      <c r="J624" t="n">
+        <v>6</v>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr"/>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N624" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q624" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S624" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T624" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U624" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V624" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F625" t="n">
+        <v>119009</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CAMBIO CLIMÁTICO Y GESTIÓN DEL RIESGO DE DESASTRES</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I625" t="n">
+        <v>37</v>
+      </c>
+      <c r="J625" t="n">
+        <v>3</v>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr"/>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N625" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>Medio ambiente</t>
+        </is>
+      </c>
+      <c r="Q625" t="inlineStr">
+        <is>
+          <t>Ciencias del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R625" t="inlineStr">
+        <is>
+          <t>Geología, otros programas de ciencias naturales</t>
+        </is>
+      </c>
+      <c r="S625" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T625" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U625" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V625" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F626" t="n">
+        <v>119007</v>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DERECHOS HUMANOS Y JUSTICIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I626" t="n">
+        <v>36</v>
+      </c>
+      <c r="J626" t="n">
+        <v>3</v>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr"/>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N626" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q626" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R626" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S626" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T626" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U626" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V626" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F627" t="n">
+        <v>119008</v>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN SEGURIDAD, HIGIENE Y ERGONOMÍA</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I627" t="n">
+        <v>36</v>
+      </c>
+      <c r="J627" t="n">
+        <v>3</v>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr"/>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N627" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>Servicios de higiene y salud ocupacional</t>
+        </is>
+      </c>
+      <c r="Q627" t="inlineStr">
+        <is>
+          <t>Salud y protección laboral</t>
+        </is>
+      </c>
+      <c r="R627" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S627" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T627" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U627" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V627" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA JUAN DE CASTELLANOS</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F628" t="n">
+        <v>118999</v>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ALTA DIRECCIÓN Y AUDITORÍA EN INSTITUCIONES DE SALUD</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I628" t="n">
+        <v>22</v>
+      </c>
+      <c r="J628" t="n">
+        <v>2</v>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr"/>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N628" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q628" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R628" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S628" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T628" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U628" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V628" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EIA</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F629" t="n">
+        <v>118992</v>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN OFTALMOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I629" t="n">
+        <v>189</v>
+      </c>
+      <c r="J629" t="n">
+        <v>6</v>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr"/>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N629" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q629" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R629" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S629" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T629" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U629" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V629" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA RAFAEL NUÑEZ</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F630" t="n">
+        <v>118994</v>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANALÍTICA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I630" t="n">
+        <v>29</v>
+      </c>
+      <c r="J630" t="n">
+        <v>2</v>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr"/>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N630" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q630" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R630" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S630" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T630" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U630" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V630" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F631" t="n">
+        <v>118986</v>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GOBERNANZA DE LA INTELIGENCIA ARTIFICIAL (IA)</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I631" t="n">
+        <v>28</v>
+      </c>
+      <c r="J631" t="n">
+        <v>2</v>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr"/>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N631" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q631" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R631" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S631" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T631" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U631" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V631" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>9922</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA COMFAMILIAR RISARALDA</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F632" t="n">
+        <v>118990</v>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE SERVICIOS DE SALUD</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I632" t="n">
+        <v>30</v>
+      </c>
+      <c r="J632" t="n">
+        <v>2</v>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr"/>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N632" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P632" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q632" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R632" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S632" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T632" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="U632" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V632" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V753"/>
+  <dimension ref="A1:V796"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73950,10 +73950,8 @@
       </c>
     </row>
     <row r="751">
-      <c r="A751" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
+      <c r="A751" t="n">
+        <v>1829</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
@@ -74005,7 +74003,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N751" s="2" t="n">
+      <c r="N751" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="O751" t="inlineStr">
@@ -74050,10 +74048,8 @@
       </c>
     </row>
     <row r="752">
-      <c r="A752" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
+      <c r="A752" t="n">
+        <v>1829</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
@@ -74105,7 +74101,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N752" s="2" t="n">
+      <c r="N752" s="1" t="n">
         <v>46191</v>
       </c>
       <c r="O752" t="inlineStr">
@@ -74150,10 +74146,8 @@
       </c>
     </row>
     <row r="753">
-      <c r="A753" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A753" t="n">
+        <v>2805</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
@@ -74205,7 +74199,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N753" s="2" t="n">
+      <c r="N753" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O753" t="inlineStr">
@@ -74246,6 +74240,4306 @@
       <c r="V753" t="inlineStr">
         <is>
           <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CUNDINAMARCA</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Fusagasugá</t>
+        </is>
+      </c>
+      <c r="F754" t="n">
+        <v>119069</v>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTERVENCIÓN PSICOSOCIAL</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I754" t="n">
+        <v>20</v>
+      </c>
+      <c r="J754" t="n">
+        <v>2</v>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr"/>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N754" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P754" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q754" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R754" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S754" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T754" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U754" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V754" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INCCA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F755" t="n">
+        <v>119022</v>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I755" t="n">
+        <v>27</v>
+      </c>
+      <c r="J755" t="n">
+        <v>2</v>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr"/>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="N755" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P755" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q755" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R755" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S755" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T755" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U755" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V755" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INCCA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F756" t="n">
+        <v>119082</v>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN MUSICOTERAPIA</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I756" t="n">
+        <v>48</v>
+      </c>
+      <c r="J756" t="n">
+        <v>4</v>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr"/>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N756" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P756" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="Q756" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="R756" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S756" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T756" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U756" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V756" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INCCA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F757" t="n">
+        <v>119081</v>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN MUSICOTERAPIA</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I757" t="n">
+        <v>48</v>
+      </c>
+      <c r="J757" t="n">
+        <v>4</v>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr"/>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N757" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P757" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="Q757" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="R757" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S757" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T757" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U757" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V757" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F758" t="n">
+        <v>119089</v>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO LABORAL Y SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I758" t="n">
+        <v>28</v>
+      </c>
+      <c r="J758" t="n">
+        <v>2</v>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr"/>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N758" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P758" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q758" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R758" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S758" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T758" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U758" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V758" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F759" t="n">
+        <v>119059</v>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISEÑO Y GESTIÓN DE SOLUCIONES DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I759" t="n">
+        <v>24</v>
+      </c>
+      <c r="J759" t="n">
+        <v>2</v>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr"/>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N759" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="O759" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P759" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q759" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R759" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S759" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T759" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U759" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V759" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>1726</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE ORIENTE -UCO</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="F760" t="n">
+        <v>119070</v>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN BIG DATA Y ANALÍTICA</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I760" t="n">
+        <v>22</v>
+      </c>
+      <c r="J760" t="n">
+        <v>2</v>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr"/>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N760" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P760" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q760" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R760" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S760" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T760" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U760" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V760" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F761" t="n">
+        <v>119088</v>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DIDÁCTICA DE LAS LENGUAS EXTRANJERAS</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I761" t="n">
+        <v>40</v>
+      </c>
+      <c r="J761" t="n">
+        <v>3</v>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr"/>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N761" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O761" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P761" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q761" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R761" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S761" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T761" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U761" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V761" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE BOYACA UNIBOYACA</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F762" t="n">
+        <v>119060</v>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN INTEGRAL DEL RECURSO HÍDRICO</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I762" t="n">
+        <v>28</v>
+      </c>
+      <c r="J762" t="n">
+        <v>2</v>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr"/>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N762" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O762" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P762" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q762" t="inlineStr">
+        <is>
+          <t>Ingeniería y procesos químicos</t>
+        </is>
+      </c>
+      <c r="R762" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S762" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T762" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U762" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V762" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F763" t="n">
+        <v>118958</v>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN NEGOCIOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I763" t="n">
+        <v>40</v>
+      </c>
+      <c r="J763" t="n">
+        <v>4</v>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr"/>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N763" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="O763" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P763" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q763" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R763" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S763" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T763" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U763" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V763" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F764" t="n">
+        <v>119033</v>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN EXTENSIÓN E INNOVACIÓN RURAL</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I764" t="n">
+        <v>22</v>
+      </c>
+      <c r="J764" t="n">
+        <v>2</v>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr"/>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N764" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O764" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P764" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="Q764" t="inlineStr">
+        <is>
+          <t>Producción agrícola y ganadera</t>
+        </is>
+      </c>
+      <c r="R764" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S764" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T764" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U764" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V764" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATÓLICA LUIS AMIGÓ</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F765" t="n">
+        <v>119030</v>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN FINANZAS</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I765" t="n">
+        <v>25</v>
+      </c>
+      <c r="J765" t="n">
+        <v>2</v>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr"/>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N765" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O765" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P765" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q765" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R765" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S765" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T765" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U765" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V765" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>POLITECNICO GRANCOLOMBIANO</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F766" t="n">
+        <v>119071</v>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN NEUROPSICOLOGÍA ESCOLAR</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I766" t="n">
+        <v>25</v>
+      </c>
+      <c r="J766" t="n">
+        <v>2</v>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr"/>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N766" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O766" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P766" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q766" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R766" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S766" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T766" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U766" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V766" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CATOLICA DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Osos</t>
+        </is>
+      </c>
+      <c r="F767" t="n">
+        <v>119039</v>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN FENÓMENO RELIGIOSO, ÉTICA Y PAZ</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I767" t="n">
+        <v>26</v>
+      </c>
+      <c r="J767" t="n">
+        <v>2</v>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr"/>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N767" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P767" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q767" t="inlineStr">
+        <is>
+          <t>Religión y Teología</t>
+        </is>
+      </c>
+      <c r="R767" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S767" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T767" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U767" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V767" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAN</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F768" t="n">
+        <v>119065</v>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE LA BIOECONOMÍA Y GOBERNANZA BIOTECNOLÓGICA</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I768" t="n">
+        <v>43</v>
+      </c>
+      <c r="J768" t="n">
+        <v>3</v>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr"/>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N768" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O768" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P768" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="Q768" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="R768" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S768" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T768" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U768" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V768" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAN</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F769" t="n">
+        <v>119066</v>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE LA BIOECONOMÍA Y GOBERNANZA BIOTECNOLÓGICA</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I769" t="n">
+        <v>43</v>
+      </c>
+      <c r="J769" t="n">
+        <v>3</v>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr"/>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N769" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O769" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P769" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="Q769" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="R769" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S769" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T769" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U769" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V769" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL CARIBE - CECAR</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F770" t="n">
+        <v>119037</v>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN FAMILIAS Y CONSTRUCCIÓN DE PAZ</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I770" t="n">
+        <v>51</v>
+      </c>
+      <c r="J770" t="n">
+        <v>4</v>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr"/>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N770" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P770" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q770" t="inlineStr">
+        <is>
+          <t>Trabajo social</t>
+        </is>
+      </c>
+      <c r="R770" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S770" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T770" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U770" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V770" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL CARIBE - CECAR</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F771" t="n">
+        <v>119038</v>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN FAMILIAS Y CONSTRUCCIÓN DE PAZ</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I771" t="n">
+        <v>51</v>
+      </c>
+      <c r="J771" t="n">
+        <v>4</v>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr"/>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N771" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P771" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q771" t="inlineStr">
+        <is>
+          <t>Trabajo social</t>
+        </is>
+      </c>
+      <c r="R771" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S771" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T771" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U771" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V771" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA RAFAEL NUÑEZ</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F772" t="n">
+        <v>119078</v>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO ADMINISTRATIVO Y DE LA GESTIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I772" t="n">
+        <v>29</v>
+      </c>
+      <c r="J772" t="n">
+        <v>2</v>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr"/>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N772" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P772" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q772" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R772" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S772" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T772" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U772" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V772" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA RAFAEL NUÑEZ</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F773" t="n">
+        <v>119061</v>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I773" t="n">
+        <v>28</v>
+      </c>
+      <c r="J773" t="n">
+        <v>2</v>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr"/>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N773" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P773" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q773" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R773" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S773" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T773" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U773" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V773" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA RAFAEL NUÑEZ</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F774" t="n">
+        <v>119062</v>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORIA EN SERVICIOS DE SALUD</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I774" t="n">
+        <v>32</v>
+      </c>
+      <c r="J774" t="n">
+        <v>2</v>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr"/>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N774" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P774" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q774" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R774" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S774" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T774" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U774" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V774" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F775" t="n">
+        <v>119067</v>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN AMBIENTES DE APRENDIZAJE</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I775" t="n">
+        <v>44</v>
+      </c>
+      <c r="J775" t="n">
+        <v>4</v>
+      </c>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr"/>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N775" s="2" t="n">
+        <v>43812</v>
+      </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P775" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q775" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R775" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S775" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T775" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U775" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V775" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F776" t="n">
+        <v>119036</v>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN DE ENFERMERÍA EN CUIDADO CRITICO PARA EL ADULTO</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I776" t="n">
+        <v>26</v>
+      </c>
+      <c r="J776" t="n">
+        <v>2</v>
+      </c>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L776" t="inlineStr"/>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N776" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="O776" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P776" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q776" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R776" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S776" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T776" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U776" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V776" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F777" t="n">
+        <v>119072</v>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORÍA Y CONTROL</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I777" t="n">
+        <v>26</v>
+      </c>
+      <c r="J777" t="n">
+        <v>2</v>
+      </c>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L777" t="inlineStr"/>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="N777" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O777" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P777" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q777" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R777" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S777" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T777" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U777" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V777" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F778" t="n">
+        <v>119073</v>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORÍA Y CONTROL</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I778" t="n">
+        <v>26</v>
+      </c>
+      <c r="J778" t="n">
+        <v>2</v>
+      </c>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L778" t="inlineStr"/>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="N778" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O778" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P778" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q778" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R778" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S778" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T778" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U778" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V778" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>Apartadó</t>
+        </is>
+      </c>
+      <c r="F779" t="n">
+        <v>119055</v>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO LABORAL</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I779" t="n">
+        <v>26</v>
+      </c>
+      <c r="J779" t="n">
+        <v>2</v>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L779" t="inlineStr"/>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N779" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O779" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P779" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q779" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R779" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S779" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T779" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U779" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V779" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F780" t="n">
+        <v>119086</v>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN RESPONSABILIDAD CONTRACTUAL Y EXTRACONTRACTUAL DEL ESTADO</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I780" t="n">
+        <v>26</v>
+      </c>
+      <c r="J780" t="n">
+        <v>2</v>
+      </c>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L780" t="inlineStr"/>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>Bimensual</t>
+        </is>
+      </c>
+      <c r="N780" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O780" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P780" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q780" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R780" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S780" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T780" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U780" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V780" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA ANTONIO JOSE DE SUCRE - CORPOSUCRE</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F781" t="n">
+        <v>119045</v>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SEGURIDAD DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I781" t="n">
+        <v>26</v>
+      </c>
+      <c r="J781" t="n">
+        <v>2</v>
+      </c>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L781" t="inlineStr"/>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N781" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O781" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P781" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q781" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R781" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S781" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T781" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U781" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V781" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>3718</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>FUNDACION DE ESTUDIOS SUPERIORES COMFANORTE -F.E.S.C.-</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>San José de Cúcuta</t>
+        </is>
+      </c>
+      <c r="F782" t="n">
+        <v>119064</v>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I782" t="n">
+        <v>26</v>
+      </c>
+      <c r="J782" t="n">
+        <v>2</v>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L782" t="inlineStr"/>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N782" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="O782" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P782" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q782" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R782" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S782" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T782" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U782" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V782" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>CORPORACION TECNOLOGICA INDUSTRIAL COLOMBIANA - TEINCO</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F783" t="n">
+        <v>119080</v>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN EFICIENCIA ENERGÉTICA Y DESARROLLO SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I783" t="n">
+        <v>24</v>
+      </c>
+      <c r="J783" t="n">
+        <v>2</v>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr"/>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N783" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="O783" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P783" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q783" t="inlineStr">
+        <is>
+          <t>Electricidad y energía</t>
+        </is>
+      </c>
+      <c r="R783" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S783" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T783" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U783" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V783" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>CORPORACION TECNOLOGICA INDUSTRIAL COLOMBIANA - TEINCO</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F784" t="n">
+        <v>119079</v>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN EFICIENCIA ENERGÉTICA Y DESARROLLO SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I784" t="n">
+        <v>24</v>
+      </c>
+      <c r="J784" t="n">
+        <v>2</v>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr"/>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N784" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="O784" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P784" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q784" t="inlineStr">
+        <is>
+          <t>Electricidad y energía</t>
+        </is>
+      </c>
+      <c r="R784" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S784" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T784" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U784" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V784" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>3831</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA COMFACAUCA - UNICOMFACAUCA</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F785" t="n">
+        <v>118804</v>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GOBERNANZA Y CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I785" t="n">
+        <v>43</v>
+      </c>
+      <c r="J785" t="n">
+        <v>4</v>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr"/>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N785" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O785" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P785" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q785" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R785" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S785" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T785" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U785" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V785" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA SAN MATEO - SAN MATEO EDUCACION SUPERIOR</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F786" t="n">
+        <v>119090</v>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I786" t="n">
+        <v>28</v>
+      </c>
+      <c r="J786" t="n">
+        <v>2</v>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr"/>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N786" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O786" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P786" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q786" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R786" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S786" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T786" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U786" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V786" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F787" t="n">
+        <v>119032</v>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISEÑO Y DESARROLLO DE VIDEOJUEGOS</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I787" t="n">
+        <v>28</v>
+      </c>
+      <c r="J787" t="n">
+        <v>2</v>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr"/>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N787" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O787" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P787" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q787" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R787" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S787" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T787" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U787" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V787" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F788" t="n">
+        <v>119049</v>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I788" t="n">
+        <v>136</v>
+      </c>
+      <c r="J788" t="n">
+        <v>8</v>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L788" t="inlineStr"/>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N788" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O788" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P788" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q788" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R788" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S788" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T788" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U788" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V788" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F789" t="n">
+        <v>119047</v>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I789" t="n">
+        <v>136</v>
+      </c>
+      <c r="J789" t="n">
+        <v>8</v>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L789" t="inlineStr"/>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N789" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O789" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P789" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q789" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R789" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S789" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T789" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U789" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V789" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F790" t="n">
+        <v>119048</v>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I790" t="n">
+        <v>136</v>
+      </c>
+      <c r="J790" t="n">
+        <v>8</v>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr"/>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N790" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O790" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P790" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q790" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R790" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S790" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T790" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U790" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V790" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F791" t="n">
+        <v>119043</v>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I791" t="n">
+        <v>26</v>
+      </c>
+      <c r="J791" t="n">
+        <v>2</v>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L791" t="inlineStr"/>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N791" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="O791" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P791" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q791" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R791" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S791" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T791" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U791" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V791" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F792" t="n">
+        <v>119042</v>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I792" t="n">
+        <v>26</v>
+      </c>
+      <c r="J792" t="n">
+        <v>2</v>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr"/>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N792" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="O792" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P792" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q792" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R792" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S792" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T792" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U792" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V792" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F793" t="n">
+        <v>119044</v>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I793" t="n">
+        <v>26</v>
+      </c>
+      <c r="J793" t="n">
+        <v>2</v>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr"/>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N793" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="O793" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P793" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q793" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R793" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S793" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T793" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U793" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V793" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F794" t="n">
+        <v>119046</v>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I794" t="n">
+        <v>26</v>
+      </c>
+      <c r="J794" t="n">
+        <v>2</v>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr"/>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N794" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O794" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P794" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q794" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R794" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S794" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T794" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U794" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V794" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F795" t="n">
+        <v>119035</v>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I795" t="n">
+        <v>47</v>
+      </c>
+      <c r="J795" t="n">
+        <v>3</v>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr"/>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N795" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O795" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P795" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q795" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R795" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S795" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T795" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U795" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V795" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>9926</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA INTERNACIONAL DE LA RIOJA - UNIR</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F796" t="n">
+        <v>119040</v>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISEÑO GRÁFICO DIGITAL</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I796" t="n">
+        <v>24</v>
+      </c>
+      <c r="J796" t="n">
+        <v>2</v>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr"/>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N796" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O796" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P796" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q796" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R796" t="inlineStr">
+        <is>
+          <t>Artes plásticas, visuales y afines</t>
+        </is>
+      </c>
+      <c r="S796" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T796" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="U796" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V796" t="inlineStr">
+        <is>
+          <t>Música</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V796"/>
+  <dimension ref="A1:V837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74244,10 +74244,8 @@
       </c>
     </row>
     <row r="754">
-      <c r="A754" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
+      <c r="A754" t="n">
+        <v>1214</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
@@ -74299,7 +74297,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N754" s="2" t="n">
+      <c r="N754" s="1" t="n">
         <v>46079</v>
       </c>
       <c r="O754" t="inlineStr">
@@ -74344,10 +74342,8 @@
       </c>
     </row>
     <row r="755">
-      <c r="A755" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
+      <c r="A755" t="n">
+        <v>1703</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
@@ -74399,7 +74395,7 @@
           <t>Mensual</t>
         </is>
       </c>
-      <c r="N755" s="2" t="n">
+      <c r="N755" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O755" t="inlineStr">
@@ -74444,10 +74440,8 @@
       </c>
     </row>
     <row r="756">
-      <c r="A756" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
+      <c r="A756" t="n">
+        <v>1703</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
@@ -74499,7 +74493,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N756" s="2" t="n">
+      <c r="N756" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="O756" t="inlineStr">
@@ -74544,10 +74538,8 @@
       </c>
     </row>
     <row r="757">
-      <c r="A757" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
+      <c r="A757" t="n">
+        <v>1703</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
@@ -74599,7 +74591,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N757" s="2" t="n">
+      <c r="N757" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="O757" t="inlineStr">
@@ -74644,10 +74636,8 @@
       </c>
     </row>
     <row r="758">
-      <c r="A758" t="inlineStr">
-        <is>
-          <t>1709</t>
-        </is>
+      <c r="A758" t="n">
+        <v>1709</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
@@ -74699,7 +74689,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N758" s="2" t="n">
+      <c r="N758" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="O758" t="inlineStr">
@@ -74744,10 +74734,8 @@
       </c>
     </row>
     <row r="759">
-      <c r="A759" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A759" t="n">
+        <v>1711</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
@@ -74799,7 +74787,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N759" s="2" t="n">
+      <c r="N759" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="O759" t="inlineStr">
@@ -74844,10 +74832,8 @@
       </c>
     </row>
     <row r="760">
-      <c r="A760" t="inlineStr">
-        <is>
-          <t>1726</t>
-        </is>
+      <c r="A760" t="n">
+        <v>1726</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
@@ -74899,7 +74885,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N760" s="2" t="n">
+      <c r="N760" s="1" t="n">
         <v>46079</v>
       </c>
       <c r="O760" t="inlineStr">
@@ -74944,10 +74930,8 @@
       </c>
     </row>
     <row r="761">
-      <c r="A761" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
+      <c r="A761" t="n">
+        <v>1732</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
@@ -74999,7 +74983,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N761" s="2" t="n">
+      <c r="N761" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="O761" t="inlineStr">
@@ -75044,10 +75028,8 @@
       </c>
     </row>
     <row r="762">
-      <c r="A762" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
+      <c r="A762" t="n">
+        <v>1734</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
@@ -75099,7 +75081,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N762" s="2" t="n">
+      <c r="N762" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O762" t="inlineStr">
@@ -75144,10 +75126,8 @@
       </c>
     </row>
     <row r="763">
-      <c r="A763" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A763" t="n">
+        <v>1823</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
@@ -75199,7 +75179,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N763" s="2" t="n">
+      <c r="N763" s="1" t="n">
         <v>46126</v>
       </c>
       <c r="O763" t="inlineStr">
@@ -75244,10 +75224,8 @@
       </c>
     </row>
     <row r="764">
-      <c r="A764" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A764" t="n">
+        <v>2102</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
@@ -75299,7 +75277,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N764" s="2" t="n">
+      <c r="N764" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O764" t="inlineStr">
@@ -75344,10 +75322,8 @@
       </c>
     </row>
     <row r="765">
-      <c r="A765" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
+      <c r="A765" t="n">
+        <v>2719</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
@@ -75399,7 +75375,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N765" s="2" t="n">
+      <c r="N765" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O765" t="inlineStr">
@@ -75444,10 +75420,8 @@
       </c>
     </row>
     <row r="766">
-      <c r="A766" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
+      <c r="A766" t="n">
+        <v>2725</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
@@ -75499,7 +75473,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N766" s="2" t="n">
+      <c r="N766" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O766" t="inlineStr">
@@ -75544,10 +75518,8 @@
       </c>
     </row>
     <row r="767">
-      <c r="A767" t="inlineStr">
-        <is>
-          <t>2732</t>
-        </is>
+      <c r="A767" t="n">
+        <v>2732</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
@@ -75599,7 +75571,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N767" s="2" t="n">
+      <c r="N767" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="O767" t="inlineStr">
@@ -75644,10 +75616,8 @@
       </c>
     </row>
     <row r="768">
-      <c r="A768" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
+      <c r="A768" t="n">
+        <v>2812</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
@@ -75699,7 +75669,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N768" s="2" t="n">
+      <c r="N768" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="O768" t="inlineStr">
@@ -75744,10 +75714,8 @@
       </c>
     </row>
     <row r="769">
-      <c r="A769" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
+      <c r="A769" t="n">
+        <v>2812</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
@@ -75799,7 +75767,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N769" s="2" t="n">
+      <c r="N769" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="O769" t="inlineStr">
@@ -75844,10 +75812,8 @@
       </c>
     </row>
     <row r="770">
-      <c r="A770" t="inlineStr">
-        <is>
-          <t>2823</t>
-        </is>
+      <c r="A770" t="n">
+        <v>2823</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
@@ -75899,7 +75865,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N770" s="2" t="n">
+      <c r="N770" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="O770" t="inlineStr">
@@ -75944,10 +75910,8 @@
       </c>
     </row>
     <row r="771">
-      <c r="A771" t="inlineStr">
-        <is>
-          <t>2823</t>
-        </is>
+      <c r="A771" t="n">
+        <v>2823</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
@@ -75999,7 +75963,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N771" s="2" t="n">
+      <c r="N771" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="O771" t="inlineStr">
@@ -76044,10 +76008,8 @@
       </c>
     </row>
     <row r="772">
-      <c r="A772" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
+      <c r="A772" t="n">
+        <v>2825</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
@@ -76099,7 +76061,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N772" s="2" t="n">
+      <c r="N772" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O772" t="inlineStr">
@@ -76144,10 +76106,8 @@
       </c>
     </row>
     <row r="773">
-      <c r="A773" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
+      <c r="A773" t="n">
+        <v>2825</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
@@ -76199,7 +76159,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N773" s="2" t="n">
+      <c r="N773" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O773" t="inlineStr">
@@ -76244,10 +76204,8 @@
       </c>
     </row>
     <row r="774">
-      <c r="A774" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
+      <c r="A774" t="n">
+        <v>2825</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
@@ -76299,7 +76257,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N774" s="2" t="n">
+      <c r="N774" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O774" t="inlineStr">
@@ -76344,10 +76302,8 @@
       </c>
     </row>
     <row r="775">
-      <c r="A775" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A775" t="n">
+        <v>2829</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
@@ -76399,7 +76355,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N775" s="2" t="n">
+      <c r="N775" s="1" t="n">
         <v>43812</v>
       </c>
       <c r="O775" t="inlineStr">
@@ -76444,10 +76400,8 @@
       </c>
     </row>
     <row r="776">
-      <c r="A776" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A776" t="n">
+        <v>2832</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
@@ -76499,7 +76453,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N776" s="2" t="n">
+      <c r="N776" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="O776" t="inlineStr">
@@ -76544,10 +76498,8 @@
       </c>
     </row>
     <row r="777">
-      <c r="A777" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A777" t="n">
+        <v>2833</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
@@ -76599,7 +76551,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N777" s="2" t="n">
+      <c r="N777" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O777" t="inlineStr">
@@ -76644,10 +76596,8 @@
       </c>
     </row>
     <row r="778">
-      <c r="A778" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A778" t="n">
+        <v>2833</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
@@ -76699,7 +76649,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N778" s="2" t="n">
+      <c r="N778" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O778" t="inlineStr">
@@ -76744,10 +76694,8 @@
       </c>
     </row>
     <row r="779">
-      <c r="A779" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A779" t="n">
+        <v>2833</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
@@ -76799,7 +76747,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N779" s="2" t="n">
+      <c r="N779" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O779" t="inlineStr">
@@ -76844,10 +76792,8 @@
       </c>
     </row>
     <row r="780">
-      <c r="A780" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A780" t="n">
+        <v>2833</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
@@ -76899,7 +76845,7 @@
           <t>Bimensual</t>
         </is>
       </c>
-      <c r="N780" s="2" t="n">
+      <c r="N780" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="O780" t="inlineStr">
@@ -76944,10 +76890,8 @@
       </c>
     </row>
     <row r="781">
-      <c r="A781" t="inlineStr">
-        <is>
-          <t>2850</t>
-        </is>
+      <c r="A781" t="n">
+        <v>2850</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
@@ -76999,7 +76943,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N781" s="2" t="n">
+      <c r="N781" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O781" t="inlineStr">
@@ -77044,10 +76988,8 @@
       </c>
     </row>
     <row r="782">
-      <c r="A782" t="inlineStr">
-        <is>
-          <t>3718</t>
-        </is>
+      <c r="A782" t="n">
+        <v>3718</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
@@ -77099,7 +77041,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N782" s="2" t="n">
+      <c r="N782" s="1" t="n">
         <v>46105</v>
       </c>
       <c r="O782" t="inlineStr">
@@ -77144,10 +77086,8 @@
       </c>
     </row>
     <row r="783">
-      <c r="A783" t="inlineStr">
-        <is>
-          <t>3819</t>
-        </is>
+      <c r="A783" t="n">
+        <v>3819</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
@@ -77199,7 +77139,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N783" s="2" t="n">
+      <c r="N783" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="O783" t="inlineStr">
@@ -77244,10 +77184,8 @@
       </c>
     </row>
     <row r="784">
-      <c r="A784" t="inlineStr">
-        <is>
-          <t>3819</t>
-        </is>
+      <c r="A784" t="n">
+        <v>3819</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
@@ -77299,7 +77237,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N784" s="2" t="n">
+      <c r="N784" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="O784" t="inlineStr">
@@ -77344,10 +77282,8 @@
       </c>
     </row>
     <row r="785">
-      <c r="A785" t="inlineStr">
-        <is>
-          <t>3831</t>
-        </is>
+      <c r="A785" t="n">
+        <v>3831</v>
       </c>
       <c r="B785" t="inlineStr">
         <is>
@@ -77399,7 +77335,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N785" s="2" t="n">
+      <c r="N785" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O785" t="inlineStr">
@@ -77444,10 +77380,8 @@
       </c>
     </row>
     <row r="786">
-      <c r="A786" t="inlineStr">
-        <is>
-          <t>4726</t>
-        </is>
+      <c r="A786" t="n">
+        <v>4726</v>
       </c>
       <c r="B786" t="inlineStr">
         <is>
@@ -77499,7 +77433,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N786" s="2" t="n">
+      <c r="N786" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="O786" t="inlineStr">
@@ -77544,10 +77478,8 @@
       </c>
     </row>
     <row r="787">
-      <c r="A787" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A787" t="n">
+        <v>4813</v>
       </c>
       <c r="B787" t="inlineStr">
         <is>
@@ -77599,7 +77531,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N787" s="2" t="n">
+      <c r="N787" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O787" t="inlineStr">
@@ -77644,10 +77576,8 @@
       </c>
     </row>
     <row r="788">
-      <c r="A788" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A788" t="n">
+        <v>9119</v>
       </c>
       <c r="B788" t="inlineStr">
         <is>
@@ -77699,7 +77629,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N788" s="2" t="n">
+      <c r="N788" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="O788" t="inlineStr">
@@ -77744,10 +77674,8 @@
       </c>
     </row>
     <row r="789">
-      <c r="A789" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A789" t="n">
+        <v>9119</v>
       </c>
       <c r="B789" t="inlineStr">
         <is>
@@ -77799,7 +77727,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N789" s="2" t="n">
+      <c r="N789" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="O789" t="inlineStr">
@@ -77844,10 +77772,8 @@
       </c>
     </row>
     <row r="790">
-      <c r="A790" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A790" t="n">
+        <v>9119</v>
       </c>
       <c r="B790" t="inlineStr">
         <is>
@@ -77899,7 +77825,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N790" s="2" t="n">
+      <c r="N790" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="O790" t="inlineStr">
@@ -77944,10 +77870,8 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A791" t="n">
+        <v>9119</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
@@ -77999,7 +77923,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N791" s="2" t="n">
+      <c r="N791" s="1" t="n">
         <v>46092</v>
       </c>
       <c r="O791" t="inlineStr">
@@ -78044,10 +77968,8 @@
       </c>
     </row>
     <row r="792">
-      <c r="A792" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A792" t="n">
+        <v>9119</v>
       </c>
       <c r="B792" t="inlineStr">
         <is>
@@ -78099,7 +78021,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N792" s="2" t="n">
+      <c r="N792" s="1" t="n">
         <v>46092</v>
       </c>
       <c r="O792" t="inlineStr">
@@ -78144,10 +78066,8 @@
       </c>
     </row>
     <row r="793">
-      <c r="A793" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A793" t="n">
+        <v>9119</v>
       </c>
       <c r="B793" t="inlineStr">
         <is>
@@ -78199,7 +78119,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N793" s="2" t="n">
+      <c r="N793" s="1" t="n">
         <v>46092</v>
       </c>
       <c r="O793" t="inlineStr">
@@ -78244,10 +78164,8 @@
       </c>
     </row>
     <row r="794">
-      <c r="A794" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A794" t="n">
+        <v>9119</v>
       </c>
       <c r="B794" t="inlineStr">
         <is>
@@ -78299,7 +78217,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N794" s="2" t="n">
+      <c r="N794" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="O794" t="inlineStr">
@@ -78344,10 +78262,8 @@
       </c>
     </row>
     <row r="795">
-      <c r="A795" t="inlineStr">
-        <is>
-          <t>9913</t>
-        </is>
+      <c r="A795" t="n">
+        <v>9913</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
@@ -78399,7 +78315,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N795" s="2" t="n">
+      <c r="N795" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O795" t="inlineStr">
@@ -78444,10 +78360,8 @@
       </c>
     </row>
     <row r="796">
-      <c r="A796" t="inlineStr">
-        <is>
-          <t>9926</t>
-        </is>
+      <c r="A796" t="n">
+        <v>9926</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
@@ -78499,7 +78413,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N796" s="2" t="n">
+      <c r="N796" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="O796" t="inlineStr">
@@ -78540,6 +78454,4002 @@
       <c r="V796" t="inlineStr">
         <is>
           <t>Música</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD TECNOLOGICA DE PEREIRA - UTP</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F797" t="n">
+        <v>119146</v>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EDUCACIÓN PARA LAS CIENCIAS DE LA SALUD</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I797" t="n">
+        <v>50</v>
+      </c>
+      <c r="J797" t="n">
+        <v>4</v>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr"/>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N797" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O797" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P797" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q797" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R797" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S797" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T797" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U797" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V797" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F798" t="n">
+        <v>119155</v>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I798" t="n">
+        <v>100</v>
+      </c>
+      <c r="J798" t="n">
+        <v>8</v>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr"/>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N798" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O798" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P798" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q798" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R798" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S798" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T798" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U798" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V798" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F799" t="n">
+        <v>119162</v>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANÁLISIS DE DATOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I799" t="n">
+        <v>30</v>
+      </c>
+      <c r="J799" t="n">
+        <v>2</v>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr"/>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N799" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O799" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P799" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q799" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R799" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S799" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T799" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U799" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V799" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F800" t="n">
+        <v>119156</v>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I800" t="n">
+        <v>50</v>
+      </c>
+      <c r="J800" t="n">
+        <v>6</v>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr"/>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N800" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O800" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P800" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q800" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R800" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S800" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T800" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U800" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V800" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD-COLEGIO MAYOR DE CUNDINAMARCA</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F801" t="n">
+        <v>119148</v>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>MAESTRÍA DE ADMINISTRACIÓN DE NEGOCIOS (MBA)</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I801" t="n">
+        <v>42</v>
+      </c>
+      <c r="J801" t="n">
+        <v>3</v>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr"/>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N801" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O801" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P801" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q801" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R801" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S801" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T801" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U801" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V801" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD-COLEGIO MAYOR DE CUNDINAMARCA</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F802" t="n">
+        <v>119143</v>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DERECHO</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I802" t="n">
+        <v>42</v>
+      </c>
+      <c r="J802" t="n">
+        <v>3</v>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr"/>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N802" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O802" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P802" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q802" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R802" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S802" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T802" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U802" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V802" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL ATLANTICO</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Puerto Colombia</t>
+        </is>
+      </c>
+      <c r="F803" t="n">
+        <v>119164</v>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN TEORÍA DEL DELITO Y CASACIÓN PENAL</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I803" t="n">
+        <v>26</v>
+      </c>
+      <c r="J803" t="n">
+        <v>2</v>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr"/>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N803" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O803" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P803" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q803" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R803" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S803" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T803" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U803" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V803" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL ATLANTICO</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Puerto Colombia</t>
+        </is>
+      </c>
+      <c r="F804" t="n">
+        <v>119144</v>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EDUCACIÓN AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I804" t="n">
+        <v>48</v>
+      </c>
+      <c r="J804" t="n">
+        <v>4</v>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr"/>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N804" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O804" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P804" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q804" t="inlineStr">
+        <is>
+          <t>Educación no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R804" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S804" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T804" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U804" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V804" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL QUINDIO</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F805" t="n">
+        <v>119133</v>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GINECOLOGÍA Y OBSTETRICIA</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I805" t="n">
+        <v>180</v>
+      </c>
+      <c r="J805" t="n">
+        <v>3</v>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr"/>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N805" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O805" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P805" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q805" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R805" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S805" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T805" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U805" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V805" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL QUINDIO</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr"/>
+      <c r="E806" t="inlineStr"/>
+      <c r="F806" t="n">
+        <v>119111</v>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I806" t="n">
+        <v>40</v>
+      </c>
+      <c r="J806" t="n">
+        <v>4</v>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr"/>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N806" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O806" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P806" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q806" t="inlineStr">
+        <is>
+          <t>Bibliotecología, información y archivología</t>
+        </is>
+      </c>
+      <c r="R806" t="inlineStr">
+        <is>
+          <t>Bibliotecología, otros de ciencias sociales y humanas</t>
+        </is>
+      </c>
+      <c r="S806" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T806" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U806" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V806" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>1217</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SUCRE</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F807" t="n">
+        <v>119130</v>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISCAPACIDAD</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I807" t="n">
+        <v>28</v>
+      </c>
+      <c r="J807" t="n">
+        <v>2</v>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr"/>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N807" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="O807" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P807" t="inlineStr">
+        <is>
+          <t>Bienestar</t>
+        </is>
+      </c>
+      <c r="Q807" t="inlineStr">
+        <is>
+          <t>Bienestar no clasificado en otra parte</t>
+        </is>
+      </c>
+      <c r="R807" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S807" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T807" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U807" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V807" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr"/>
+      <c r="E808" t="inlineStr"/>
+      <c r="F808" t="n">
+        <v>119113</v>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO DEL TRABAJO Y GESTIÓN HUMANA</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I808" t="n">
+        <v>25</v>
+      </c>
+      <c r="J808" t="n">
+        <v>2</v>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr"/>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N808" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="O808" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P808" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q808" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R808" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S808" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T808" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U808" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V808" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F809" t="n">
+        <v>119132</v>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN RADIOLOGÍA ORAL Y MAXILOFACIAL</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I809" t="n">
+        <v>42</v>
+      </c>
+      <c r="J809" t="n">
+        <v>4</v>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr"/>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N809" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="O809" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P809" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q809" t="inlineStr">
+        <is>
+          <t>Odontología y estudios dentales</t>
+        </is>
+      </c>
+      <c r="R809" t="inlineStr">
+        <is>
+          <t>Odontología</t>
+        </is>
+      </c>
+      <c r="S809" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T809" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U809" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V809" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE BOGOTA - JORGE TADEO LOZANO</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F810" t="n">
+        <v>119168</v>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN SOSTENIBLE DEL AGUA</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I810" t="n">
+        <v>42</v>
+      </c>
+      <c r="J810" t="n">
+        <v>4</v>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr"/>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N810" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O810" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P810" t="inlineStr">
+        <is>
+          <t>Medio ambiente</t>
+        </is>
+      </c>
+      <c r="Q810" t="inlineStr">
+        <is>
+          <t>Ciencias del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R810" t="inlineStr">
+        <is>
+          <t>Geología, otros programas de ciencias naturales</t>
+        </is>
+      </c>
+      <c r="S810" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T810" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U810" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V810" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F811" t="n">
+        <v>119136</v>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN TERAPIA MANUAL ORTOPÉDICA</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I811" t="n">
+        <v>27</v>
+      </c>
+      <c r="J811" t="n">
+        <v>2</v>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr"/>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N811" s="2" t="n">
+        <v>45044</v>
+      </c>
+      <c r="O811" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P811" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q811" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R811" t="inlineStr">
+        <is>
+          <t>Terapias</t>
+        </is>
+      </c>
+      <c r="S811" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T811" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U811" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V811" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F812" t="n">
+        <v>119166</v>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN FORMACIÓN ÉTICA Y RELIGIOSA EN LA ERA DIGITAL</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I812" t="n">
+        <v>36</v>
+      </c>
+      <c r="J812" t="n">
+        <v>3</v>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr"/>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="N812" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O812" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P812" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q812" t="inlineStr">
+        <is>
+          <t>Formación para docentes con asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R812" t="inlineStr">
+        <is>
+          <t>Filosofía, teología y afines</t>
+        </is>
+      </c>
+      <c r="S812" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T812" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U812" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V812" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>COLEGIO MAYOR DE NUESTRA SEÑORA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F813" t="n">
+        <v>119151</v>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GENÉTICA MÉDICA</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I813" t="n">
+        <v>147</v>
+      </c>
+      <c r="J813" t="n">
+        <v>6</v>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr"/>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N813" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O813" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P813" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q813" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R813" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S813" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T813" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U813" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V813" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr"/>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="n">
+        <v>119106</v>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO CONSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I814" t="n">
+        <v>25</v>
+      </c>
+      <c r="J814" t="n">
+        <v>2</v>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr"/>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N814" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O814" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P814" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q814" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R814" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S814" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T814" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U814" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V814" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr"/>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="n">
+        <v>119110</v>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORIA Y GESTIÓN DE RIESGOS</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I815" t="n">
+        <v>25</v>
+      </c>
+      <c r="J815" t="n">
+        <v>2</v>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr"/>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N815" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O815" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P815" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q815" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R815" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S815" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T815" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U815" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V815" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD MANUELA BELTRAN-UMB-</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F816" t="n">
+        <v>118900</v>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN BIOESTADÍSTICA</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I816" t="n">
+        <v>53</v>
+      </c>
+      <c r="J816" t="n">
+        <v>4</v>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr"/>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N816" s="2" t="n">
+        <v>45309</v>
+      </c>
+      <c r="O816" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P816" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q816" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R816" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S816" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T816" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U816" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V816" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD MANUELA BELTRAN-UMB-</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F817" t="n">
+        <v>118899</v>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN TECNOLOGÍAS PARA EL MANEJO DE AGUAS Y RESIDUOS</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I817" t="n">
+        <v>53</v>
+      </c>
+      <c r="J817" t="n">
+        <v>4</v>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr"/>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N817" s="2" t="n">
+        <v>45362</v>
+      </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P817" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q817" t="inlineStr">
+        <is>
+          <t>Tecnología de protección del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R817" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S817" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T817" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U817" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V817" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>1807</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LIBRE</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F818" t="n">
+        <v>119165</v>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SALUD FAMILIAR Y COMUNITARIA</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I818" t="n">
+        <v>24</v>
+      </c>
+      <c r="J818" t="n">
+        <v>2</v>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr"/>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N818" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O818" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P818" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q818" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R818" t="inlineStr">
+        <is>
+          <t>Optometría, otros programas de ciencias de la salud</t>
+        </is>
+      </c>
+      <c r="S818" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T818" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U818" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V818" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>1807</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LIBRE</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F819" t="n">
+        <v>119167</v>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DERECHO DE FAMILIA</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I819" t="n">
+        <v>39</v>
+      </c>
+      <c r="J819" t="n">
+        <v>3</v>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr"/>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N819" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O819" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P819" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q819" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R819" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S819" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T819" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U819" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V819" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MEDELLIN</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr"/>
+      <c r="E820" t="inlineStr"/>
+      <c r="F820" t="n">
+        <v>119114</v>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISEÑO Y GESTIÓN DE CIUDADES INCLUSIVAS</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I820" t="n">
+        <v>24</v>
+      </c>
+      <c r="J820" t="n">
+        <v>2</v>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr"/>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N820" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="O820" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P820" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q820" t="inlineStr">
+        <is>
+          <t>Arquitectura y urbanismo</t>
+        </is>
+      </c>
+      <c r="R820" t="inlineStr">
+        <is>
+          <t>Arquitectura y afines</t>
+        </is>
+      </c>
+      <c r="S820" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T820" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U820" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V820" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F821" t="n">
+        <v>119131</v>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I821" t="n">
+        <v>24</v>
+      </c>
+      <c r="J821" t="n">
+        <v>1</v>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr"/>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N821" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="O821" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P821" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q821" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R821" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S821" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T821" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U821" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V821" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F822" t="n">
+        <v>119139</v>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN HIDROGEOLOGIA</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I822" t="n">
+        <v>25</v>
+      </c>
+      <c r="J822" t="n">
+        <v>4</v>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr"/>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N822" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O822" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P822" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="Q822" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="R822" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S822" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T822" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U822" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V822" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>UNIDAD CENTRAL DEL VALLE DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>Tuluá</t>
+        </is>
+      </c>
+      <c r="F823" t="n">
+        <v>119147</v>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN BILINGÜÍSMO Y EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I823" t="n">
+        <v>40</v>
+      </c>
+      <c r="J823" t="n">
+        <v>4</v>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr"/>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N823" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O823" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P823" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q823" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R823" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S823" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T823" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U823" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V823" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SIMÓN BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr"/>
+      <c r="E824" t="inlineStr"/>
+      <c r="F824" t="n">
+        <v>119112</v>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTELIGENCIA DE NEGOCIOS PARA LA TOMA DE DECISIONES</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I824" t="n">
+        <v>24</v>
+      </c>
+      <c r="J824" t="n">
+        <v>2</v>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr"/>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N824" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O824" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P824" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q824" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R824" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S824" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T824" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U824" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V824" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2847</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE INVESTIGACION Y DESARROLLO - UDI</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F825" t="n">
+        <v>119163</v>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN  GESTIÓN TECNOLOGÍA E INNOVACIÓN</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I825" t="n">
+        <v>89</v>
+      </c>
+      <c r="J825" t="n">
+        <v>8</v>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr"/>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N825" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O825" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P825" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q825" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R825" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S825" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T825" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U825" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V825" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA SAN MATEO - SAN MATEO EDUCACION SUPERIOR</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr"/>
+      <c r="E826" t="inlineStr"/>
+      <c r="F826" t="n">
+        <v>119108</v>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN HIGIENE, SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I826" t="n">
+        <v>32</v>
+      </c>
+      <c r="J826" t="n">
+        <v>2</v>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr"/>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N826" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O826" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P826" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q826" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R826" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S826" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T826" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U826" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V826" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F827" t="n">
+        <v>119153</v>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN MARKETING POLÍTICO</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I827" t="n">
+        <v>28</v>
+      </c>
+      <c r="J827" t="n">
+        <v>2</v>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr"/>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N827" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O827" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P827" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q827" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R827" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S827" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T827" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U827" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V827" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F828" t="n">
+        <v>119135</v>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CONTRATACIÓN ESTATAL</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I828" t="n">
+        <v>28</v>
+      </c>
+      <c r="J828" t="n">
+        <v>2</v>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr"/>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N828" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O828" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P828" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q828" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R828" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S828" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T828" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U828" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V828" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F829" t="n">
+        <v>119134</v>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CONTRATACIÓN ESTATAL</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I829" t="n">
+        <v>28</v>
+      </c>
+      <c r="J829" t="n">
+        <v>2</v>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr"/>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N829" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O829" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P829" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q829" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R829" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S829" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T829" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U829" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V829" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr"/>
+      <c r="E830" t="inlineStr"/>
+      <c r="F830" t="n">
+        <v>119120</v>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE LA SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I830" t="n">
+        <v>28</v>
+      </c>
+      <c r="J830" t="n">
+        <v>2</v>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr"/>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N830" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O830" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P830" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q830" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R830" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S830" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T830" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U830" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V830" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr"/>
+      <c r="E831" t="inlineStr"/>
+      <c r="F831" t="n">
+        <v>119118</v>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN PÚBLICA TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I831" t="n">
+        <v>28</v>
+      </c>
+      <c r="J831" t="n">
+        <v>2</v>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr"/>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N831" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O831" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P831" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q831" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R831" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S831" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T831" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U831" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V831" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr"/>
+      <c r="E832" t="inlineStr"/>
+      <c r="F832" t="n">
+        <v>119117</v>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN PÚBLICA TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I832" t="n">
+        <v>28</v>
+      </c>
+      <c r="J832" t="n">
+        <v>2</v>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr"/>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N832" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O832" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P832" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q832" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R832" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S832" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T832" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U832" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V832" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr"/>
+      <c r="E833" t="inlineStr"/>
+      <c r="F833" t="n">
+        <v>119115</v>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN RESPONSABILIDAD SOCIAL CORPORATIVA</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I833" t="n">
+        <v>25</v>
+      </c>
+      <c r="J833" t="n">
+        <v>2</v>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr"/>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N833" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O833" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P833" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q833" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R833" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S833" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T833" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U833" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V833" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr"/>
+      <c r="E834" t="inlineStr"/>
+      <c r="F834" t="n">
+        <v>119116</v>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN RESPONSABILIDAD SOCIAL CORPORATIVA</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I834" t="n">
+        <v>25</v>
+      </c>
+      <c r="J834" t="n">
+        <v>2</v>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr"/>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N834" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O834" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P834" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q834" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R834" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S834" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T834" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U834" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V834" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>9915</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA VIRTUAL INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F835" t="n">
+        <v>118878</v>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE LA SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I835" t="n">
+        <v>26</v>
+      </c>
+      <c r="J835" t="n">
+        <v>4</v>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr"/>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N835" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="O835" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P835" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q835" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R835" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S835" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T835" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U835" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V835" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>9915</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA VIRTUAL INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F836" t="n">
+        <v>118879</v>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I836" t="n">
+        <v>26</v>
+      </c>
+      <c r="J836" t="n">
+        <v>4</v>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr"/>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N836" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="O836" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P836" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q836" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R836" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S836" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T836" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U836" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V836" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>9926</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA INTERNACIONAL DE LA RIOJA - UNIR</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr"/>
+      <c r="E837" t="inlineStr"/>
+      <c r="F837" t="n">
+        <v>119107</v>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIENCIAS PENALES</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I837" t="n">
+        <v>24</v>
+      </c>
+      <c r="J837" t="n">
+        <v>2</v>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr"/>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N837" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O837" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P837" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q837" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R837" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S837" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T837" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="U837" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V837" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V837"/>
+  <dimension ref="A1:V902"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78458,10 +78458,8 @@
       </c>
     </row>
     <row r="797">
-      <c r="A797" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A797" t="n">
+        <v>1111</v>
       </c>
       <c r="B797" t="inlineStr">
         <is>
@@ -78513,7 +78511,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N797" s="2" t="n">
+      <c r="N797" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O797" t="inlineStr">
@@ -78558,10 +78556,8 @@
       </c>
     </row>
     <row r="798">
-      <c r="A798" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
+      <c r="A798" t="n">
+        <v>1112</v>
       </c>
       <c r="B798" t="inlineStr">
         <is>
@@ -78613,7 +78609,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N798" s="2" t="n">
+      <c r="N798" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O798" t="inlineStr">
@@ -78658,10 +78654,8 @@
       </c>
     </row>
     <row r="799">
-      <c r="A799" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
+      <c r="A799" t="n">
+        <v>1112</v>
       </c>
       <c r="B799" t="inlineStr">
         <is>
@@ -78713,7 +78707,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N799" s="2" t="n">
+      <c r="N799" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="O799" t="inlineStr">
@@ -78758,10 +78752,8 @@
       </c>
     </row>
     <row r="800">
-      <c r="A800" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
+      <c r="A800" t="n">
+        <v>1112</v>
       </c>
       <c r="B800" t="inlineStr">
         <is>
@@ -78813,7 +78805,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N800" s="2" t="n">
+      <c r="N800" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O800" t="inlineStr">
@@ -78858,10 +78850,8 @@
       </c>
     </row>
     <row r="801">
-      <c r="A801" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
+      <c r="A801" t="n">
+        <v>1121</v>
       </c>
       <c r="B801" t="inlineStr">
         <is>
@@ -78913,7 +78903,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N801" s="2" t="n">
+      <c r="N801" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O801" t="inlineStr">
@@ -78958,10 +78948,8 @@
       </c>
     </row>
     <row r="802">
-      <c r="A802" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
+      <c r="A802" t="n">
+        <v>1121</v>
       </c>
       <c r="B802" t="inlineStr">
         <is>
@@ -79013,7 +79001,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N802" s="2" t="n">
+      <c r="N802" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="O802" t="inlineStr">
@@ -79058,10 +79046,8 @@
       </c>
     </row>
     <row r="803">
-      <c r="A803" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
+      <c r="A803" t="n">
+        <v>1202</v>
       </c>
       <c r="B803" t="inlineStr">
         <is>
@@ -79113,7 +79099,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N803" s="2" t="n">
+      <c r="N803" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O803" t="inlineStr">
@@ -79158,10 +79144,8 @@
       </c>
     </row>
     <row r="804">
-      <c r="A804" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
+      <c r="A804" t="n">
+        <v>1202</v>
       </c>
       <c r="B804" t="inlineStr">
         <is>
@@ -79213,7 +79197,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N804" s="2" t="n">
+      <c r="N804" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="O804" t="inlineStr">
@@ -79258,10 +79242,8 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" t="inlineStr">
-        <is>
-          <t>1208</t>
-        </is>
+      <c r="A805" t="n">
+        <v>1208</v>
       </c>
       <c r="B805" t="inlineStr">
         <is>
@@ -79313,7 +79295,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N805" s="2" t="n">
+      <c r="N805" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O805" t="inlineStr">
@@ -79358,10 +79340,8 @@
       </c>
     </row>
     <row r="806">
-      <c r="A806" t="inlineStr">
-        <is>
-          <t>1208</t>
-        </is>
+      <c r="A806" t="n">
+        <v>1208</v>
       </c>
       <c r="B806" t="inlineStr">
         <is>
@@ -79405,7 +79385,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N806" s="2" t="n">
+      <c r="N806" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="O806" t="inlineStr">
@@ -79450,10 +79430,8 @@
       </c>
     </row>
     <row r="807">
-      <c r="A807" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
+      <c r="A807" t="n">
+        <v>1217</v>
       </c>
       <c r="B807" t="inlineStr">
         <is>
@@ -79505,7 +79483,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N807" s="2" t="n">
+      <c r="N807" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="O807" t="inlineStr">
@@ -79550,10 +79528,8 @@
       </c>
     </row>
     <row r="808">
-      <c r="A808" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="A808" t="n">
+        <v>1705</v>
       </c>
       <c r="B808" t="inlineStr">
         <is>
@@ -79597,7 +79573,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N808" s="2" t="n">
+      <c r="N808" s="1" t="n">
         <v>46132</v>
       </c>
       <c r="O808" t="inlineStr">
@@ -79642,10 +79618,8 @@
       </c>
     </row>
     <row r="809">
-      <c r="A809" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="A809" t="n">
+        <v>1705</v>
       </c>
       <c r="B809" t="inlineStr">
         <is>
@@ -79697,7 +79671,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N809" s="2" t="n">
+      <c r="N809" s="1" t="n">
         <v>46079</v>
       </c>
       <c r="O809" t="inlineStr">
@@ -79742,10 +79716,8 @@
       </c>
     </row>
     <row r="810">
-      <c r="A810" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
+      <c r="A810" t="n">
+        <v>1707</v>
       </c>
       <c r="B810" t="inlineStr">
         <is>
@@ -79797,7 +79769,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N810" s="2" t="n">
+      <c r="N810" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O810" t="inlineStr">
@@ -79842,10 +79814,8 @@
       </c>
     </row>
     <row r="811">
-      <c r="A811" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A811" t="n">
+        <v>1711</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
@@ -79897,7 +79867,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N811" s="2" t="n">
+      <c r="N811" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="O811" t="inlineStr">
@@ -79942,10 +79912,8 @@
       </c>
     </row>
     <row r="812">
-      <c r="A812" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A812" t="n">
+        <v>1711</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
@@ -79997,7 +79965,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N812" s="2" t="n">
+      <c r="N812" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O812" t="inlineStr">
@@ -80042,10 +80010,8 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A813" t="n">
+        <v>1714</v>
       </c>
       <c r="B813" t="inlineStr">
         <is>
@@ -80097,7 +80063,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N813" s="2" t="n">
+      <c r="N813" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O813" t="inlineStr">
@@ -80142,10 +80108,8 @@
       </c>
     </row>
     <row r="814">
-      <c r="A814" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A814" t="n">
+        <v>1716</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
@@ -80189,7 +80153,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N814" s="2" t="n">
+      <c r="N814" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="O814" t="inlineStr">
@@ -80234,10 +80198,8 @@
       </c>
     </row>
     <row r="815">
-      <c r="A815" t="inlineStr">
-        <is>
-          <t>1732</t>
-        </is>
+      <c r="A815" t="n">
+        <v>1732</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
@@ -80281,7 +80243,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N815" s="2" t="n">
+      <c r="N815" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="O815" t="inlineStr">
@@ -80326,10 +80288,8 @@
       </c>
     </row>
     <row r="816">
-      <c r="A816" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
+      <c r="A816" t="n">
+        <v>1735</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
@@ -80381,7 +80341,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N816" s="2" t="n">
+      <c r="N816" s="1" t="n">
         <v>45309</v>
       </c>
       <c r="O816" t="inlineStr">
@@ -80426,10 +80386,8 @@
       </c>
     </row>
     <row r="817">
-      <c r="A817" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
+      <c r="A817" t="n">
+        <v>1735</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
@@ -80481,7 +80439,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N817" s="2" t="n">
+      <c r="N817" s="1" t="n">
         <v>45362</v>
       </c>
       <c r="O817" t="inlineStr">
@@ -80526,10 +80484,8 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" t="inlineStr">
-        <is>
-          <t>1807</t>
-        </is>
+      <c r="A818" t="n">
+        <v>1807</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
@@ -80581,7 +80537,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N818" s="2" t="n">
+      <c r="N818" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O818" t="inlineStr">
@@ -80626,10 +80582,8 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" t="inlineStr">
-        <is>
-          <t>1807</t>
-        </is>
+      <c r="A819" t="n">
+        <v>1807</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
@@ -80681,7 +80635,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N819" s="2" t="n">
+      <c r="N819" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O819" t="inlineStr">
@@ -80726,10 +80680,8 @@
       </c>
     </row>
     <row r="820">
-      <c r="A820" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A820" t="n">
+        <v>1812</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
@@ -80773,7 +80725,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N820" s="2" t="n">
+      <c r="N820" s="1" t="n">
         <v>46132</v>
       </c>
       <c r="O820" t="inlineStr">
@@ -80818,10 +80770,8 @@
       </c>
     </row>
     <row r="821">
-      <c r="A821" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A821" t="n">
+        <v>1818</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
@@ -80873,7 +80823,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N821" s="2" t="n">
+      <c r="N821" s="1" t="n">
         <v>46071</v>
       </c>
       <c r="O821" t="inlineStr">
@@ -80918,10 +80868,8 @@
       </c>
     </row>
     <row r="822">
-      <c r="A822" t="inlineStr">
-        <is>
-          <t>1827</t>
-        </is>
+      <c r="A822" t="n">
+        <v>1827</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
@@ -80973,7 +80921,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N822" s="2" t="n">
+      <c r="N822" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="O822" t="inlineStr">
@@ -81018,10 +80966,8 @@
       </c>
     </row>
     <row r="823">
-      <c r="A823" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
+      <c r="A823" t="n">
+        <v>2301</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
@@ -81073,7 +81019,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N823" s="2" t="n">
+      <c r="N823" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O823" t="inlineStr">
@@ -81118,10 +81064,8 @@
       </c>
     </row>
     <row r="824">
-      <c r="A824" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A824" t="n">
+        <v>2805</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
@@ -81165,7 +81109,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N824" s="2" t="n">
+      <c r="N824" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="O824" t="inlineStr">
@@ -81210,10 +81154,8 @@
       </c>
     </row>
     <row r="825">
-      <c r="A825" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
+      <c r="A825" t="n">
+        <v>2847</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
@@ -81265,7 +81207,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N825" s="2" t="n">
+      <c r="N825" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O825" t="inlineStr">
@@ -81310,10 +81252,8 @@
       </c>
     </row>
     <row r="826">
-      <c r="A826" t="inlineStr">
-        <is>
-          <t>4726</t>
-        </is>
+      <c r="A826" t="n">
+        <v>4726</v>
       </c>
       <c r="B826" t="inlineStr">
         <is>
@@ -81357,7 +81297,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N826" s="2" t="n">
+      <c r="N826" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="O826" t="inlineStr">
@@ -81402,10 +81342,8 @@
       </c>
     </row>
     <row r="827">
-      <c r="A827" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A827" t="n">
+        <v>4813</v>
       </c>
       <c r="B827" t="inlineStr">
         <is>
@@ -81457,7 +81395,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N827" s="2" t="n">
+      <c r="N827" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O827" t="inlineStr">
@@ -81502,10 +81440,8 @@
       </c>
     </row>
     <row r="828">
-      <c r="A828" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A828" t="n">
+        <v>9119</v>
       </c>
       <c r="B828" t="inlineStr">
         <is>
@@ -81557,7 +81493,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N828" s="2" t="n">
+      <c r="N828" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O828" t="inlineStr">
@@ -81602,10 +81538,8 @@
       </c>
     </row>
     <row r="829">
-      <c r="A829" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A829" t="n">
+        <v>9119</v>
       </c>
       <c r="B829" t="inlineStr">
         <is>
@@ -81657,7 +81591,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N829" s="2" t="n">
+      <c r="N829" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O829" t="inlineStr">
@@ -81702,10 +81636,8 @@
       </c>
     </row>
     <row r="830">
-      <c r="A830" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A830" t="n">
+        <v>9119</v>
       </c>
       <c r="B830" t="inlineStr">
         <is>
@@ -81749,7 +81681,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N830" s="2" t="n">
+      <c r="N830" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O830" t="inlineStr">
@@ -81794,10 +81726,8 @@
       </c>
     </row>
     <row r="831">
-      <c r="A831" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A831" t="n">
+        <v>9119</v>
       </c>
       <c r="B831" t="inlineStr">
         <is>
@@ -81841,7 +81771,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N831" s="2" t="n">
+      <c r="N831" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="O831" t="inlineStr">
@@ -81886,10 +81816,8 @@
       </c>
     </row>
     <row r="832">
-      <c r="A832" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A832" t="n">
+        <v>9119</v>
       </c>
       <c r="B832" t="inlineStr">
         <is>
@@ -81933,7 +81861,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N832" s="2" t="n">
+      <c r="N832" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="O832" t="inlineStr">
@@ -81978,10 +81906,8 @@
       </c>
     </row>
     <row r="833">
-      <c r="A833" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A833" t="n">
+        <v>9119</v>
       </c>
       <c r="B833" t="inlineStr">
         <is>
@@ -82025,7 +81951,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N833" s="2" t="n">
+      <c r="N833" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="O833" t="inlineStr">
@@ -82070,10 +81996,8 @@
       </c>
     </row>
     <row r="834">
-      <c r="A834" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A834" t="n">
+        <v>9119</v>
       </c>
       <c r="B834" t="inlineStr">
         <is>
@@ -82117,7 +82041,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N834" s="2" t="n">
+      <c r="N834" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="O834" t="inlineStr">
@@ -82162,10 +82086,8 @@
       </c>
     </row>
     <row r="835">
-      <c r="A835" t="inlineStr">
-        <is>
-          <t>9915</t>
-        </is>
+      <c r="A835" t="n">
+        <v>9915</v>
       </c>
       <c r="B835" t="inlineStr">
         <is>
@@ -82217,7 +82139,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N835" s="2" t="n">
+      <c r="N835" s="1" t="n">
         <v>46036</v>
       </c>
       <c r="O835" t="inlineStr">
@@ -82262,10 +82184,8 @@
       </c>
     </row>
     <row r="836">
-      <c r="A836" t="inlineStr">
-        <is>
-          <t>9915</t>
-        </is>
+      <c r="A836" t="n">
+        <v>9915</v>
       </c>
       <c r="B836" t="inlineStr">
         <is>
@@ -82317,7 +82237,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N836" s="2" t="n">
+      <c r="N836" s="1" t="n">
         <v>46036</v>
       </c>
       <c r="O836" t="inlineStr">
@@ -82362,10 +82282,8 @@
       </c>
     </row>
     <row r="837">
-      <c r="A837" t="inlineStr">
-        <is>
-          <t>9926</t>
-        </is>
+      <c r="A837" t="n">
+        <v>9926</v>
       </c>
       <c r="B837" t="inlineStr">
         <is>
@@ -82409,7 +82327,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N837" s="2" t="n">
+      <c r="N837" s="1" t="n">
         <v>46125</v>
       </c>
       <c r="O837" t="inlineStr">
@@ -82450,6 +82368,6508 @@
       <c r="V837" t="inlineStr">
         <is>
           <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F838" t="n">
+        <v>119173</v>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CIENCIAS BIOLÓGICAS</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I838" t="n">
+        <v>54</v>
+      </c>
+      <c r="J838" t="n">
+        <v>4</v>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr"/>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N838" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O838" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P838" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines</t>
+        </is>
+      </c>
+      <c r="Q838" t="inlineStr">
+        <is>
+          <t>Biología</t>
+        </is>
+      </c>
+      <c r="R838" t="inlineStr">
+        <is>
+          <t>Biología, microbiología y afines</t>
+        </is>
+      </c>
+      <c r="S838" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T838" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U838" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V838" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD POPULAR DEL CESAR</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F839" t="n">
+        <v>119016</v>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN PEDAGOGÍA AMBIENTAL PARA EL DESARROLLO SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I839" t="n">
+        <v>48</v>
+      </c>
+      <c r="J839" t="n">
+        <v>4</v>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr"/>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N839" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="O839" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P839" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q839" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R839" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S839" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T839" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U839" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V839" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F840" t="n">
+        <v>119287</v>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN CULTURAL</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I840" t="n">
+        <v>55</v>
+      </c>
+      <c r="J840" t="n">
+        <v>4</v>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr"/>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N840" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O840" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P840" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q840" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R840" t="inlineStr">
+        <is>
+          <t>Bibliotecología, otros de ciencias sociales y humanas</t>
+        </is>
+      </c>
+      <c r="S840" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T840" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U840" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V840" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE NARIÑO</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F841" t="n">
+        <v>119203</v>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN TECNOLOGÍAS EMERGENTES PARA CIENCIAS AGRARIAS Y AMBIENTALES</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I841" t="n">
+        <v>28</v>
+      </c>
+      <c r="J841" t="n">
+        <v>1</v>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr"/>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N841" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O841" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P841" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="Q841" t="inlineStr">
+        <is>
+          <t>Producción agrícola y ganadera</t>
+        </is>
+      </c>
+      <c r="R841" t="inlineStr">
+        <is>
+          <t>Agronomía</t>
+        </is>
+      </c>
+      <c r="S841" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T841" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U841" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V841" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE PAMPLONA</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Pamplona</t>
+        </is>
+      </c>
+      <c r="F842" t="n">
+        <v>119183</v>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN CIENCIAS AMBIENTALES Y SOSTENIBILIDAD</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I842" t="n">
+        <v>90</v>
+      </c>
+      <c r="J842" t="n">
+        <v>8</v>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr"/>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N842" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O842" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P842" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="Q842" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="R842" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S842" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T842" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U842" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V842" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE PAMPLONA</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Pamplona</t>
+        </is>
+      </c>
+      <c r="F843" t="n">
+        <v>119181</v>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN SALUD MENTAL</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>Híbrida (A distancia-Virtual)</t>
+        </is>
+      </c>
+      <c r="I843" t="n">
+        <v>100</v>
+      </c>
+      <c r="J843" t="n">
+        <v>8</v>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr"/>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N843" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O843" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P843" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q843" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R843" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S843" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T843" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U843" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V843" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CUNDINAMARCA</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Fusagasugá</t>
+        </is>
+      </c>
+      <c r="F844" t="n">
+        <v>119085</v>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SEGURIDAD DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I844" t="n">
+        <v>20</v>
+      </c>
+      <c r="J844" t="n">
+        <v>2</v>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr"/>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N844" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O844" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P844" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q844" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R844" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S844" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T844" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U844" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V844" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>PONTIFICIA UNIVERSIDAD JAVERIANA</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F845" t="n">
+        <v>119204</v>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ASEGURAMIENTO Y COMPLIANCE CON ENFOQUE EN TECNOLOGÍAS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I845" t="n">
+        <v>36</v>
+      </c>
+      <c r="J845" t="n">
+        <v>3</v>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr"/>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N845" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O845" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P845" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q845" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R845" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S845" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T845" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U845" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V845" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>1702</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>PONTIFICIA UNIVERSIDAD JAVERIANA</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F846" t="n">
+        <v>119185</v>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN CIENCIAS ECONÓMICAS Y DE GESTIÓN</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I846" t="n">
+        <v>112</v>
+      </c>
+      <c r="J846" t="n">
+        <v>4</v>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr"/>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N846" s="2" t="n">
+        <v>45112</v>
+      </c>
+      <c r="O846" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P846" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q846" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R846" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S846" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T846" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U846" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V846" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>1702</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>PONTIFICIA UNIVERSIDAD JAVERIANA</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F847" t="n">
+        <v>119170</v>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISEÑO DE EXPERIENCIAS EXPOSITIVAS</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I847" t="n">
+        <v>23</v>
+      </c>
+      <c r="J847" t="n">
+        <v>2</v>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr"/>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N847" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O847" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P847" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q847" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R847" t="inlineStr">
+        <is>
+          <t>Artes plásticas, visuales y afines</t>
+        </is>
+      </c>
+      <c r="S847" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T847" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U847" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V847" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F848" t="n">
+        <v>119252</v>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIRUGÍA ORAL Y PATOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I848" t="n">
+        <v>112</v>
+      </c>
+      <c r="J848" t="n">
+        <v>4</v>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr"/>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N848" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O848" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P848" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q848" t="inlineStr">
+        <is>
+          <t>Odontología y estudios dentales</t>
+        </is>
+      </c>
+      <c r="R848" t="inlineStr">
+        <is>
+          <t>Odontología</t>
+        </is>
+      </c>
+      <c r="S848" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T848" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U848" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V848" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE BOGOTA - JORGE TADEO LOZANO</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F849" t="n">
+        <v>119233</v>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN CIENCIAS AMBIENTALES</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I849" t="n">
+        <v>42</v>
+      </c>
+      <c r="J849" t="n">
+        <v>4</v>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr"/>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N849" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O849" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P849" t="inlineStr">
+        <is>
+          <t>Medio ambiente</t>
+        </is>
+      </c>
+      <c r="Q849" t="inlineStr">
+        <is>
+          <t>Ciencias del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R849" t="inlineStr">
+        <is>
+          <t>Geología, otros programas de ciencias naturales</t>
+        </is>
+      </c>
+      <c r="S849" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T849" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U849" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V849" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F850" t="n">
+        <v>119269</v>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN LITERATURA</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I850" t="n">
+        <v>36</v>
+      </c>
+      <c r="J850" t="n">
+        <v>3</v>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr"/>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N850" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="O850" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P850" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="Q850" t="inlineStr">
+        <is>
+          <t>Literatura y lingüística</t>
+        </is>
+      </c>
+      <c r="R850" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S850" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T850" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U850" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V850" t="inlineStr">
+        <is>
+          <t>Instituto de Idiomas</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F851" t="n">
+        <v>119191</v>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN PSICOPEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I851" t="n">
+        <v>38</v>
+      </c>
+      <c r="J851" t="n">
+        <v>3</v>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr"/>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N851" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="O851" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P851" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q851" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R851" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S851" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T851" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U851" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V851" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F852" t="n">
+        <v>119275</v>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ADMINISTRACIÓN DE RIESGOS</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I852" t="n">
+        <v>27</v>
+      </c>
+      <c r="J852" t="n">
+        <v>2</v>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr"/>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N852" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O852" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P852" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q852" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R852" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S852" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T852" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U852" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V852" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="F853" t="n">
+        <v>119274</v>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ADMINISTRACIÓN DE RIESGOS</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I853" t="n">
+        <v>27</v>
+      </c>
+      <c r="J853" t="n">
+        <v>2</v>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr"/>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N853" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O853" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P853" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q853" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R853" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S853" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T853" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U853" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V853" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F854" t="n">
+        <v>119208</v>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AGILIDAD EMPRESARIAL</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I854" t="n">
+        <v>18</v>
+      </c>
+      <c r="J854" t="n">
+        <v>3</v>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr"/>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N854" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O854" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P854" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q854" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R854" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S854" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T854" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U854" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V854" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F855" t="n">
+        <v>119256</v>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ESTUDIOS DEL COMPORTAMIENTO</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I855" t="n">
+        <v>36</v>
+      </c>
+      <c r="J855" t="n">
+        <v>3</v>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr"/>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N855" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P855" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q855" t="inlineStr">
+        <is>
+          <t>Sociología, Antropología y estudios culturales</t>
+        </is>
+      </c>
+      <c r="R855" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S855" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T855" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U855" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V855" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>1726</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE ORIENTE -UCO</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="F856" t="n">
+        <v>119217</v>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ENTRENAMIENTO DEPORTIVO</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I856" t="n">
+        <v>22</v>
+      </c>
+      <c r="J856" t="n">
+        <v>2</v>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr"/>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N856" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="O856" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P856" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q856" t="inlineStr">
+        <is>
+          <t>Formación para docentes con asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R856" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S856" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T856" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U856" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V856" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F857" t="n">
+        <v>20781</v>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DOCENCIA DE LA EDUCACION SUPERIOR</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I857" t="n">
+        <v>24</v>
+      </c>
+      <c r="J857" t="n">
+        <v>2</v>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L857" t="n">
+        <v>7535000</v>
+      </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N857" s="2" t="n">
+        <v>44120</v>
+      </c>
+      <c r="O857" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P857" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q857" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R857" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S857" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T857" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U857" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V857" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD MANUELA BELTRAN-UMB-</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F858" t="n">
+        <v>119221</v>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN GESTION DE TECNOLOGIAS EN SALUD</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I858" t="n">
+        <v>45</v>
+      </c>
+      <c r="J858" t="n">
+        <v>4</v>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr"/>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N858" s="2" t="n">
+        <v>44687</v>
+      </c>
+      <c r="O858" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P858" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q858" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R858" t="inlineStr">
+        <is>
+          <t>Ingeniería biomédica y afines</t>
+        </is>
+      </c>
+      <c r="S858" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T858" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U858" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V858" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LA GRAN COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F859" t="n">
+        <v>119212</v>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CONSTRUCCIONES EFICIENTES</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I859" t="n">
+        <v>40</v>
+      </c>
+      <c r="J859" t="n">
+        <v>3</v>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr"/>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N859" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O859" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P859" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q859" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R859" t="inlineStr">
+        <is>
+          <t>Arquitectura y afines</t>
+        </is>
+      </c>
+      <c r="S859" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T859" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U859" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V859" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SALLE</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F860" t="n">
+        <v>119266</v>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INFRAESTRUCTURA HIDRÁULICA</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I860" t="n">
+        <v>26</v>
+      </c>
+      <c r="J860" t="n">
+        <v>2</v>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr"/>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N860" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="O860" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P860" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q860" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R860" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S860" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T860" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U860" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V860" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SALLE</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F861" t="n">
+        <v>119268</v>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INFRAESTRUCTURA VIAL</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I861" t="n">
+        <v>26</v>
+      </c>
+      <c r="J861" t="n">
+        <v>2</v>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr"/>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N861" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="O861" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P861" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q861" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R861" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S861" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T861" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U861" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V861" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>1814</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA LATINOAMERICANA-UNAULA-</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F862" t="n">
+        <v>119219</v>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN DERECHO PROBATORIO</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I862" t="n">
+        <v>42</v>
+      </c>
+      <c r="J862" t="n">
+        <v>3</v>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr"/>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N862" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O862" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P862" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q862" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R862" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S862" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T862" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U862" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V862" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>1824</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F863" t="n">
+        <v>119263</v>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DOCENCIA UNIVERSITARIA</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I863" t="n">
+        <v>25</v>
+      </c>
+      <c r="J863" t="n">
+        <v>2</v>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr"/>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N863" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O863" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P863" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q863" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R863" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S863" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T863" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U863" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V863" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2209</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>POLITECNICO COLOMBIANO JAIME ISAZA CADAVID</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F864" t="n">
+        <v>115821</v>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CONSTRUCCIÓN DE PAZ Y RECONCILIACIÓN</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I864" t="n">
+        <v>24</v>
+      </c>
+      <c r="J864" t="n">
+        <v>2</v>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr"/>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N864" s="2" t="n">
+        <v>45828</v>
+      </c>
+      <c r="O864" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P864" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q864" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R864" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S864" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T864" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U864" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V864" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2707</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA JUAN N. CORPAS</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F865" t="n">
+        <v>119253</v>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN SALUD FAMILIAR Y COMUNITARIA</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I865" t="n">
+        <v>46</v>
+      </c>
+      <c r="J865" t="n">
+        <v>3</v>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr"/>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N865" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O865" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P865" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q865" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R865" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S865" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T865" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U865" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V865" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA KONRAD LORENZ</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F866" t="n">
+        <v>119297</v>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANALÍTICA DE DATOS E INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I866" t="n">
+        <v>24</v>
+      </c>
+      <c r="J866" t="n">
+        <v>2</v>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr"/>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N866" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O866" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P866" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q866" t="inlineStr">
+        <is>
+          <t>Estadística</t>
+        </is>
+      </c>
+      <c r="R866" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S866" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T866" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U866" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V866" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2713</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA LOS LIBERTADORES</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F867" t="n">
+        <v>119196</v>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PSICOLOGÍA EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I867" t="n">
+        <v>24</v>
+      </c>
+      <c r="J867" t="n">
+        <v>4</v>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr"/>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N867" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O867" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P867" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q867" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R867" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S867" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T867" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U867" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V867" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA JUAN DE CASTELLANOS</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F868" t="n">
+        <v>119180</v>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN TÉCNICAS MÉDICO QUIRÚRGICAS EN CAMPO</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I868" t="n">
+        <v>24</v>
+      </c>
+      <c r="J868" t="n">
+        <v>2</v>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr"/>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N868" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O868" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P868" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="Q868" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="R868" t="inlineStr">
+        <is>
+          <t>Medicina veterinaria</t>
+        </is>
+      </c>
+      <c r="S868" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T868" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U868" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V868" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA MARIA CANO</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F869" t="n">
+        <v>119241</v>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CREACIÓN DE RECURSOS EDUCATIVOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I869" t="n">
+        <v>26</v>
+      </c>
+      <c r="J869" t="n">
+        <v>2</v>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr"/>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N869" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O869" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P869" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q869" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R869" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S869" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T869" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U869" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V869" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA MARIA CANO</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F870" t="n">
+        <v>119240</v>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISCAPACIDAD E INCLUSIÓN</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I870" t="n">
+        <v>27</v>
+      </c>
+      <c r="J870" t="n">
+        <v>2</v>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr"/>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N870" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O870" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P870" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q870" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R870" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S870" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T870" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U870" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V870" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2723</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA AGRARIA DE COLOMBIA -UNIAGRARIA-</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F871" t="n">
+        <v>119270</v>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>SALUD Y MANEJO DE FAUNA SILVESTRE</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I871" t="n">
+        <v>30</v>
+      </c>
+      <c r="J871" t="n">
+        <v>2</v>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr"/>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N871" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="O871" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P871" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="Q871" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="R871" t="inlineStr">
+        <is>
+          <t>Medicina veterinaria</t>
+        </is>
+      </c>
+      <c r="S871" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T871" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U871" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V871" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F872" t="n">
+        <v>119232</v>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INTELIGENCIA DE NEGOCIOS</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I872" t="n">
+        <v>45</v>
+      </c>
+      <c r="J872" t="n">
+        <v>3</v>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr"/>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N872" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="O872" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P872" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q872" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R872" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S872" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T872" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U872" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V872" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F873" t="n">
+        <v>119231</v>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>MAESTRÍA ECONOMÍA Y GESTIÓN DE LA SALUD</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I873" t="n">
+        <v>48</v>
+      </c>
+      <c r="J873" t="n">
+        <v>3</v>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr"/>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N873" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O873" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P873" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q873" t="inlineStr">
+        <is>
+          <t>Salud no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R873" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S873" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T873" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U873" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V873" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EIA</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F874" t="n">
+        <v>119216</v>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ANALÍTICA Y CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I874" t="n">
+        <v>45</v>
+      </c>
+      <c r="J874" t="n">
+        <v>3</v>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr"/>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N874" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="O874" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P874" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q874" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R874" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S874" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T874" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U874" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V874" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EIA</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F875" t="n">
+        <v>119229</v>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CIUDADES INTELIGENTES</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I875" t="n">
+        <v>40</v>
+      </c>
+      <c r="J875" t="n">
+        <v>3</v>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr"/>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N875" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O875" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P875" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q875" t="inlineStr">
+        <is>
+          <t>Arquitectura y urbanismo</t>
+        </is>
+      </c>
+      <c r="R875" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S875" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T875" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U875" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V875" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA RAFAEL NUÑEZ</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F876" t="n">
+        <v>119278</v>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I876" t="n">
+        <v>27</v>
+      </c>
+      <c r="J876" t="n">
+        <v>2</v>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr"/>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N876" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O876" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P876" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q876" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R876" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S876" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T876" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U876" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V876" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F877" t="n">
+        <v>119234</v>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE MARCA</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I877" t="n">
+        <v>24</v>
+      </c>
+      <c r="J877" t="n">
+        <v>2</v>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr"/>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N877" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O877" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P877" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q877" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R877" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S877" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T877" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U877" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V877" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F878" t="n">
+        <v>119235</v>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE MARCA</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I878" t="n">
+        <v>24</v>
+      </c>
+      <c r="J878" t="n">
+        <v>2</v>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr"/>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N878" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O878" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P878" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q878" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R878" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S878" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T878" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U878" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V878" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2830</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA IBEROAMERICANA</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F879" t="n">
+        <v>119272</v>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I879" t="n">
+        <v>84</v>
+      </c>
+      <c r="J879" t="n">
+        <v>6</v>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr"/>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N879" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O879" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P879" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q879" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R879" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S879" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T879" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U879" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V879" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2830</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA IBEROAMERICANA</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F880" t="n">
+        <v>119276</v>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I880" t="n">
+        <v>24</v>
+      </c>
+      <c r="J880" t="n">
+        <v>2</v>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr"/>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N880" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O880" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P880" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q880" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R880" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S880" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T880" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U880" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V880" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F881" t="n">
+        <v>119220</v>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN BIOÉTICA</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I881" t="n">
+        <v>39</v>
+      </c>
+      <c r="J881" t="n">
+        <v>3</v>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr"/>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N881" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O881" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P881" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q881" t="inlineStr">
+        <is>
+          <t>Filosofía y ética</t>
+        </is>
+      </c>
+      <c r="R881" t="inlineStr">
+        <is>
+          <t>Filosofía, teología y afines</t>
+        </is>
+      </c>
+      <c r="S881" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T881" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U881" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V881" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F882" t="n">
+        <v>119189</v>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE TECNOLOGÍAS DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I882" t="n">
+        <v>42</v>
+      </c>
+      <c r="J882" t="n">
+        <v>3</v>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr"/>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N882" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O882" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P882" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q882" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R882" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S882" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T882" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U882" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V882" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F883" t="n">
+        <v>119190</v>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE TECNOLOGÍAS DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I883" t="n">
+        <v>42</v>
+      </c>
+      <c r="J883" t="n">
+        <v>3</v>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr"/>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N883" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O883" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P883" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q883" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R883" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S883" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T883" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U883" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V883" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2847</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE INVESTIGACION Y DESARROLLO - UDI</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F884" t="n">
+        <v>119198</v>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I884" t="n">
+        <v>52</v>
+      </c>
+      <c r="J884" t="n">
+        <v>4</v>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr"/>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N884" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O884" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P884" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q884" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R884" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S884" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T884" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U884" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V884" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>ESCUELA NAVAL DE SUBOFICIALES ARC BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F885" t="n">
+        <v>115882</v>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN TECNOLÓGICA EN GESTIÓN DEL TALENTO HUMANO Y LIDERAZGO</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I885" t="n">
+        <v>21</v>
+      </c>
+      <c r="J885" t="n">
+        <v>1</v>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr"/>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N885" s="2" t="n">
+        <v>45306</v>
+      </c>
+      <c r="O885" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P885" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q885" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R885" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S885" t="inlineStr">
+        <is>
+          <t>Especialización tecnológica</t>
+        </is>
+      </c>
+      <c r="T885" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U885" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V885" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>3720</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA ESUMER</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F886" t="n">
+        <v>119192</v>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I886" t="n">
+        <v>46</v>
+      </c>
+      <c r="J886" t="n">
+        <v>4</v>
+      </c>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr"/>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N886" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O886" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P886" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q886" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R886" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S886" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T886" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U886" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V886" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>4818</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA LATINOAMERICANA - CUL</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F887" t="n">
+        <v>119210</v>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I887" t="n">
+        <v>20</v>
+      </c>
+      <c r="J887" t="n">
+        <v>2</v>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr"/>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N887" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O887" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P887" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q887" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R887" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S887" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T887" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U887" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V887" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>4818</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA LATINOAMERICANA - CUL</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F888" t="n">
+        <v>119209</v>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I888" t="n">
+        <v>20</v>
+      </c>
+      <c r="J888" t="n">
+        <v>2</v>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr"/>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N888" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O888" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P888" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q888" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R888" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S888" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T888" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U888" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V888" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>4818</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA LATINOAMERICANA - CUL</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F889" t="n">
+        <v>119206</v>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA FINANCIERA Y NEGOCIOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I889" t="n">
+        <v>22</v>
+      </c>
+      <c r="J889" t="n">
+        <v>2</v>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L889" t="inlineStr"/>
+      <c r="M889" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N889" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O889" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P889" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q889" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R889" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S889" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T889" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U889" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V889" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>4818</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA LATINOAMERICANA - CUL</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F890" t="n">
+        <v>119207</v>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA FINANCIERA Y NEGOCIOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I890" t="n">
+        <v>22</v>
+      </c>
+      <c r="J890" t="n">
+        <v>2</v>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr"/>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N890" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O890" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P890" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q890" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R890" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S890" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T890" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U890" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V890" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F891" t="n">
+        <v>119199</v>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CRISIS, CONFLICTO Y SALUD MENTAL EN LA ADOLESCENCIA</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I891" t="n">
+        <v>28</v>
+      </c>
+      <c r="J891" t="n">
+        <v>2</v>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr"/>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N891" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O891" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P891" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q891" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R891" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S891" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T891" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U891" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V891" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F892" t="n">
+        <v>119200</v>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CRISIS, CONFLICTO Y SALUD MENTAL EN LA ADOLESCENCIA</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I892" t="n">
+        <v>28</v>
+      </c>
+      <c r="J892" t="n">
+        <v>2</v>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr"/>
+      <c r="M892" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N892" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O892" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P892" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q892" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R892" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S892" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T892" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U892" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V892" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F893" t="n">
+        <v>119205</v>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I893" t="n">
+        <v>26</v>
+      </c>
+      <c r="J893" t="n">
+        <v>2</v>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr"/>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N893" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O893" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P893" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q893" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R893" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S893" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T893" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U893" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V893" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>9127</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE SABANETA - UNISABANETA</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="F894" t="n">
+        <v>119254</v>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I894" t="n">
+        <v>24</v>
+      </c>
+      <c r="J894" t="n">
+        <v>2</v>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr"/>
+      <c r="M894" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N894" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O894" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P894" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q894" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R894" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S894" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T894" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U894" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V894" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>9127</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE SABANETA - UNISABANETA</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="F895" t="n">
+        <v>119255</v>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I895" t="n">
+        <v>24</v>
+      </c>
+      <c r="J895" t="n">
+        <v>2</v>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr"/>
+      <c r="M895" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N895" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O895" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P895" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q895" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R895" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S895" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T895" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U895" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V895" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>9900</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA U DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F896" t="n">
+        <v>119223</v>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTELIGENCIA ARTIFICIAL APLICADA</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I896" t="n">
+        <v>28</v>
+      </c>
+      <c r="J896" t="n">
+        <v>2</v>
+      </c>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr"/>
+      <c r="M896" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N896" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="O896" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P896" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q896" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R896" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S896" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T896" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U896" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V896" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F897" t="n">
+        <v>119202</v>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL Y PROBATORIO</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I897" t="n">
+        <v>24</v>
+      </c>
+      <c r="J897" t="n">
+        <v>2</v>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr"/>
+      <c r="M897" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N897" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O897" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P897" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q897" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R897" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S897" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T897" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U897" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V897" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>9926</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA INTERNACIONAL DE LA RIOJA - UNIR</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F898" t="n">
+        <v>119251</v>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORÍA EN SALUD</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I898" t="n">
+        <v>24</v>
+      </c>
+      <c r="J898" t="n">
+        <v>2</v>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr"/>
+      <c r="M898" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N898" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O898" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P898" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q898" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R898" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S898" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T898" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U898" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V898" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>9926</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA INTERNACIONAL DE LA RIOJA - UNIR</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F899" t="n">
+        <v>119187</v>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTERVENCIÓN SOCIAL</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I899" t="n">
+        <v>24</v>
+      </c>
+      <c r="J899" t="n">
+        <v>2</v>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr"/>
+      <c r="M899" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N899" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O899" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P899" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q899" t="inlineStr">
+        <is>
+          <t>Trabajo social</t>
+        </is>
+      </c>
+      <c r="R899" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S899" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T899" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U899" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V899" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>9928</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA SALESIANA</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F900" t="n">
+        <v>119249</v>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISEÑO Y GESTIÓN DE AMBIENTES EDUCATIVOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I900" t="n">
+        <v>28</v>
+      </c>
+      <c r="J900" t="n">
+        <v>1</v>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr"/>
+      <c r="M900" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N900" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O900" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P900" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q900" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R900" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S900" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T900" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U900" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V900" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>9928</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA SALESIANA</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F901" t="n">
+        <v>119250</v>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISEÑO Y GESTIÓN DE AMBIENTES EDUCATIVOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I901" t="n">
+        <v>28</v>
+      </c>
+      <c r="J901" t="n">
+        <v>1</v>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr"/>
+      <c r="M901" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N901" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O901" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P901" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q901" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R901" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S901" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T901" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U901" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V901" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>9928</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA SALESIANA</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F902" t="n">
+        <v>119248</v>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DISEÑO Y GESTIÓN DE AMBIENTES EDUCATIVOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I902" t="n">
+        <v>28</v>
+      </c>
+      <c r="J902" t="n">
+        <v>1</v>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L902" t="inlineStr"/>
+      <c r="M902" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N902" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O902" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P902" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q902" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R902" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S902" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T902" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="U902" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V902" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Nuevos_posgrado.xlsx
+++ b/data/novedades/Nuevos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V902"/>
+  <dimension ref="A1:V966"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82372,10 +82372,8 @@
       </c>
     </row>
     <row r="838">
-      <c r="A838" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
+      <c r="A838" t="n">
+        <v>1112</v>
       </c>
       <c r="B838" t="inlineStr">
         <is>
@@ -82427,7 +82425,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N838" s="2" t="n">
+      <c r="N838" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O838" t="inlineStr">
@@ -82472,10 +82470,8 @@
       </c>
     </row>
     <row r="839">
-      <c r="A839" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
+      <c r="A839" t="n">
+        <v>1120</v>
       </c>
       <c r="B839" t="inlineStr">
         <is>
@@ -82527,7 +82523,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N839" s="2" t="n">
+      <c r="N839" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="O839" t="inlineStr">
@@ -82572,10 +82568,8 @@
       </c>
     </row>
     <row r="840">
-      <c r="A840" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
+      <c r="A840" t="n">
+        <v>1201</v>
       </c>
       <c r="B840" t="inlineStr">
         <is>
@@ -82627,7 +82621,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N840" s="2" t="n">
+      <c r="N840" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O840" t="inlineStr">
@@ -82672,10 +82666,8 @@
       </c>
     </row>
     <row r="841">
-      <c r="A841" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
+      <c r="A841" t="n">
+        <v>1206</v>
       </c>
       <c r="B841" t="inlineStr">
         <is>
@@ -82727,7 +82719,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N841" s="2" t="n">
+      <c r="N841" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O841" t="inlineStr">
@@ -82772,10 +82764,8 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
+      <c r="A842" t="n">
+        <v>1212</v>
       </c>
       <c r="B842" t="inlineStr">
         <is>
@@ -82827,7 +82817,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N842" s="2" t="n">
+      <c r="N842" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="O842" t="inlineStr">
@@ -82872,10 +82862,8 @@
       </c>
     </row>
     <row r="843">
-      <c r="A843" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
+      <c r="A843" t="n">
+        <v>1212</v>
       </c>
       <c r="B843" t="inlineStr">
         <is>
@@ -82927,7 +82915,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N843" s="2" t="n">
+      <c r="N843" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="O843" t="inlineStr">
@@ -82972,10 +82960,8 @@
       </c>
     </row>
     <row r="844">
-      <c r="A844" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
+      <c r="A844" t="n">
+        <v>1214</v>
       </c>
       <c r="B844" t="inlineStr">
         <is>
@@ -83027,7 +83013,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N844" s="2" t="n">
+      <c r="N844" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="O844" t="inlineStr">
@@ -83072,10 +83058,8 @@
       </c>
     </row>
     <row r="845">
-      <c r="A845" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A845" t="n">
+        <v>1701</v>
       </c>
       <c r="B845" t="inlineStr">
         <is>
@@ -83127,7 +83111,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N845" s="2" t="n">
+      <c r="N845" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O845" t="inlineStr">
@@ -83172,10 +83156,8 @@
       </c>
     </row>
     <row r="846">
-      <c r="A846" t="inlineStr">
-        <is>
-          <t>1702</t>
-        </is>
+      <c r="A846" t="n">
+        <v>1702</v>
       </c>
       <c r="B846" t="inlineStr">
         <is>
@@ -83227,7 +83209,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N846" s="2" t="n">
+      <c r="N846" s="1" t="n">
         <v>45112</v>
       </c>
       <c r="O846" t="inlineStr">
@@ -83272,10 +83254,8 @@
       </c>
     </row>
     <row r="847">
-      <c r="A847" t="inlineStr">
-        <is>
-          <t>1702</t>
-        </is>
+      <c r="A847" t="n">
+        <v>1702</v>
       </c>
       <c r="B847" t="inlineStr">
         <is>
@@ -83327,7 +83307,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N847" s="2" t="n">
+      <c r="N847" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O847" t="inlineStr">
@@ -83372,10 +83352,8 @@
       </c>
     </row>
     <row r="848">
-      <c r="A848" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
+      <c r="A848" t="n">
+        <v>1705</v>
       </c>
       <c r="B848" t="inlineStr">
         <is>
@@ -83427,7 +83405,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N848" s="2" t="n">
+      <c r="N848" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O848" t="inlineStr">
@@ -83472,10 +83450,8 @@
       </c>
     </row>
     <row r="849">
-      <c r="A849" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
+      <c r="A849" t="n">
+        <v>1707</v>
       </c>
       <c r="B849" t="inlineStr">
         <is>
@@ -83527,7 +83503,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N849" s="2" t="n">
+      <c r="N849" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O849" t="inlineStr">
@@ -83572,10 +83548,8 @@
       </c>
     </row>
     <row r="850">
-      <c r="A850" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A850" t="n">
+        <v>1710</v>
       </c>
       <c r="B850" t="inlineStr">
         <is>
@@ -83627,7 +83601,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N850" s="2" t="n">
+      <c r="N850" s="1" t="n">
         <v>46218</v>
       </c>
       <c r="O850" t="inlineStr">
@@ -83672,10 +83646,8 @@
       </c>
     </row>
     <row r="851">
-      <c r="A851" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A851" t="n">
+        <v>1710</v>
       </c>
       <c r="B851" t="inlineStr">
         <is>
@@ -83727,7 +83699,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N851" s="2" t="n">
+      <c r="N851" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="O851" t="inlineStr">
@@ -83772,10 +83744,8 @@
       </c>
     </row>
     <row r="852">
-      <c r="A852" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A852" t="n">
+        <v>1712</v>
       </c>
       <c r="B852" t="inlineStr">
         <is>
@@ -83827,7 +83797,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N852" s="2" t="n">
+      <c r="N852" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="O852" t="inlineStr">
@@ -83872,10 +83842,8 @@
       </c>
     </row>
     <row r="853">
-      <c r="A853" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A853" t="n">
+        <v>1712</v>
       </c>
       <c r="B853" t="inlineStr">
         <is>
@@ -83927,7 +83895,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N853" s="2" t="n">
+      <c r="N853" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="O853" t="inlineStr">
@@ -83972,10 +83940,8 @@
       </c>
     </row>
     <row r="854">
-      <c r="A854" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A854" t="n">
+        <v>1712</v>
       </c>
       <c r="B854" t="inlineStr">
         <is>
@@ -84027,7 +83993,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N854" s="2" t="n">
+      <c r="N854" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O854" t="inlineStr">
@@ -84072,10 +84038,8 @@
       </c>
     </row>
     <row r="855">
-      <c r="A855" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
+      <c r="A855" t="n">
+        <v>1712</v>
       </c>
       <c r="B855" t="inlineStr">
         <is>
@@ -84127,7 +84091,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N855" s="2" t="n">
+      <c r="N855" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O855" t="inlineStr">
@@ -84172,10 +84136,8 @@
       </c>
     </row>
     <row r="856">
-      <c r="A856" t="inlineStr">
-        <is>
-          <t>1726</t>
-        </is>
+      <c r="A856" t="n">
+        <v>1726</v>
       </c>
       <c r="B856" t="inlineStr">
         <is>
@@ -84227,7 +84189,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N856" s="2" t="n">
+      <c r="N856" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="O856" t="inlineStr">
@@ -84272,10 +84234,8 @@
       </c>
     </row>
     <row r="857">
-      <c r="A857" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A857" t="n">
+        <v>1729</v>
       </c>
       <c r="B857" t="inlineStr">
         <is>
@@ -84329,7 +84289,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N857" s="2" t="n">
+      <c r="N857" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="O857" t="inlineStr">
@@ -84374,10 +84334,8 @@
       </c>
     </row>
     <row r="858">
-      <c r="A858" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
+      <c r="A858" t="n">
+        <v>1735</v>
       </c>
       <c r="B858" t="inlineStr">
         <is>
@@ -84429,7 +84387,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N858" s="2" t="n">
+      <c r="N858" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="O858" t="inlineStr">
@@ -84474,10 +84432,8 @@
       </c>
     </row>
     <row r="859">
-      <c r="A859" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
+      <c r="A859" t="n">
+        <v>1802</v>
       </c>
       <c r="B859" t="inlineStr">
         <is>
@@ -84529,7 +84485,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N859" s="2" t="n">
+      <c r="N859" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O859" t="inlineStr">
@@ -84574,10 +84530,8 @@
       </c>
     </row>
     <row r="860">
-      <c r="A860" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="A860" t="n">
+        <v>1803</v>
       </c>
       <c r="B860" t="inlineStr">
         <is>
@@ -84629,7 +84583,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N860" s="2" t="n">
+      <c r="N860" s="1" t="n">
         <v>46218</v>
       </c>
       <c r="O860" t="inlineStr">
@@ -84674,10 +84628,8 @@
       </c>
     </row>
     <row r="861">
-      <c r="A861" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="A861" t="n">
+        <v>1803</v>
       </c>
       <c r="B861" t="inlineStr">
         <is>
@@ -84729,7 +84681,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N861" s="2" t="n">
+      <c r="N861" s="1" t="n">
         <v>46218</v>
       </c>
       <c r="O861" t="inlineStr">
@@ -84774,10 +84726,8 @@
       </c>
     </row>
     <row r="862">
-      <c r="A862" t="inlineStr">
-        <is>
-          <t>1814</t>
-        </is>
+      <c r="A862" t="n">
+        <v>1814</v>
       </c>
       <c r="B862" t="inlineStr">
         <is>
@@ -84829,7 +84779,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N862" s="2" t="n">
+      <c r="N862" s="1" t="n">
         <v>46168</v>
       </c>
       <c r="O862" t="inlineStr">
@@ -84874,10 +84824,8 @@
       </c>
     </row>
     <row r="863">
-      <c r="A863" t="inlineStr">
-        <is>
-          <t>1824</t>
-        </is>
+      <c r="A863" t="n">
+        <v>1824</v>
       </c>
       <c r="B863" t="inlineStr">
         <is>
@@ -84929,7 +84877,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N863" s="2" t="n">
+      <c r="N863" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O863" t="inlineStr">
@@ -84974,10 +84922,8 @@
       </c>
     </row>
     <row r="864">
-      <c r="A864" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
+      <c r="A864" t="n">
+        <v>2209</v>
       </c>
       <c r="B864" t="inlineStr">
         <is>
@@ -85029,7 +84975,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N864" s="2" t="n">
+      <c r="N864" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="O864" t="inlineStr">
@@ -85074,10 +85020,8 @@
       </c>
     </row>
     <row r="865">
-      <c r="A865" t="inlineStr">
-        <is>
-          <t>2707</t>
-        </is>
+      <c r="A865" t="n">
+        <v>2707</v>
       </c>
       <c r="B865" t="inlineStr">
         <is>
@@ -85129,7 +85073,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N865" s="2" t="n">
+      <c r="N865" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O865" t="inlineStr">
@@ -85174,10 +85118,8 @@
       </c>
     </row>
     <row r="866">
-      <c r="A866" t="inlineStr">
-        <is>
-          <t>2712</t>
-        </is>
+      <c r="A866" t="n">
+        <v>2712</v>
       </c>
       <c r="B866" t="inlineStr">
         <is>
@@ -85229,7 +85171,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N866" s="2" t="n">
+      <c r="N866" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O866" t="inlineStr">
@@ -85274,10 +85216,8 @@
       </c>
     </row>
     <row r="867">
-      <c r="A867" t="inlineStr">
-        <is>
-          <t>2713</t>
-        </is>
+      <c r="A867" t="n">
+        <v>2713</v>
       </c>
       <c r="B867" t="inlineStr">
         <is>
@@ -85329,7 +85269,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N867" s="2" t="n">
+      <c r="N867" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="O867" t="inlineStr">
@@ -85374,10 +85314,8 @@
       </c>
     </row>
     <row r="868">
-      <c r="A868" t="inlineStr">
-        <is>
-          <t>2720</t>
-        </is>
+      <c r="A868" t="n">
+        <v>2720</v>
       </c>
       <c r="B868" t="inlineStr">
         <is>
@@ -85429,7 +85367,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N868" s="2" t="n">
+      <c r="N868" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O868" t="inlineStr">
@@ -85474,10 +85412,8 @@
       </c>
     </row>
     <row r="869">
-      <c r="A869" t="inlineStr">
-        <is>
-          <t>2721</t>
-        </is>
+      <c r="A869" t="n">
+        <v>2721</v>
       </c>
       <c r="B869" t="inlineStr">
         <is>
@@ -85529,7 +85465,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N869" s="2" t="n">
+      <c r="N869" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O869" t="inlineStr">
@@ -85574,10 +85510,8 @@
       </c>
     </row>
     <row r="870">
-      <c r="A870" t="inlineStr">
-        <is>
-          <t>2721</t>
-        </is>
+      <c r="A870" t="n">
+        <v>2721</v>
       </c>
       <c r="B870" t="inlineStr">
         <is>
@@ -85629,7 +85563,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N870" s="2" t="n">
+      <c r="N870" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O870" t="inlineStr">
@@ -85674,10 +85608,8 @@
       </c>
     </row>
     <row r="871">
-      <c r="A871" t="inlineStr">
-        <is>
-          <t>2723</t>
-        </is>
+      <c r="A871" t="n">
+        <v>2723</v>
       </c>
       <c r="B871" t="inlineStr">
         <is>
@@ -85729,7 +85661,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N871" s="2" t="n">
+      <c r="N871" s="1" t="n">
         <v>46219</v>
       </c>
       <c r="O871" t="inlineStr">
@@ -85774,10 +85706,8 @@
       </c>
     </row>
     <row r="872">
-      <c r="A872" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A872" t="n">
+        <v>2728</v>
       </c>
       <c r="B872" t="inlineStr">
         <is>
@@ -85829,7 +85759,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N872" s="2" t="n">
+      <c r="N872" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="O872" t="inlineStr">
@@ -85874,10 +85804,8 @@
       </c>
     </row>
     <row r="873">
-      <c r="A873" t="inlineStr">
-        <is>
-          <t>2737</t>
-        </is>
+      <c r="A873" t="n">
+        <v>2737</v>
       </c>
       <c r="B873" t="inlineStr">
         <is>
@@ -85929,7 +85857,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N873" s="2" t="n">
+      <c r="N873" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O873" t="inlineStr">
@@ -85974,10 +85902,8 @@
       </c>
     </row>
     <row r="874">
-      <c r="A874" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
+      <c r="A874" t="n">
+        <v>2813</v>
       </c>
       <c r="B874" t="inlineStr">
         <is>
@@ -86029,7 +85955,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N874" s="2" t="n">
+      <c r="N874" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="O874" t="inlineStr">
@@ -86074,10 +86000,8 @@
       </c>
     </row>
     <row r="875">
-      <c r="A875" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
+      <c r="A875" t="n">
+        <v>2813</v>
       </c>
       <c r="B875" t="inlineStr">
         <is>
@@ -86129,7 +86053,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N875" s="2" t="n">
+      <c r="N875" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="O875" t="inlineStr">
@@ -86174,10 +86098,8 @@
       </c>
     </row>
     <row r="876">
-      <c r="A876" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
+      <c r="A876" t="n">
+        <v>2825</v>
       </c>
       <c r="B876" t="inlineStr">
         <is>
@@ -86229,7 +86151,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N876" s="2" t="n">
+      <c r="N876" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O876" t="inlineStr">
@@ -86274,10 +86196,8 @@
       </c>
     </row>
     <row r="877">
-      <c r="A877" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A877" t="n">
+        <v>2829</v>
       </c>
       <c r="B877" t="inlineStr">
         <is>
@@ -86329,7 +86249,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N877" s="2" t="n">
+      <c r="N877" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O877" t="inlineStr">
@@ -86374,10 +86294,8 @@
       </c>
     </row>
     <row r="878">
-      <c r="A878" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A878" t="n">
+        <v>2829</v>
       </c>
       <c r="B878" t="inlineStr">
         <is>
@@ -86429,7 +86347,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N878" s="2" t="n">
+      <c r="N878" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O878" t="inlineStr">
@@ -86474,10 +86392,8 @@
       </c>
     </row>
     <row r="879">
-      <c r="A879" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
+      <c r="A879" t="n">
+        <v>2830</v>
       </c>
       <c r="B879" t="inlineStr">
         <is>
@@ -86529,7 +86445,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N879" s="2" t="n">
+      <c r="N879" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="O879" t="inlineStr">
@@ -86574,10 +86490,8 @@
       </c>
     </row>
     <row r="880">
-      <c r="A880" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
+      <c r="A880" t="n">
+        <v>2830</v>
       </c>
       <c r="B880" t="inlineStr">
         <is>
@@ -86629,7 +86543,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N880" s="2" t="n">
+      <c r="N880" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O880" t="inlineStr">
@@ -86674,10 +86588,8 @@
       </c>
     </row>
     <row r="881">
-      <c r="A881" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A881" t="n">
+        <v>2832</v>
       </c>
       <c r="B881" t="inlineStr">
         <is>
@@ -86729,7 +86641,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N881" s="2" t="n">
+      <c r="N881" s="1" t="n">
         <v>46168</v>
       </c>
       <c r="O881" t="inlineStr">
@@ -86774,10 +86686,8 @@
       </c>
     </row>
     <row r="882">
-      <c r="A882" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A882" t="n">
+        <v>2833</v>
       </c>
       <c r="B882" t="inlineStr">
         <is>
@@ -86829,7 +86739,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N882" s="2" t="n">
+      <c r="N882" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="O882" t="inlineStr">
@@ -86874,10 +86784,8 @@
       </c>
     </row>
     <row r="883">
-      <c r="A883" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A883" t="n">
+        <v>2833</v>
       </c>
       <c r="B883" t="inlineStr">
         <is>
@@ -86929,7 +86837,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N883" s="2" t="n">
+      <c r="N883" s="1" t="n">
         <v>46119</v>
       </c>
       <c r="O883" t="inlineStr">
@@ -86974,10 +86882,8 @@
       </c>
     </row>
     <row r="884">
-      <c r="A884" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
+      <c r="A884" t="n">
+        <v>2847</v>
       </c>
       <c r="B884" t="inlineStr">
         <is>
@@ -87029,7 +86935,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N884" s="2" t="n">
+      <c r="N884" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O884" t="inlineStr">
@@ -87074,10 +86980,8 @@
       </c>
     </row>
     <row r="885">
-      <c r="A885" t="inlineStr">
-        <is>
-          <t>3114</t>
-        </is>
+      <c r="A885" t="n">
+        <v>3114</v>
       </c>
       <c r="B885" t="inlineStr">
         <is>
@@ -87129,7 +87033,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N885" s="2" t="n">
+      <c r="N885" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="O885" t="inlineStr">
@@ -87174,10 +87078,8 @@
       </c>
     </row>
     <row r="886">
-      <c r="A886" t="inlineStr">
-        <is>
-          <t>3720</t>
-        </is>
+      <c r="A886" t="n">
+        <v>3720</v>
       </c>
       <c r="B886" t="inlineStr">
         <is>
@@ -87229,7 +87131,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N886" s="2" t="n">
+      <c r="N886" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O886" t="inlineStr">
@@ -87274,10 +87176,8 @@
       </c>
     </row>
     <row r="887">
-      <c r="A887" t="inlineStr">
-        <is>
-          <t>4818</t>
-        </is>
+      <c r="A887" t="n">
+        <v>4818</v>
       </c>
       <c r="B887" t="inlineStr">
         <is>
@@ -87329,7 +87229,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N887" s="2" t="n">
+      <c r="N887" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="O887" t="inlineStr">
@@ -87374,10 +87274,8 @@
       </c>
     </row>
     <row r="888">
-      <c r="A888" t="inlineStr">
-        <is>
-          <t>4818</t>
-        </is>
+      <c r="A888" t="n">
+        <v>4818</v>
       </c>
       <c r="B888" t="inlineStr">
         <is>
@@ -87429,7 +87327,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N888" s="2" t="n">
+      <c r="N888" s="1" t="n">
         <v>46217</v>
       </c>
       <c r="O888" t="inlineStr">
@@ -87474,10 +87372,8 @@
       </c>
     </row>
     <row r="889">
-      <c r="A889" t="inlineStr">
-        <is>
-          <t>4818</t>
-        </is>
+      <c r="A889" t="n">
+        <v>4818</v>
       </c>
       <c r="B889" t="inlineStr">
         <is>
@@ -87529,7 +87425,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N889" s="2" t="n">
+      <c r="N889" s="1" t="n">
         <v>46168</v>
       </c>
       <c r="O889" t="inlineStr">
@@ -87574,10 +87470,8 @@
       </c>
     </row>
     <row r="890">
-      <c r="A890" t="inlineStr">
-        <is>
-          <t>4818</t>
-        </is>
+      <c r="A890" t="n">
+        <v>4818</v>
       </c>
       <c r="B890" t="inlineStr">
         <is>
@@ -87629,7 +87523,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N890" s="2" t="n">
+      <c r="N890" s="1" t="n">
         <v>46168</v>
       </c>
       <c r="O890" t="inlineStr">
@@ -87674,10 +87568,8 @@
       </c>
     </row>
     <row r="891">
-      <c r="A891" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A891" t="n">
+        <v>9119</v>
       </c>
       <c r="B891" t="inlineStr">
         <is>
@@ -87729,7 +87621,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N891" s="2" t="n">
+      <c r="N891" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O891" t="inlineStr">
@@ -87774,10 +87666,8 @@
       </c>
     </row>
     <row r="892">
-      <c r="A892" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A892" t="n">
+        <v>9119</v>
       </c>
       <c r="B892" t="inlineStr">
         <is>
@@ -87829,7 +87719,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N892" s="2" t="n">
+      <c r="N892" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O892" t="inlineStr">
@@ -87874,10 +87764,8 @@
       </c>
     </row>
     <row r="893">
-      <c r="A893" t="inlineStr">
-        <is>
-          <t>9119</t>
-        </is>
+      <c r="A893" t="n">
+        <v>9119</v>
       </c>
       <c r="B893" t="inlineStr">
         <is>
@@ -87929,7 +87817,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N893" s="2" t="n">
+      <c r="N893" s="1" t="n">
         <v>46134</v>
       </c>
       <c r="O893" t="inlineStr">
@@ -87974,10 +87862,8 @@
       </c>
     </row>
     <row r="894">
-      <c r="A894" t="inlineStr">
-        <is>
-          <t>9127</t>
-        </is>
+      <c r="A894" t="n">
+        <v>9127</v>
       </c>
       <c r="B894" t="inlineStr">
         <is>
@@ -88029,7 +87915,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N894" s="2" t="n">
+      <c r="N894" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O894" t="inlineStr">
@@ -88074,10 +87960,8 @@
       </c>
     </row>
     <row r="895">
-      <c r="A895" t="inlineStr">
-        <is>
-          <t>9127</t>
-        </is>
+      <c r="A895" t="n">
+        <v>9127</v>
       </c>
       <c r="B895" t="inlineStr">
         <is>
@@ -88129,7 +88013,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N895" s="2" t="n">
+      <c r="N895" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O895" t="inlineStr">
@@ -88174,10 +88058,8 @@
       </c>
     </row>
     <row r="896">
-      <c r="A896" t="inlineStr">
-        <is>
-          <t>9900</t>
-        </is>
+      <c r="A896" t="n">
+        <v>9900</v>
       </c>
       <c r="B896" t="inlineStr">
         <is>
@@ -88229,7 +88111,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N896" s="2" t="n">
+      <c r="N896" s="1" t="n">
         <v>46168</v>
       </c>
       <c r="O896" t="inlineStr">
@@ -88274,10 +88156,8 @@
       </c>
     </row>
     <row r="897">
-      <c r="A897" t="inlineStr">
-        <is>
-          <t>9913</t>
-        </is>
+      <c r="A897" t="n">
+        <v>9913</v>
       </c>
       <c r="B897" t="inlineStr">
         <is>
@@ -88329,7 +88209,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N897" s="2" t="n">
+      <c r="N897" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O897" t="inlineStr">
@@ -88374,10 +88254,8 @@
       </c>
     </row>
     <row r="898">
-      <c r="A898" t="inlineStr">
-        <is>
-          <t>9926</t>
-        </is>
+      <c r="A898" t="n">
+        <v>9926</v>
       </c>
       <c r="B898" t="inlineStr">
         <is>
@@ -88429,7 +88307,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N898" s="2" t="n">
+      <c r="N898" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O898" t="inlineStr">
@@ -88474,10 +88352,8 @@
       </c>
     </row>
     <row r="899">
-      <c r="A899" t="inlineStr">
-        <is>
-          <t>9926</t>
-        </is>
+      <c r="A899" t="n">
+        <v>9926</v>
       </c>
       <c r="B899" t="inlineStr">
         <is>
@@ -88529,7 +88405,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N899" s="2" t="n">
+      <c r="N899" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O899" t="inlineStr">
@@ -88574,10 +88450,8 @@
       </c>
     </row>
     <row r="900">
-      <c r="A900" t="inlineStr">
-        <is>
-          <t>9928</t>
-        </is>
+      <c r="A900" t="n">
+        <v>9928</v>
       </c>
       <c r="B900" t="inlineStr">
         <is>
@@ -88629,7 +88503,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N900" s="2" t="n">
+      <c r="N900" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O900" t="inlineStr">
@@ -88674,10 +88548,8 @@
       </c>
     </row>
     <row r="901">
-      <c r="A901" t="inlineStr">
-        <is>
-          <t>9928</t>
-        </is>
+      <c r="A901" t="n">
+        <v>9928</v>
       </c>
       <c r="B901" t="inlineStr">
         <is>
@@ -88729,7 +88601,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N901" s="2" t="n">
+      <c r="N901" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O901" t="inlineStr">
@@ -88774,10 +88646,8 @@
       </c>
     </row>
     <row r="902">
-      <c r="A902" t="inlineStr">
-        <is>
-          <t>9928</t>
-        </is>
+      <c r="A902" t="n">
+        <v>9928</v>
       </c>
       <c r="B902" t="inlineStr">
         <is>
@@ -88829,7 +88699,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N902" s="2" t="n">
+      <c r="N902" s="1" t="n">
         <v>46147</v>
       </c>
       <c r="O902" t="inlineStr">
@@ -88870,6 +88740,6408 @@
       <c r="V902" t="inlineStr">
         <is>
           <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL CAUCA</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F903" t="n">
+        <v>119345</v>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GOBIERNO Y POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I903" t="n">
+        <v>50</v>
+      </c>
+      <c r="J903" t="n">
+        <v>4</v>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr"/>
+      <c r="M903" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N903" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="O903" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P903" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q903" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R903" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S903" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T903" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U903" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V903" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD TECNOLOGICA DE PEREIRA - UTP</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F904" t="n">
+        <v>119322</v>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANESTESIOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I904" t="n">
+        <v>253</v>
+      </c>
+      <c r="J904" t="n">
+        <v>4</v>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr"/>
+      <c r="M904" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N904" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O904" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P904" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q904" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R904" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S904" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T904" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U904" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V904" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL ATLANTICO</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Puerto Colombia</t>
+        </is>
+      </c>
+      <c r="F905" t="n">
+        <v>119359</v>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL, PROBATORIO Y TECNOLOGÍAS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I905" t="n">
+        <v>26</v>
+      </c>
+      <c r="J905" t="n">
+        <v>2</v>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L905" t="inlineStr"/>
+      <c r="M905" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N905" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O905" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P905" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q905" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R905" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S905" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T905" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U905" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V905" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F906" t="n">
+        <v>119305</v>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA E INNOVACIÓN EN TECNOLOGÍAS</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I906" t="n">
+        <v>48</v>
+      </c>
+      <c r="J906" t="n">
+        <v>3</v>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr"/>
+      <c r="M906" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N906" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O906" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P906" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q906" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R906" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S906" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T906" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U906" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V906" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>1702</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>PONTIFICIA UNIVERSIDAD JAVERIANA</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F907" t="n">
+        <v>119295</v>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIRUGÍA GENERAL</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I907" t="n">
+        <v>263</v>
+      </c>
+      <c r="J907" t="n">
+        <v>4</v>
+      </c>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L907" t="inlineStr"/>
+      <c r="M907" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N907" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O907" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P907" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q907" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R907" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S907" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T907" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U907" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V907" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F908" t="n">
+        <v>119311</v>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN INTELIGENCIA ARTIFICIAL Y APRENDIZAJE  AUTOMÁTICO</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I908" t="n">
+        <v>36</v>
+      </c>
+      <c r="J908" t="n">
+        <v>3</v>
+      </c>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr"/>
+      <c r="M908" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N908" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O908" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P908" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q908" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R908" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S908" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T908" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U908" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V908" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F909" t="n">
+        <v>119386</v>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DERECHO</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I909" t="n">
+        <v>36</v>
+      </c>
+      <c r="J909" t="n">
+        <v>3</v>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L909" t="inlineStr"/>
+      <c r="M909" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N909" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O909" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P909" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q909" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R909" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S909" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T909" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U909" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V909" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F910" t="n">
+        <v>119352</v>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN COMUNICACIÓN DIGITAL E INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I910" t="n">
+        <v>24</v>
+      </c>
+      <c r="J910" t="n">
+        <v>2</v>
+      </c>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L910" t="inlineStr"/>
+      <c r="M910" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N910" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O910" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P910" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q910" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R910" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S910" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T910" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U910" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V910" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F911" t="n">
+        <v>119388</v>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I911" t="n">
+        <v>28</v>
+      </c>
+      <c r="J911" t="n">
+        <v>2</v>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr"/>
+      <c r="M911" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N911" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O911" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P911" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q911" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R911" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S911" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T911" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U911" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V911" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F912" t="n">
+        <v>119389</v>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I912" t="n">
+        <v>28</v>
+      </c>
+      <c r="J912" t="n">
+        <v>2</v>
+      </c>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L912" t="inlineStr"/>
+      <c r="M912" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N912" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O912" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P912" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q912" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R912" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S912" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T912" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U912" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V912" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F913" t="n">
+        <v>119350</v>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN COMUNICACIÓN Y REPUTACIÓN CORPORATIVA</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I913" t="n">
+        <v>24</v>
+      </c>
+      <c r="J913" t="n">
+        <v>2</v>
+      </c>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr"/>
+      <c r="M913" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N913" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O913" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P913" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q913" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R913" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S913" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T913" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U913" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V913" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F914" t="n">
+        <v>119325</v>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CONTRATACIÓN ESTATAL</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I914" t="n">
+        <v>24</v>
+      </c>
+      <c r="J914" t="n">
+        <v>2</v>
+      </c>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L914" t="inlineStr"/>
+      <c r="M914" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N914" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="O914" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P914" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q914" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R914" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S914" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T914" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U914" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V914" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F915" t="n">
+        <v>119341</v>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO DE LA RESPONSABILIDAD</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I915" t="n">
+        <v>24</v>
+      </c>
+      <c r="J915" t="n">
+        <v>2</v>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr"/>
+      <c r="M915" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N915" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O915" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P915" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q915" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R915" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S915" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T915" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U915" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V915" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAFIT-</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F916" t="n">
+        <v>119411</v>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN DE TECNOLOGÍAS DE INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I916" t="n">
+        <v>24</v>
+      </c>
+      <c r="J916" t="n">
+        <v>2</v>
+      </c>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr"/>
+      <c r="M916" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N916" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O916" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P916" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q916" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R916" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S916" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T916" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U916" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V916" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F917" t="n">
+        <v>119349</v>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CONTRATACIÓN ESTATAL Y DERECHO SANCIONATORIO</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I917" t="n">
+        <v>23</v>
+      </c>
+      <c r="J917" t="n">
+        <v>2</v>
+      </c>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L917" t="inlineStr"/>
+      <c r="M917" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="N917" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O917" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P917" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q917" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R917" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S917" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T917" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U917" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V917" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>1719</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F918" t="n">
+        <v>119339</v>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DERECHO DEL TRABAJO Y SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I918" t="n">
+        <v>49</v>
+      </c>
+      <c r="J918" t="n">
+        <v>4</v>
+      </c>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L918" t="inlineStr"/>
+      <c r="M918" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N918" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="O918" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P918" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q918" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R918" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S918" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T918" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U918" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V918" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>1719</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F919" t="n">
+        <v>119355</v>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN ECONÓMICA Y EVALUACIÓN DE IMPACTO</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I919" t="n">
+        <v>42</v>
+      </c>
+      <c r="J919" t="n">
+        <v>3</v>
+      </c>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr"/>
+      <c r="M919" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N919" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O919" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P919" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q919" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R919" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S919" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T919" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U919" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V919" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F920" t="n">
+        <v>119319</v>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN SOSTENIBILIDAD</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I920" t="n">
+        <v>80</v>
+      </c>
+      <c r="J920" t="n">
+        <v>3</v>
+      </c>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr"/>
+      <c r="M920" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N920" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O920" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P920" t="inlineStr">
+        <is>
+          <t>Medio ambiente</t>
+        </is>
+      </c>
+      <c r="Q920" t="inlineStr">
+        <is>
+          <t>Ciencias del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R920" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S920" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T920" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U920" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V920" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F921" t="n">
+        <v>119353</v>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GOBIERNO Y POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I921" t="n">
+        <v>25</v>
+      </c>
+      <c r="J921" t="n">
+        <v>2</v>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr"/>
+      <c r="M921" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N921" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O921" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P921" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q921" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R921" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S921" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T921" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U921" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V921" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>1733</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SERGIO ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F922" t="n">
+        <v>119313</v>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I922" t="n">
+        <v>45</v>
+      </c>
+      <c r="J922" t="n">
+        <v>3</v>
+      </c>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr"/>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N922" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O922" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P922" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q922" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R922" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S922" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T922" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U922" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V922" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE BOYACA UNIBOYACA</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F923" t="n">
+        <v>119382</v>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN SALUD PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I923" t="n">
+        <v>95</v>
+      </c>
+      <c r="J923" t="n">
+        <v>7</v>
+      </c>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr"/>
+      <c r="M923" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N923" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O923" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P923" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q923" t="inlineStr">
+        <is>
+          <t>Salud no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R923" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S923" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T923" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U923" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V923" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE BOYACA UNIBOYACA</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F924" t="n">
+        <v>119398</v>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I924" t="n">
+        <v>42</v>
+      </c>
+      <c r="J924" t="n">
+        <v>3</v>
+      </c>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L924" t="inlineStr"/>
+      <c r="M924" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N924" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O924" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P924" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q924" t="inlineStr">
+        <is>
+          <t>Salud no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R924" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S924" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T924" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U924" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V924" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SALLE</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F925" t="n">
+        <v>119395</v>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ACOMPAÑAMIENTO PSICOSOCIAL</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I925" t="n">
+        <v>47</v>
+      </c>
+      <c r="J925" t="n">
+        <v>3</v>
+      </c>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L925" t="inlineStr"/>
+      <c r="M925" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N925" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O925" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P925" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q925" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R925" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S925" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T925" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U925" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V925" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LIBRE</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F926" t="n">
+        <v>119407</v>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN INGENIERÍA DE LA SOSTENIBILIDAD</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I926" t="n">
+        <v>90</v>
+      </c>
+      <c r="J926" t="n">
+        <v>6</v>
+      </c>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L926" t="inlineStr"/>
+      <c r="M926" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N926" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="O926" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P926" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q926" t="inlineStr">
+        <is>
+          <t>Tecnología de protección del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R926" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S926" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T926" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U926" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V926" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>1814</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA LATINOAMERICANA-UNAULA-</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F927" t="n">
+        <v>119393</v>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO LABORAL Y SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I927" t="n">
+        <v>24</v>
+      </c>
+      <c r="J927" t="n">
+        <v>2</v>
+      </c>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L927" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="M927" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N927" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O927" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P927" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q927" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R927" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S927" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T927" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U927" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V927" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>1816</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F928" t="n">
+        <v>119332</v>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTERVENCIÓN COMUNITARIA</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I928" t="n">
+        <v>22</v>
+      </c>
+      <c r="J928" t="n">
+        <v>2</v>
+      </c>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr"/>
+      <c r="M928" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N928" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O928" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P928" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q928" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R928" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S928" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T928" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U928" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V928" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="F929" t="n">
+        <v>119333</v>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANÁLISIS Y DISEÑO DE ESTRUCTURAS</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I929" t="n">
+        <v>24</v>
+      </c>
+      <c r="J929" t="n">
+        <v>2</v>
+      </c>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L929" t="inlineStr"/>
+      <c r="M929" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N929" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O929" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P929" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q929" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R929" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S929" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T929" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U929" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V929" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="F930" t="n">
+        <v>119337</v>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO LABORAL Y SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I930" t="n">
+        <v>19</v>
+      </c>
+      <c r="J930" t="n">
+        <v>2</v>
+      </c>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L930" t="inlineStr"/>
+      <c r="M930" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N930" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O930" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P930" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q930" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R930" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S930" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T930" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U930" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V930" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="F931" t="n">
+        <v>119335</v>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PENAL</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I931" t="n">
+        <v>24</v>
+      </c>
+      <c r="J931" t="n">
+        <v>2</v>
+      </c>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L931" t="inlineStr"/>
+      <c r="M931" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N931" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O931" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P931" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q931" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R931" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S931" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T931" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U931" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V931" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F932" t="n">
+        <v>119399</v>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN FAMILIA Y GÉNERO</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I932" t="n">
+        <v>20</v>
+      </c>
+      <c r="J932" t="n">
+        <v>2</v>
+      </c>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L932" t="inlineStr"/>
+      <c r="M932" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N932" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O932" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P932" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q932" t="inlineStr">
+        <is>
+          <t>Sociología, Antropología y estudios culturales</t>
+        </is>
+      </c>
+      <c r="R932" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S932" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T932" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U932" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V932" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="F933" t="n">
+        <v>119331</v>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GEOTECNIA</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I933" t="n">
+        <v>24</v>
+      </c>
+      <c r="J933" t="n">
+        <v>2</v>
+      </c>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L933" t="inlineStr"/>
+      <c r="M933" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N933" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O933" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P933" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q933" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R933" t="inlineStr">
+        <is>
+          <t>Arquitectura y afines</t>
+        </is>
+      </c>
+      <c r="S933" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T933" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U933" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V933" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F934" t="n">
+        <v>119336</v>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DERECHO</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I934" t="n">
+        <v>40</v>
+      </c>
+      <c r="J934" t="n">
+        <v>3</v>
+      </c>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L934" t="inlineStr"/>
+      <c r="M934" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N934" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O934" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P934" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q934" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R934" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S934" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T934" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U934" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V934" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>1819</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F935" t="n">
+        <v>119400</v>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I935" t="n">
+        <v>22</v>
+      </c>
+      <c r="J935" t="n">
+        <v>2</v>
+      </c>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr"/>
+      <c r="M935" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N935" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="O935" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P935" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q935" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R935" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S935" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T935" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U935" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V935" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F936" t="n">
+        <v>119354</v>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN BIOCIENCIAS</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I936" t="n">
+        <v>65</v>
+      </c>
+      <c r="J936" t="n">
+        <v>6</v>
+      </c>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L936" t="inlineStr"/>
+      <c r="M936" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N936" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O936" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P936" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines</t>
+        </is>
+      </c>
+      <c r="Q936" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R936" t="inlineStr">
+        <is>
+          <t>Biología, microbiología y afines</t>
+        </is>
+      </c>
+      <c r="S936" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T936" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U936" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V936" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F937" t="n">
+        <v>119321</v>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN NEUROEDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I937" t="n">
+        <v>36</v>
+      </c>
+      <c r="J937" t="n">
+        <v>6</v>
+      </c>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L937" t="inlineStr"/>
+      <c r="M937" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N937" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O937" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P937" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q937" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R937" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S937" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T937" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U937" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V937" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2209</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>POLITECNICO COLOMBIANO JAIME ISAZA CADAVID</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F938" t="n">
+        <v>119417</v>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN SALUD Y SEGURIDAD LABORAL</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I938" t="n">
+        <v>64</v>
+      </c>
+      <c r="J938" t="n">
+        <v>2</v>
+      </c>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L938" t="inlineStr"/>
+      <c r="M938" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N938" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O938" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="P938" t="inlineStr">
+        <is>
+          <t>Servicios de higiene y salud ocupacional</t>
+        </is>
+      </c>
+      <c r="Q938" t="inlineStr">
+        <is>
+          <t>Salud y protección laboral</t>
+        </is>
+      </c>
+      <c r="R938" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S938" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T938" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U938" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V938" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F939" t="n">
+        <v>119309</v>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN TRIBUTARIA</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I939" t="n">
+        <v>26</v>
+      </c>
+      <c r="J939" t="n">
+        <v>2</v>
+      </c>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L939" t="inlineStr"/>
+      <c r="M939" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N939" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O939" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P939" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q939" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R939" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S939" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T939" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U939" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V939" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATÓLICA LUIS AMIGÓ</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F940" t="n">
+        <v>119316</v>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I940" t="n">
+        <v>80</v>
+      </c>
+      <c r="J940" t="n">
+        <v>6</v>
+      </c>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L940" t="inlineStr"/>
+      <c r="M940" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N940" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="O940" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P940" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q940" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R940" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S940" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T940" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U940" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V940" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATÓLICA LUIS AMIGÓ</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F941" t="n">
+        <v>119415</v>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN NEUROPSICOPEDAGOGÍA INFANTIL</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I941" t="n">
+        <v>24</v>
+      </c>
+      <c r="J941" t="n">
+        <v>2</v>
+      </c>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L941" t="inlineStr"/>
+      <c r="M941" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N941" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O941" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P941" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q941" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R941" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S941" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T941" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U941" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V941" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F942" t="n">
+        <v>119344</v>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIBERSEGURIDAD</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I942" t="n">
+        <v>28</v>
+      </c>
+      <c r="J942" t="n">
+        <v>2</v>
+      </c>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L942" t="inlineStr"/>
+      <c r="M942" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N942" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O942" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P942" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q942" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R942" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S942" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T942" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U942" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V942" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA SANITAS</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F943" t="n">
+        <v>119188</v>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANALÍTICA DE DATOS APLICADA AL SECTOR SALUD</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I943" t="n">
+        <v>30</v>
+      </c>
+      <c r="J943" t="n">
+        <v>2</v>
+      </c>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr"/>
+      <c r="M943" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N943" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="O943" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P943" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q943" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R943" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S943" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T943" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U943" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V943" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SIMÓN BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>San José de Cúcuta</t>
+        </is>
+      </c>
+      <c r="F944" t="n">
+        <v>119374</v>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN FAMILIA, DESARROLLO Y CUIDADO</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I944" t="n">
+        <v>42</v>
+      </c>
+      <c r="J944" t="n">
+        <v>3</v>
+      </c>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L944" t="inlineStr"/>
+      <c r="M944" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N944" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O944" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P944" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q944" t="inlineStr">
+        <is>
+          <t>Sociología, Antropología y estudios culturales</t>
+        </is>
+      </c>
+      <c r="R944" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S944" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T944" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U944" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V944" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAN</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F945" t="n">
+        <v>119397</v>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CREACIÓN DE CONTENIDO Y SOCIAL LISTENING</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I945" t="n">
+        <v>36</v>
+      </c>
+      <c r="J945" t="n">
+        <v>2</v>
+      </c>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L945" t="inlineStr"/>
+      <c r="M945" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N945" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O945" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P945" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="Q945" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="R945" t="inlineStr">
+        <is>
+          <t>Otros programas asociados a bellas artes</t>
+        </is>
+      </c>
+      <c r="S945" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T945" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U945" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V945" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAN</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F946" t="n">
+        <v>119396</v>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CREACIÓN DE CONTENIDO Y SOCIAL LISTENING</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I946" t="n">
+        <v>36</v>
+      </c>
+      <c r="J946" t="n">
+        <v>2</v>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr"/>
+      <c r="M946" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N946" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O946" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P946" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="Q946" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a artes y humanidades</t>
+        </is>
+      </c>
+      <c r="R946" t="inlineStr">
+        <is>
+          <t>Otros programas asociados a bellas artes</t>
+        </is>
+      </c>
+      <c r="S946" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T946" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U946" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V946" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAN</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F947" t="n">
+        <v>119358</v>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA EN INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I947" t="n">
+        <v>43</v>
+      </c>
+      <c r="J947" t="n">
+        <v>3</v>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr"/>
+      <c r="M947" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N947" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O947" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P947" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q947" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R947" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S947" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T947" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U947" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V947" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAN</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F948" t="n">
+        <v>119357</v>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA EN INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I948" t="n">
+        <v>43</v>
+      </c>
+      <c r="J948" t="n">
+        <v>3</v>
+      </c>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L948" t="inlineStr"/>
+      <c r="M948" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N948" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O948" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P948" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q948" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R948" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S948" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T948" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U948" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V948" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2818</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE SANTA ROSA DE CABAL-UNISARC-</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Cabal</t>
+        </is>
+      </c>
+      <c r="F949" t="n">
+        <v>119420</v>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PROTECCIÓN Y BIENESTAR ANIMAL</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I949" t="n">
+        <v>28</v>
+      </c>
+      <c r="J949" t="n">
+        <v>2</v>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr"/>
+      <c r="M949" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N949" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O949" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P949" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="Q949" t="inlineStr">
+        <is>
+          <t>Producción agrícola y ganadera</t>
+        </is>
+      </c>
+      <c r="R949" t="inlineStr">
+        <is>
+          <t>Zootecnia</t>
+        </is>
+      </c>
+      <c r="S949" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T949" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U949" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V949" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F950" t="n">
+        <v>119409</v>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA Y AUDITORÍA DE LA CALIDAD EN SALUD</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I950" t="n">
+        <v>24</v>
+      </c>
+      <c r="J950" t="n">
+        <v>2</v>
+      </c>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr"/>
+      <c r="M950" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N950" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="O950" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P950" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q950" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R950" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S950" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T950" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U950" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V950" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F951" t="n">
+        <v>119410</v>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EVALUACIÓN Y ASEGURAMIENTO DE LA CALIDAD DE LA EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I951" t="n">
+        <v>42</v>
+      </c>
+      <c r="J951" t="n">
+        <v>4</v>
+      </c>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L951" t="inlineStr"/>
+      <c r="M951" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N951" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="O951" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P951" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q951" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R951" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S951" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T951" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U951" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V951" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F952" t="n">
+        <v>119412</v>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA ESTRATÉGICA DE OPERACIONES</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I952" t="n">
+        <v>42</v>
+      </c>
+      <c r="J952" t="n">
+        <v>4</v>
+      </c>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr"/>
+      <c r="M952" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N952" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="O952" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P952" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q952" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R952" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S952" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T952" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U952" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V952" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F953" t="n">
+        <v>119348</v>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN NEUROEDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I953" t="n">
+        <v>42</v>
+      </c>
+      <c r="J953" t="n">
+        <v>4</v>
+      </c>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L953" t="inlineStr"/>
+      <c r="M953" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N953" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O953" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P953" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q953" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R953" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S953" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T953" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U953" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V953" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DE BARRANQUILLA - IUB</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F954" t="n">
+        <v>119369</v>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE SISTEMAS INTEGRADOS DE GESTIÓN</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I954" t="n">
+        <v>30</v>
+      </c>
+      <c r="J954" t="n">
+        <v>2</v>
+      </c>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L954" t="inlineStr"/>
+      <c r="M954" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N954" s="2" t="n">
+        <v>45650</v>
+      </c>
+      <c r="O954" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P954" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q954" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R954" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S954" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T954" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U954" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V954" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>4810</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA CENDA</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F955" t="n">
+        <v>119360</v>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I955" t="n">
+        <v>24</v>
+      </c>
+      <c r="J955" t="n">
+        <v>2</v>
+      </c>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr"/>
+      <c r="M955" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N955" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="O955" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P955" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q955" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R955" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S955" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T955" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U955" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V955" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F956" t="n">
+        <v>119419</v>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL Y PROBATORIO</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I956" t="n">
+        <v>28</v>
+      </c>
+      <c r="J956" t="n">
+        <v>2</v>
+      </c>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L956" t="inlineStr"/>
+      <c r="M956" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N956" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O956" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P956" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q956" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R956" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S956" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T956" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U956" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V956" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F957" t="n">
+        <v>119418</v>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PROCESAL Y PROBATORIO</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I957" t="n">
+        <v>28</v>
+      </c>
+      <c r="J957" t="n">
+        <v>2</v>
+      </c>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr"/>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N957" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O957" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P957" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q957" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R957" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S957" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T957" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U957" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V957" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F958" t="n">
+        <v>119384</v>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE LA FELICIDAD ORGANIZACIONAL</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I958" t="n">
+        <v>28</v>
+      </c>
+      <c r="J958" t="n">
+        <v>2</v>
+      </c>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L958" t="inlineStr"/>
+      <c r="M958" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N958" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O958" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P958" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q958" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R958" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S958" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T958" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U958" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V958" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>9127</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE SABANETA - UNISABANETA</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="F959" t="n">
+        <v>119380</v>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>ESPECIACLIZACIÓN EN GERENCIAL DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I959" t="n">
+        <v>24</v>
+      </c>
+      <c r="J959" t="n">
+        <v>2</v>
+      </c>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L959" t="inlineStr"/>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N959" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O959" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P959" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q959" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R959" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S959" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T959" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U959" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V959" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>9127</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE SABANETA - UNISABANETA</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="F960" t="n">
+        <v>119379</v>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>ESPECIACLIZACIÓN EN GERENCIAL DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I960" t="n">
+        <v>24</v>
+      </c>
+      <c r="J960" t="n">
+        <v>2</v>
+      </c>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr"/>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N960" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O960" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P960" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q960" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R960" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S960" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T960" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U960" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V960" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F961" t="n">
+        <v>119391</v>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA INTEGRAL DEL RIESGO</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I961" t="n">
+        <v>47</v>
+      </c>
+      <c r="J961" t="n">
+        <v>3</v>
+      </c>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr"/>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N961" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O961" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P961" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q961" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R961" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S961" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T961" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U961" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V961" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>9926</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA INTERNACIONAL DE LA RIOJA - UNIR</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F962" t="n">
+        <v>119392</v>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CONTRATACIÓN ESTATAL</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I962" t="n">
+        <v>24</v>
+      </c>
+      <c r="J962" t="n">
+        <v>2</v>
+      </c>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L962" t="inlineStr"/>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N962" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O962" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P962" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q962" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R962" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S962" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T962" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U962" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V962" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>9941</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN INSTITUCIÓN UNIVERSITARIA SALUD COLOMBIA - UNISALUD</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F963" t="n">
+        <v>119363</v>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANESTESIOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I963" t="n">
+        <v>207</v>
+      </c>
+      <c r="J963" t="n">
+        <v>6</v>
+      </c>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L963" t="inlineStr"/>
+      <c r="M963" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N963" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O963" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P963" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q963" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R963" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S963" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T963" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U963" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V963" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>9941</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN INSTITUCIÓN UNIVERSITARIA SALUD COLOMBIA - UNISALUD</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F964" t="n">
+        <v>119323</v>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN CIRUGÍA PLÁSTICA RECONSTRUCTIVA Y ESTÉTICA</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I964" t="n">
+        <v>273</v>
+      </c>
+      <c r="J964" t="n">
+        <v>8</v>
+      </c>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr"/>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N964" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O964" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P964" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q964" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R964" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S964" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T964" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U964" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V964" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>9941</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN INSTITUCIÓN UNIVERSITARIA SALUD COLOMBIA - UNISALUD</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F965" t="n">
+        <v>119326</v>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GINECOLOGÍA Y OBSTETRICIA</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I965" t="n">
+        <v>270</v>
+      </c>
+      <c r="J965" t="n">
+        <v>8</v>
+      </c>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr"/>
+      <c r="M965" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N965" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="O965" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P965" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q965" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R965" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S965" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T965" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U965" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V965" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>9941</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN INSTITUCIÓN UNIVERSITARIA SALUD COLOMBIA - UNISALUD</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F966" t="n">
+        <v>119387</v>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PERFUSIÓN Y CIRCULACIÓN EXTRACORPÓREA</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I966" t="n">
+        <v>71</v>
+      </c>
+      <c r="J966" t="n">
+        <v>3</v>
+      </c>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L966" t="inlineStr"/>
+      <c r="M966" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N966" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O966" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P966" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q966" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R966" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S966" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T966" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="U966" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="V966" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
         </is>
       </c>
     </row>
